--- a/research/traditional_assets/database/data/belgium/belgium_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_beverage_alcoholic.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0179</v>
+        <v>0.02125</v>
       </c>
       <c r="E2">
         <v>-0.0726</v>
@@ -599,22 +599,22 @@
         <v>0.103</v>
       </c>
       <c r="G2">
-        <v>0.3108922558922559</v>
+        <v>0.3103619266471139</v>
       </c>
       <c r="H2">
-        <v>0.3065824915824916</v>
+        <v>0.306061675015202</v>
       </c>
       <c r="I2">
-        <v>0.2511279461279461</v>
+        <v>0.2504918412803999</v>
       </c>
       <c r="J2">
-        <v>0.1880813048517967</v>
+        <v>0.2190483689323216</v>
       </c>
       <c r="K2">
-        <v>6526</v>
+        <v>6521.13</v>
       </c>
       <c r="L2">
-        <v>0.1098653198653199</v>
+        <v>0.1095410153297252</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -638,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>7.320621948684671E-05</v>
       </c>
       <c r="W2">
-        <v>0.08424993545055512</v>
+        <v>0.02141918541235239</v>
       </c>
       <c r="X2">
-        <v>0.1024066674169306</v>
+        <v>0.09493896508457489</v>
       </c>
       <c r="Y2">
-        <v>-0.01815673196637546</v>
+        <v>-0.07351977967222251</v>
       </c>
       <c r="Z2">
-        <v>0.3747326717682462</v>
+        <v>0.3752620823779677</v>
       </c>
       <c r="AA2">
-        <v>0.07048020987677177</v>
+        <v>0.01599550488622392</v>
       </c>
       <c r="AB2">
-        <v>0.07740242921038981</v>
+        <v>0.07824157203049939</v>
       </c>
       <c r="AC2">
-        <v>-0.006922219333618043</v>
+        <v>-0.06224606714427548</v>
       </c>
       <c r="AD2">
-        <v>78256</v>
+        <v>78283.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>78256</v>
+        <v>78283.7</v>
       </c>
       <c r="AG2">
-        <v>78256</v>
+        <v>78276.48</v>
       </c>
       <c r="AH2">
-        <v>0.4427158321712344</v>
+        <v>0.442507794959222</v>
       </c>
       <c r="AI2">
-        <v>0.4672055785740725</v>
+        <v>0.4669681017641708</v>
       </c>
       <c r="AJ2">
-        <v>0.4427158321712344</v>
+        <v>0.4424850417163222</v>
       </c>
       <c r="AK2">
-        <v>0.4672055785740725</v>
+        <v>0.4669451442440994</v>
       </c>
       <c r="AL2">
-        <v>3666</v>
+        <v>3666.819</v>
       </c>
       <c r="AM2">
-        <v>3113</v>
+        <v>3113.819</v>
       </c>
       <c r="AN2">
-        <v>4.250040732091457</v>
+        <v>4.249403439747957</v>
       </c>
       <c r="AO2">
-        <v>4.069012547735952</v>
+        <v>4.066775589414148</v>
       </c>
       <c r="AP2">
-        <v>4.250040732091457</v>
+        <v>4.249011523003667</v>
       </c>
       <c r="AQ2">
-        <v>4.791840668165756</v>
+        <v>4.789016317261857</v>
       </c>
     </row>
     <row r="3">
@@ -781,10 +781,10 @@
         <v>0.08424993545055512</v>
       </c>
       <c r="X3">
-        <v>0.1024066674169306</v>
+        <v>0.1023802315451649</v>
       </c>
       <c r="Y3">
-        <v>-0.01815673196637546</v>
+        <v>-0.0181302960946098</v>
       </c>
       <c r="Z3">
         <v>0.3747326717682462</v>
@@ -793,10 +793,10 @@
         <v>0.07048020987677177</v>
       </c>
       <c r="AB3">
-        <v>0.07740242921038981</v>
+        <v>0.07738769691759206</v>
       </c>
       <c r="AC3">
-        <v>-0.006922219333618043</v>
+        <v>-0.006907487040820295</v>
       </c>
       <c r="AD3">
         <v>78256</v>
@@ -839,6 +839,134 @@
       </c>
       <c r="AQ3">
         <v>4.791840668165756</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brouwerij Handelsmaatschappij NV (ENXTBR:COBH)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Beverage (Alcoholic)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0246</v>
+      </c>
+      <c r="G4">
+        <v>0.07062404870624048</v>
+      </c>
+      <c r="H4">
+        <v>0.07062404870624048</v>
+      </c>
+      <c r="I4">
+        <v>-0.03706240487062405</v>
+      </c>
+      <c r="J4">
+        <v>-0.03706240487062405</v>
+      </c>
+      <c r="K4">
+        <v>-4.87</v>
+      </c>
+      <c r="L4">
+        <v>-0.03706240487062405</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>7.22</v>
+      </c>
+      <c r="V4">
+        <v>0.0611864406779661</v>
+      </c>
+      <c r="W4">
+        <v>-0.04141156462585034</v>
+      </c>
+      <c r="X4">
+        <v>0.08749769862398486</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1289092632498352</v>
+      </c>
+      <c r="Z4">
+        <v>1.038497103430834</v>
+      </c>
+      <c r="AA4">
+        <v>-0.03848920010432392</v>
+      </c>
+      <c r="AB4">
+        <v>0.07909544714340673</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1175846472477307</v>
+      </c>
+      <c r="AD4">
+        <v>27.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>27.7</v>
+      </c>
+      <c r="AG4">
+        <v>20.48</v>
+      </c>
+      <c r="AH4">
+        <v>0.1901166781056967</v>
+      </c>
+      <c r="AI4">
+        <v>0.1916955017301038</v>
+      </c>
+      <c r="AJ4">
+        <v>0.14789139225881</v>
+      </c>
+      <c r="AK4">
+        <v>0.1491841491841492</v>
+      </c>
+      <c r="AL4">
+        <v>0.819</v>
+      </c>
+      <c r="AM4">
+        <v>0.819</v>
+      </c>
+      <c r="AN4">
+        <v>2.984913793103448</v>
+      </c>
+      <c r="AO4">
+        <v>-5.946275946275946</v>
+      </c>
+      <c r="AP4">
+        <v>2.206896551724138</v>
+      </c>
+      <c r="AQ4">
+        <v>-5.946275946275946</v>
       </c>
     </row>
   </sheetData>
@@ -1133,49 +1261,49 @@
         <v>4.06901254773595</v>
       </c>
       <c r="F2">
-        <v>3.01169748312395</v>
+        <v>3.00597023151562</v>
       </c>
       <c r="G2">
         <v>4.25004073209146</v>
       </c>
       <c r="H2">
-        <v>4.31996822896866</v>
+        <v>4.51196681692283</v>
       </c>
       <c r="I2">
         <v>0.442715832171234</v>
       </c>
       <c r="J2">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="K2">
         <v>98507.5</v>
       </c>
       <c r="L2">
-        <v>95004.9153897077</v>
+        <v>94344.10721432741</v>
       </c>
       <c r="M2">
         <v>176763.5</v>
       </c>
       <c r="N2">
-        <v>174548.490389708</v>
+        <v>177422.952214327</v>
       </c>
       <c r="O2">
         <v>78256</v>
       </c>
       <c r="P2">
-        <v>79543.575</v>
+        <v>83078.845</v>
       </c>
       <c r="Q2">
-        <v>0.0774024292103898</v>
+        <v>0.07738769691759211</v>
       </c>
       <c r="R2">
-        <v>0.0782162616610452</v>
+        <v>0.0771493315941065</v>
       </c>
       <c r="S2">
         <v>0.0459274624969006</v>
       </c>
       <c r="T2">
-        <v>0.0478774624969006</v>
+        <v>0.0459274624969006</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1316,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.102406667416931</v>
+        <v>0.102380231545165</v>
       </c>
       <c r="X2">
-        <v>0.103038915522618</v>
+        <v>0.104836649472761</v>
       </c>
       <c r="Y2">
         <v>1.10285402554486</v>
       </c>
       <c r="Z2">
-        <v>1.11517196264165</v>
+        <v>1.15073418308199</v>
       </c>
       <c r="AA2">
         <v>78256</v>
@@ -1230,7 +1358,7 @@
         <v>98507.5</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08127200398584784</v>
+        <v>0.08125543821026995</v>
       </c>
       <c r="C2">
-        <v>166704.9308931385</v>
+        <v>166709.2961049704</v>
       </c>
       <c r="D2">
-        <v>166704.9308931385</v>
+        <v>166709.2961049704</v>
       </c>
       <c r="E2">
         <v>-78256</v>
@@ -1469,19 +1597,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08127200398584784</v>
+        <v>0.08125543821026995</v>
       </c>
       <c r="T2">
         <v>0.6910924838905984</v>
       </c>
       <c r="U2">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1628,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08115759860085223</v>
+        <v>0.08113057423971329</v>
       </c>
       <c r="C3">
-        <v>165218.2313464768</v>
+        <v>165248.3463270674</v>
       </c>
       <c r="D3">
-        <v>166985.8663464768</v>
+        <v>167015.9813270674</v>
       </c>
       <c r="E3">
         <v>-76488.36500000001</v>
@@ -1533,37 +1661,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M3">
-        <v>101.8805008942784</v>
+        <v>99.40581189427844</v>
       </c>
       <c r="N3">
-        <v>15190.8950093098</v>
+        <v>15193.36969830981</v>
       </c>
       <c r="O3">
-        <v>3797.723752327451</v>
+        <v>3798.342424577451</v>
       </c>
       <c r="P3">
-        <v>11393.17125698235</v>
+        <v>11395.02727373235</v>
       </c>
       <c r="Q3">
-        <v>14889.17125698235</v>
+        <v>14891.02727373235</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08154073128877093</v>
+        <v>0.08152404001489322</v>
       </c>
       <c r="T3">
         <v>0.6963280330109817</v>
       </c>
       <c r="U3">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>150.1050286950731</v>
+        <v>153.8418651664803</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1710,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08104319321585661</v>
+        <v>0.08100571026915664</v>
       </c>
       <c r="C4">
-        <v>163732.480277572</v>
+        <v>163788.5270100983</v>
       </c>
       <c r="D4">
-        <v>167267.750277572</v>
+        <v>167323.7970100983</v>
       </c>
       <c r="E4">
         <v>-74720.73</v>
@@ -1615,37 +1743,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M4">
-        <v>203.7610017885569</v>
+        <v>198.8116237885569</v>
       </c>
       <c r="N4">
-        <v>15089.01450841553</v>
+        <v>15093.96388641553</v>
       </c>
       <c r="O4">
-        <v>3772.253627103882</v>
+        <v>3773.490971603881</v>
       </c>
       <c r="P4">
-        <v>11316.76088131165</v>
+        <v>11320.47291481164</v>
       </c>
       <c r="Q4">
-        <v>14812.76088131165</v>
+        <v>14816.47291481164</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08181494282236593</v>
+        <v>0.08179812348899859</v>
       </c>
       <c r="T4">
         <v>0.7016704300725974</v>
       </c>
       <c r="U4">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>75.05251434753654</v>
+        <v>76.92093258324013</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1792,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08092878783086099</v>
+        <v>0.08088084629859994</v>
       </c>
       <c r="C5">
-        <v>162247.6824978382</v>
+        <v>162329.8444160288</v>
       </c>
       <c r="D5">
-        <v>167550.5874978382</v>
+        <v>167632.7494160288</v>
       </c>
       <c r="E5">
         <v>-72953.095</v>
@@ -1697,37 +1825,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M5">
-        <v>305.6415026828353</v>
+        <v>298.2174356828353</v>
       </c>
       <c r="N5">
-        <v>14987.13400752125</v>
+        <v>14994.55807452125</v>
       </c>
       <c r="O5">
-        <v>3746.783501880312</v>
+        <v>3748.639518630312</v>
       </c>
       <c r="P5">
-        <v>11240.35050564094</v>
+        <v>11245.91855589094</v>
       </c>
       <c r="Q5">
-        <v>14736.35050564094</v>
+        <v>14741.91855589094</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08209480820201442</v>
+        <v>0.0820778581687556</v>
       </c>
       <c r="T5">
         <v>0.7071229796509473</v>
       </c>
       <c r="U5">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.03500956502436</v>
+        <v>51.28062172216009</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1874,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08081438244586539</v>
+        <v>0.08075598232804329</v>
       </c>
       <c r="C6">
-        <v>160763.8428512879</v>
+        <v>160872.3048531594</v>
       </c>
       <c r="D6">
-        <v>167834.3828512879</v>
+        <v>167942.8448531594</v>
       </c>
       <c r="E6">
         <v>-71185.46000000001</v>
@@ -1779,37 +1907,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M6">
-        <v>407.5220035771138</v>
+        <v>397.6232475771138</v>
       </c>
       <c r="N6">
-        <v>14885.25350662697</v>
+        <v>14895.15226262697</v>
       </c>
       <c r="O6">
-        <v>3721.313376656742</v>
+        <v>3723.788065656742</v>
       </c>
       <c r="P6">
-        <v>11163.94012997023</v>
+        <v>11171.36419697023</v>
       </c>
       <c r="Q6">
-        <v>14659.94012997023</v>
+        <v>14667.36419697023</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08238050411040559</v>
+        <v>0.08236342065434091</v>
       </c>
       <c r="T6">
         <v>0.7126891240121797</v>
       </c>
       <c r="U6">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.52625717376826</v>
+        <v>38.46046629162007</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1956,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08069997706086977</v>
+        <v>0.08063111835748661</v>
       </c>
       <c r="C7">
-        <v>159280.966214808</v>
+        <v>159415.9146765548</v>
       </c>
       <c r="D7">
-        <v>168119.141214808</v>
+        <v>168254.0896765548</v>
       </c>
       <c r="E7">
         <v>-69417.825</v>
@@ -1861,37 +1989,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M7">
-        <v>509.4025044713923</v>
+        <v>497.0290594713923</v>
       </c>
       <c r="N7">
-        <v>14783.37300573269</v>
+        <v>14795.74645073269</v>
       </c>
       <c r="O7">
-        <v>3695.843251433173</v>
+        <v>3698.936612683173</v>
       </c>
       <c r="P7">
-        <v>11087.52975429952</v>
+        <v>11096.80983804952</v>
       </c>
       <c r="Q7">
-        <v>14583.52975429952</v>
+        <v>14592.80983804952</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08267221466949973</v>
+        <v>0.08265499498172799</v>
       </c>
       <c r="T7">
         <v>0.7183724503599641</v>
       </c>
       <c r="U7">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.02100573901461</v>
+        <v>30.76837303329605</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +2038,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08058557167587416</v>
+        <v>0.08050625438692993</v>
       </c>
       <c r="C8">
-        <v>157799.0574984395</v>
+        <v>157960.6802884777</v>
       </c>
       <c r="D8">
-        <v>168404.8674984395</v>
+        <v>168566.4902884777</v>
       </c>
       <c r="E8">
         <v>-67650.19</v>
@@ -1943,37 +2071,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M8">
-        <v>611.2830053656706</v>
+        <v>596.4348713656706</v>
       </c>
       <c r="N8">
-        <v>14681.49250483841</v>
+        <v>14696.34063883841</v>
       </c>
       <c r="O8">
-        <v>3670.373126209603</v>
+        <v>3674.085159709603</v>
       </c>
       <c r="P8">
-        <v>11011.11937862881</v>
+        <v>11022.25547912881</v>
       </c>
       <c r="Q8">
-        <v>14507.11937862881</v>
+        <v>14518.25547912881</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08297013183623418</v>
+        <v>0.08295277301820841</v>
       </c>
       <c r="T8">
         <v>0.7241766985449356</v>
       </c>
       <c r="U8">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.01750478251218</v>
+        <v>25.64031086108005</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +2120,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08047116629087854</v>
+        <v>0.08038139041637327</v>
       </c>
       <c r="C9">
-        <v>156318.1216456594</v>
+        <v>156506.6081388285</v>
       </c>
       <c r="D9">
-        <v>168691.5666456594</v>
+        <v>168880.0531388285</v>
       </c>
       <c r="E9">
         <v>-65882.55499999999</v>
@@ -2025,37 +2153,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M9">
-        <v>713.1635062599491</v>
+        <v>695.8406832599492</v>
       </c>
       <c r="N9">
-        <v>14579.61200394413</v>
+        <v>14596.93482694413</v>
       </c>
       <c r="O9">
-        <v>3644.903000986033</v>
+        <v>3649.233706736034</v>
       </c>
       <c r="P9">
-        <v>10934.7090029581</v>
+        <v>10947.7011202081</v>
       </c>
       <c r="Q9">
-        <v>14430.7090029581</v>
+        <v>14443.7011202081</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08327445582375861</v>
+        <v>0.08325695488343036</v>
       </c>
       <c r="T9">
         <v>0.7301057692715193</v>
       </c>
       <c r="U9">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.44357552786758</v>
+        <v>21.97740930949718</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2202,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08035676090588294</v>
+        <v>0.08025652644581661</v>
       </c>
       <c r="C10">
-        <v>154838.1636336662</v>
+        <v>155053.7047255883</v>
       </c>
       <c r="D10">
-        <v>168979.2436336662</v>
+        <v>169194.7847255883</v>
       </c>
       <c r="E10">
         <v>-64114.92</v>
@@ -2107,37 +2235,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M10">
-        <v>815.0440071542275</v>
+        <v>795.2464951542275</v>
       </c>
       <c r="N10">
-        <v>14477.73150304986</v>
+        <v>14497.52901504985</v>
       </c>
       <c r="O10">
-        <v>3619.432875762464</v>
+        <v>3624.382253762464</v>
       </c>
       <c r="P10">
-        <v>10858.29862728739</v>
+        <v>10873.14676128739</v>
       </c>
       <c r="Q10">
-        <v>14354.29862728739</v>
+        <v>14369.14676128739</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08358539555014227</v>
+        <v>0.08356774939789627</v>
       </c>
       <c r="T10">
         <v>0.7361637328399853</v>
       </c>
       <c r="U10">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.76312858688413</v>
+        <v>19.23023314581003</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2284,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08024235552088732</v>
+        <v>0.08013166247525993</v>
       </c>
       <c r="C11">
-        <v>153359.1884736677</v>
+        <v>153601.9765952687</v>
       </c>
       <c r="D11">
-        <v>169267.9034736677</v>
+        <v>169510.6915952687</v>
       </c>
       <c r="E11">
         <v>-62347.285</v>
@@ -2189,37 +2317,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M11">
-        <v>916.9245080485059</v>
+        <v>894.6523070485059</v>
       </c>
       <c r="N11">
-        <v>14375.85100215558</v>
+        <v>14398.12320315558</v>
       </c>
       <c r="O11">
-        <v>3593.962750538894</v>
+        <v>3599.530800788894</v>
       </c>
       <c r="P11">
-        <v>10781.88825161668</v>
+        <v>10798.59240236668</v>
       </c>
       <c r="Q11">
-        <v>14277.88825161668</v>
+        <v>14294.59240236668</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08390316911666623</v>
+        <v>0.08388537456103175</v>
       </c>
       <c r="T11">
         <v>0.742354838464901</v>
       </c>
       <c r="U11">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.67833652167479</v>
+        <v>17.09354057405336</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2366,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.0801279501358917</v>
+        <v>0.08000679850470327</v>
       </c>
       <c r="C12">
-        <v>151881.2012111719</v>
+        <v>152151.4303433649</v>
       </c>
       <c r="D12">
-        <v>169557.5512111719</v>
+        <v>169827.7803433649</v>
       </c>
       <c r="E12">
         <v>-60579.64999999999</v>
@@ -2271,37 +2399,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M12">
-        <v>1018.805008942785</v>
+        <v>994.0581189427845</v>
       </c>
       <c r="N12">
-        <v>14273.9705012613</v>
+        <v>14298.7173912613</v>
       </c>
       <c r="O12">
-        <v>3568.492625315324</v>
+        <v>3574.679347815324</v>
       </c>
       <c r="P12">
-        <v>10705.47787594597</v>
+        <v>10724.03804344597</v>
       </c>
       <c r="Q12">
-        <v>14201.47787594597</v>
+        <v>14220.03804344597</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08422800431800183</v>
+        <v>0.08421005806112579</v>
       </c>
       <c r="T12">
         <v>0.7486835242148149</v>
       </c>
       <c r="U12">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.0105028695073</v>
+        <v>15.38418651664802</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2448,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.0800135447508961</v>
+        <v>0.0798819345341466</v>
       </c>
       <c r="C13">
-        <v>150404.2069262811</v>
+        <v>150702.0726148151</v>
       </c>
       <c r="D13">
-        <v>169848.1919262811</v>
+        <v>170146.0576148151</v>
       </c>
       <c r="E13">
         <v>-58812.015</v>
@@ -2353,37 +2481,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M13">
-        <v>1120.685509837063</v>
+        <v>1093.463930837063</v>
       </c>
       <c r="N13">
-        <v>14172.09000036702</v>
+        <v>14199.31157936702</v>
       </c>
       <c r="O13">
-        <v>3543.022500091755</v>
+        <v>3549.827894841755</v>
       </c>
       <c r="P13">
-        <v>10629.06750027527</v>
+        <v>10649.48368452526</v>
       </c>
       <c r="Q13">
-        <v>14125.06750027527</v>
+        <v>14145.48368452526</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08456013918678318</v>
+        <v>0.08454203781964892</v>
       </c>
       <c r="T13">
         <v>0.7551544276220303</v>
       </c>
       <c r="U13">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>13.6459116995521</v>
+        <v>13.98562410604366</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2530,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07989913936590048</v>
+        <v>0.07975707056358994</v>
       </c>
       <c r="C14">
-        <v>148928.2107339889</v>
+        <v>149253.9101044647</v>
       </c>
       <c r="D14">
-        <v>170139.8307339889</v>
+        <v>170465.5301044647</v>
       </c>
       <c r="E14">
         <v>-57044.38</v>
@@ -2435,37 +2563,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M14">
-        <v>1222.566010731341</v>
+        <v>1192.869742731341</v>
       </c>
       <c r="N14">
-        <v>14070.20949947274</v>
+        <v>14099.90576747274</v>
       </c>
       <c r="O14">
-        <v>3517.552374868185</v>
+        <v>3524.976441868185</v>
       </c>
       <c r="P14">
-        <v>10552.65712460456</v>
+        <v>10574.92932560456</v>
       </c>
       <c r="Q14">
-        <v>14048.65712460456</v>
+        <v>14070.92932560456</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08489982257530956</v>
+        <v>0.08488156257268394</v>
       </c>
       <c r="T14">
         <v>0.7617723970157733</v>
       </c>
       <c r="U14">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.50875239125609</v>
+        <v>12.82015543054002</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2612,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07978473398090487</v>
+        <v>0.07963220659303326</v>
       </c>
       <c r="C15">
-        <v>147453.2177844803</v>
+        <v>147806.9495575356</v>
       </c>
       <c r="D15">
-        <v>170432.4727844803</v>
+        <v>170786.2045575356</v>
       </c>
       <c r="E15">
         <v>-55276.745</v>
@@ -2517,37 +2645,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M15">
-        <v>1324.44651162562</v>
+        <v>1292.27555462562</v>
       </c>
       <c r="N15">
-        <v>13968.32899857846</v>
+        <v>14000.49995557846</v>
       </c>
       <c r="O15">
-        <v>3492.082249644616</v>
+        <v>3500.124988894616</v>
       </c>
       <c r="P15">
-        <v>10476.24674893385</v>
+        <v>10500.37496668385</v>
       </c>
       <c r="Q15">
-        <v>13972.24674893385</v>
+        <v>13996.37496668385</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08524731477736527</v>
+        <v>0.08522889249245538</v>
       </c>
       <c r="T15">
         <v>0.7685425036369585</v>
       </c>
       <c r="U15">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.54654066885177</v>
+        <v>11.83398962819079</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2694,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07967032859590925</v>
+        <v>0.07950734262247659</v>
       </c>
       <c r="C16">
-        <v>145979.2332634348</v>
+        <v>146361.197770101</v>
       </c>
       <c r="D16">
-        <v>170726.1232634348</v>
+        <v>171108.087770101</v>
       </c>
       <c r="E16">
         <v>-53509.11</v>
@@ -2599,37 +2727,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M16">
-        <v>1426.327012519898</v>
+        <v>1391.681366519898</v>
       </c>
       <c r="N16">
-        <v>13866.44849768418</v>
+        <v>13901.09414368418</v>
       </c>
       <c r="O16">
-        <v>3466.612124421046</v>
+        <v>3475.273535921046</v>
       </c>
       <c r="P16">
-        <v>10399.83637326314</v>
+        <v>10425.82060776314</v>
       </c>
       <c r="Q16">
-        <v>13895.83637326314</v>
+        <v>13921.82060776314</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08560288819342229</v>
+        <v>0.08558429985222152</v>
       </c>
       <c r="T16">
         <v>0.7754700545981714</v>
       </c>
       <c r="U16">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.72178776393379</v>
+        <v>10.98870465474859</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2776,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07955592321091362</v>
+        <v>0.07938247865191993</v>
       </c>
       <c r="C17">
-        <v>144506.2623923325</v>
+        <v>144916.6615895655</v>
       </c>
       <c r="D17">
-        <v>171020.7873923325</v>
+        <v>171431.1865895654</v>
       </c>
       <c r="E17">
         <v>-51741.47500000001</v>
@@ -2681,37 +2809,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M17">
-        <v>1528.207513414176</v>
+        <v>1491.087178414176</v>
       </c>
       <c r="N17">
-        <v>13764.56799678991</v>
+        <v>13801.68833178991</v>
       </c>
       <c r="O17">
-        <v>3441.141999197477</v>
+        <v>3450.422082947477</v>
       </c>
       <c r="P17">
-        <v>10323.42599759243</v>
+        <v>10351.26624884243</v>
       </c>
       <c r="Q17">
-        <v>13819.42599759243</v>
+        <v>13847.26624884243</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08596682804279829</v>
+        <v>0.08594806973809982</v>
       </c>
       <c r="T17">
         <v>0.7825606067584717</v>
       </c>
       <c r="U17">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.00700191300487</v>
+        <v>10.25612434443202</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2858,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07944151782591802</v>
+        <v>0.07925761468136325</v>
       </c>
       <c r="C18">
-        <v>143034.310428764</v>
+        <v>143473.3479151504</v>
       </c>
       <c r="D18">
-        <v>171316.470428764</v>
+        <v>171755.5079151504</v>
       </c>
       <c r="E18">
         <v>-49973.84</v>
@@ -2763,37 +2891,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M18">
-        <v>1630.088014308455</v>
+        <v>1590.492990308455</v>
       </c>
       <c r="N18">
-        <v>13662.68749589563</v>
+        <v>13702.28251989563</v>
       </c>
       <c r="O18">
-        <v>3415.671873973907</v>
+        <v>3425.570629973907</v>
       </c>
       <c r="P18">
-        <v>10247.01562192172</v>
+        <v>10276.71188992172</v>
       </c>
       <c r="Q18">
-        <v>13743.01562192172</v>
+        <v>13772.71188992172</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08633943312668324</v>
+        <v>0.08632050081173709</v>
       </c>
       <c r="T18">
         <v>0.7898199815892553</v>
       </c>
       <c r="U18">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.381564293442068</v>
+        <v>9.615116572905015</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2940,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07932711244092241</v>
+        <v>0.07913275071080658</v>
       </c>
       <c r="C19">
-        <v>141563.382666743</v>
+        <v>142031.2636983852</v>
       </c>
       <c r="D19">
-        <v>171613.177666743</v>
+        <v>172081.0586983852</v>
       </c>
       <c r="E19">
         <v>-48206.205</v>
@@ -2845,37 +2973,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M19">
-        <v>1731.968515202733</v>
+        <v>1689.898802202734</v>
       </c>
       <c r="N19">
-        <v>13560.80699500135</v>
+        <v>13602.87670800135</v>
       </c>
       <c r="O19">
-        <v>3390.201748750337</v>
+        <v>3400.719177000337</v>
       </c>
       <c r="P19">
-        <v>10170.60524625101</v>
+        <v>10202.15753100101</v>
       </c>
       <c r="Q19">
-        <v>13666.60524625101</v>
+        <v>13698.15753100101</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08672101664632448</v>
+        <v>0.08670190612811264</v>
       </c>
       <c r="T19">
         <v>0.7972542811147567</v>
       </c>
       <c r="U19">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.829707570298416</v>
+        <v>9.049521480381191</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +3022,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07936120705592679</v>
+        <v>0.07921038674024992</v>
       </c>
       <c r="C20">
-        <v>139707.2167665847</v>
+        <v>140061.0677154825</v>
       </c>
       <c r="D20">
-        <v>171524.6467665847</v>
+        <v>171878.4977154825</v>
       </c>
       <c r="E20">
         <v>-46438.57</v>
@@ -2927,37 +3055,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M20">
-        <v>1868.848189097012</v>
+        <v>1837.030759097012</v>
       </c>
       <c r="N20">
-        <v>13423.92732110707</v>
+        <v>13455.74475110707</v>
       </c>
       <c r="O20">
-        <v>3355.981830276768</v>
+        <v>3363.936187776768</v>
       </c>
       <c r="P20">
-        <v>10067.9454908303</v>
+        <v>10091.8085633303</v>
       </c>
       <c r="Q20">
-        <v>13563.9454908303</v>
+        <v>13587.8085633303</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.0871119070810789</v>
+        <v>0.08709261401318026</v>
       </c>
       <c r="T20">
         <v>0.8048699050189286</v>
       </c>
       <c r="U20">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.04405246249690056</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.182995065850282</v>
+        <v>8.32472479541998</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +3104,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07925505167093119</v>
+        <v>0.07909677276969325</v>
       </c>
       <c r="C21">
-        <v>138215.5284290102</v>
+        <v>138590.0261065706</v>
       </c>
       <c r="D21">
-        <v>171800.5934290102</v>
+        <v>172175.0911065706</v>
       </c>
       <c r="E21">
         <v>-44670.935</v>
@@ -3009,37 +3137,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M21">
-        <v>1972.673088491291</v>
+        <v>1939.088023491291</v>
       </c>
       <c r="N21">
-        <v>13320.10242171279</v>
+        <v>13353.68748671279</v>
       </c>
       <c r="O21">
-        <v>3330.025605428198</v>
+        <v>3338.421871678198</v>
       </c>
       <c r="P21">
-        <v>9990.076816284594</v>
+        <v>10015.26561503459</v>
       </c>
       <c r="Q21">
-        <v>13486.07681628459</v>
+        <v>13511.26561503459</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08751244913150627</v>
+        <v>0.08749296900652116</v>
       </c>
       <c r="T21">
         <v>0.8126735690195001</v>
       </c>
       <c r="U21">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.04405246249690056</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.752311115016055</v>
+        <v>7.886581385134717</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3186,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07914889628593556</v>
+        <v>0.07898315879913657</v>
       </c>
       <c r="C22">
-        <v>136724.7294010826</v>
+        <v>137120.0098696521</v>
       </c>
       <c r="D22">
-        <v>172077.4294010827</v>
+        <v>172472.7098696521</v>
       </c>
       <c r="E22">
         <v>-42903.3</v>
@@ -3091,37 +3219,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M22">
-        <v>2076.497987885569</v>
+        <v>2041.145287885569</v>
       </c>
       <c r="N22">
-        <v>13216.27752231851</v>
+        <v>13251.63022231851</v>
       </c>
       <c r="O22">
-        <v>3304.069380579628</v>
+        <v>3312.907555579628</v>
       </c>
       <c r="P22">
-        <v>9912.208141738884</v>
+        <v>9938.722666738886</v>
       </c>
       <c r="Q22">
-        <v>13408.20814173888</v>
+        <v>13434.72266673889</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08792300473319431</v>
+        <v>0.08790333287469558</v>
       </c>
       <c r="T22">
         <v>0.8206723246200857</v>
       </c>
       <c r="U22">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04405246249690056</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.364695559265251</v>
+        <v>7.49225231587798</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3268,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07904274090093995</v>
+        <v>0.07886954482857991</v>
       </c>
       <c r="C23">
-        <v>135234.8239887867</v>
+        <v>135651.0243312531</v>
       </c>
       <c r="D23">
-        <v>172355.1589887867</v>
+        <v>172771.3593312531</v>
       </c>
       <c r="E23">
         <v>-41135.665</v>
@@ -3173,37 +3301,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M23">
-        <v>2180.322887279847</v>
+        <v>2143.202552279847</v>
       </c>
       <c r="N23">
-        <v>13112.45262292424</v>
+        <v>13149.57295792424</v>
       </c>
       <c r="O23">
-        <v>3278.113155731059</v>
+        <v>3287.393239481059</v>
       </c>
       <c r="P23">
-        <v>9834.339467193178</v>
+        <v>9862.179718443178</v>
       </c>
       <c r="Q23">
-        <v>13330.33946719318</v>
+        <v>13358.17971844318</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08834395414758334</v>
+        <v>0.08832408570155796</v>
       </c>
       <c r="T23">
         <v>0.8288735803624582</v>
       </c>
       <c r="U23">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.04405246249690056</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.013995770728814</v>
+        <v>7.135478396074268</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3350,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07929958551594433</v>
+        <v>0.07875593085802322</v>
       </c>
       <c r="C24">
-        <v>132796.7514501687</v>
+        <v>134183.0748548567</v>
       </c>
       <c r="D24">
-        <v>171684.7214501687</v>
+        <v>173071.0448548567</v>
       </c>
       <c r="E24">
         <v>-39368.03</v>
@@ -3255,45 +3383,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M24">
-        <v>2369.701320674126</v>
+        <v>2245.259816674126</v>
       </c>
       <c r="N24">
-        <v>12923.07418952996</v>
+        <v>13047.51569352996</v>
       </c>
       <c r="O24">
-        <v>3230.768547382489</v>
+        <v>3261.878923382489</v>
       </c>
       <c r="P24">
-        <v>9692.305642147468</v>
+        <v>9785.636770147466</v>
       </c>
       <c r="Q24">
-        <v>13188.30564214747</v>
+        <v>13281.63677014747</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08877569713670028</v>
+        <v>0.08875562706244244</v>
       </c>
       <c r="T24">
         <v>0.8372851247136095</v>
       </c>
       <c r="U24">
-        <v>0.06093661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04570246249690057</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.453461192254237</v>
+        <v>6.811138468979983</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3432,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07920993013094874</v>
+        <v>0.07893556688746656</v>
       </c>
       <c r="C25">
-        <v>131262.5491485145</v>
+        <v>131942.0807965528</v>
       </c>
       <c r="D25">
-        <v>171918.1541485145</v>
+        <v>172597.6857965528</v>
       </c>
       <c r="E25">
         <v>-37600.395</v>
@@ -3337,37 +3465,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M25">
-        <v>2477.415017068404</v>
+        <v>2416.431609568404</v>
       </c>
       <c r="N25">
-        <v>12815.36049313568</v>
+        <v>12876.34390063568</v>
       </c>
       <c r="O25">
-        <v>3203.84012328392</v>
+        <v>3219.08597515892</v>
       </c>
       <c r="P25">
-        <v>9611.520369851758</v>
+        <v>9657.257925476759</v>
       </c>
       <c r="Q25">
-        <v>13107.52036985176</v>
+        <v>13153.25792547676</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08921865422943065</v>
+        <v>0.08919837728984342</v>
       </c>
       <c r="T25">
         <v>0.8459151507362195</v>
       </c>
       <c r="U25">
-        <v>0.06093661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04570246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.172875923025791</v>
+        <v>6.328660595917095</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3514,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07912027474595312</v>
+        <v>0.0788347029169099</v>
       </c>
       <c r="C26">
-        <v>129728.9824889142</v>
+        <v>130439.9132726421</v>
       </c>
       <c r="D26">
-        <v>172152.2224889142</v>
+        <v>172863.1532726421</v>
       </c>
       <c r="E26">
         <v>-35832.76</v>
@@ -3419,37 +3547,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M26">
-        <v>2585.128713462683</v>
+        <v>2521.493853462683</v>
       </c>
       <c r="N26">
-        <v>12707.6467967414</v>
+        <v>12771.2816567414</v>
       </c>
       <c r="O26">
-        <v>3176.91169918535</v>
+        <v>3192.82041418535</v>
       </c>
       <c r="P26">
-        <v>9530.735097556049</v>
+        <v>9578.461242556052</v>
       </c>
       <c r="Q26">
-        <v>13026.73509755605</v>
+        <v>13074.46124255605</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08967326808775919</v>
+        <v>0.08965277883901812</v>
       </c>
       <c r="T26">
         <v>0.8547722827067928</v>
       </c>
       <c r="U26">
-        <v>0.06093661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.04570246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.915672759566383</v>
+        <v>6.06496640442055</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3596,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07903061936095751</v>
+        <v>0.07873383894635323</v>
       </c>
       <c r="C27">
-        <v>128196.0540712071</v>
+        <v>128938.5636222729</v>
       </c>
       <c r="D27">
-        <v>172386.9290712071</v>
+        <v>173129.4386222729</v>
       </c>
       <c r="E27">
         <v>-34065.125</v>
@@ -3501,37 +3629,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M27">
-        <v>2692.842409856961</v>
+        <v>2626.556097356961</v>
       </c>
       <c r="N27">
-        <v>12599.93310034712</v>
+        <v>12666.21941284712</v>
       </c>
       <c r="O27">
-        <v>3149.98327508678</v>
+        <v>3166.55485321178</v>
       </c>
       <c r="P27">
-        <v>9449.949825260341</v>
+        <v>9499.664559635341</v>
       </c>
       <c r="Q27">
-        <v>12945.94982526034</v>
+        <v>12995.66455963534</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09014000498230981</v>
+        <v>0.09011929776283745</v>
       </c>
       <c r="T27">
         <v>0.863865604863248</v>
       </c>
       <c r="U27">
-        <v>0.06093661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04570246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.679045849183728</v>
+        <v>5.822367748243728</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3678,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07923346397596188</v>
+        <v>0.07863297497579656</v>
       </c>
       <c r="C28">
-        <v>125898.3084495472</v>
+        <v>127438.0356309325</v>
       </c>
       <c r="D28">
-        <v>171856.8184495472</v>
+        <v>173396.5456309325</v>
       </c>
       <c r="E28">
         <v>-32297.49</v>
@@ -3583,45 +3711,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M28">
-        <v>2869.49387125124</v>
+        <v>2731.61834125124</v>
       </c>
       <c r="N28">
-        <v>12423.28163895284</v>
+        <v>12561.15716895284</v>
       </c>
       <c r="O28">
-        <v>3105.820409738211</v>
+        <v>3140.289292238211</v>
       </c>
       <c r="P28">
-        <v>9317.461229214632</v>
+        <v>9420.867876714632</v>
       </c>
       <c r="Q28">
-        <v>12813.46122921463</v>
+        <v>12916.86787671463</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09061935638752397</v>
+        <v>0.09059842530621948</v>
       </c>
       <c r="T28">
         <v>0.8732046924833913</v>
       </c>
       <c r="U28">
-        <v>0.06243661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04682746249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>5.329433062540637</v>
+        <v>5.59843052715743</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3760,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07915505859096626</v>
+        <v>0.07869411100523989</v>
       </c>
       <c r="C29">
-        <v>124335.1897223658</v>
+        <v>125508.4024872746</v>
       </c>
       <c r="D29">
-        <v>172061.3347223658</v>
+        <v>173234.5474872746</v>
       </c>
       <c r="E29">
         <v>-30529.855</v>
@@ -3665,37 +3793,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M29">
-        <v>2979.859020145518</v>
+        <v>2874.861501145518</v>
       </c>
       <c r="N29">
-        <v>12312.91649005856</v>
+        <v>12417.91400905856</v>
       </c>
       <c r="O29">
-        <v>3078.229122514641</v>
+        <v>3104.478502264641</v>
       </c>
       <c r="P29">
-        <v>9234.687367543924</v>
+        <v>9313.435506793923</v>
       </c>
       <c r="Q29">
-        <v>12730.68736754392</v>
+        <v>12809.43550679392</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09111184070794948</v>
+        <v>0.09109067963161198</v>
       </c>
       <c r="T29">
         <v>0.882799645517785</v>
       </c>
       <c r="U29">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.13204665281691</v>
+        <v>5.319482522587791</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3842,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07907665320597065</v>
+        <v>0.07859924703468323</v>
       </c>
       <c r="C30">
-        <v>122772.5583397211</v>
+        <v>123992.2676198721</v>
       </c>
       <c r="D30">
-        <v>172266.3383397211</v>
+        <v>173486.0476198721</v>
       </c>
       <c r="E30">
         <v>-28762.21999999999</v>
@@ -3747,37 +3875,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M30">
-        <v>3090.224169039797</v>
+        <v>2981.337853039797</v>
       </c>
       <c r="N30">
-        <v>12202.55134116429</v>
+        <v>12311.43765716429</v>
       </c>
       <c r="O30">
-        <v>3050.637835291071</v>
+        <v>3077.859414291072</v>
       </c>
       <c r="P30">
-        <v>9151.913505873214</v>
+        <v>9233.578242873215</v>
       </c>
       <c r="Q30">
-        <v>12647.91350587321</v>
+        <v>12729.57824287321</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09161800514838681</v>
+        <v>0.09159660768826537</v>
       </c>
       <c r="T30">
         <v>0.8926611250253563</v>
       </c>
       <c r="U30">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.948759272359163</v>
+        <v>5.129501003923941</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3924,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07899824782097503</v>
+        <v>0.07850438306412655</v>
       </c>
       <c r="C31">
-        <v>121210.4160456409</v>
+        <v>122476.8640647879</v>
       </c>
       <c r="D31">
-        <v>172471.8310456409</v>
+        <v>173738.2790647879</v>
       </c>
       <c r="E31">
         <v>-26994.58500000001</v>
@@ -3829,37 +3957,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M31">
-        <v>3200.589317934075</v>
+        <v>3087.814204934074</v>
       </c>
       <c r="N31">
-        <v>12092.18619227001</v>
+        <v>12204.96130527001</v>
       </c>
       <c r="O31">
-        <v>3023.046548067502</v>
+        <v>3051.240326317502</v>
       </c>
       <c r="P31">
-        <v>9069.139644202507</v>
+        <v>9153.720978952506</v>
       </c>
       <c r="Q31">
-        <v>12565.13964420251</v>
+        <v>12649.72097895251</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09213842774207588</v>
+        <v>0.09211678723947238</v>
       </c>
       <c r="T31">
         <v>0.9028003926880704</v>
       </c>
       <c r="U31">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.778112400898503</v>
+        <v>4.952621658961046</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +4006,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07891984243597944</v>
+        <v>0.07840951909356988</v>
       </c>
       <c r="C32">
-        <v>119648.7645924841</v>
+        <v>120962.1950164324</v>
       </c>
       <c r="D32">
-        <v>172677.8145924841</v>
+        <v>173991.2450164324</v>
       </c>
       <c r="E32">
         <v>-25226.95</v>
@@ -3911,37 +4039,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M32">
-        <v>3310.954466828353</v>
+        <v>3194.290556828353</v>
       </c>
       <c r="N32">
-        <v>11981.82104337573</v>
+        <v>12098.48495337573</v>
       </c>
       <c r="O32">
-        <v>2995.455260843933</v>
+        <v>3024.621238343932</v>
       </c>
       <c r="P32">
-        <v>8986.365782531797</v>
+        <v>9073.863715031797</v>
       </c>
       <c r="Q32">
-        <v>12482.3657825318</v>
+        <v>12569.8637150318</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09267371955272752</v>
+        <v>0.09265182906357103</v>
       </c>
       <c r="T32">
         <v>0.9132293537125764</v>
       </c>
       <c r="U32">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.61884198753522</v>
+        <v>4.787534270329012</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +4088,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07884143705098381</v>
+        <v>0.07831465512301321</v>
       </c>
       <c r="C33">
-        <v>118087.6057409914</v>
+        <v>119448.2636878474</v>
       </c>
       <c r="D33">
-        <v>172884.2907409914</v>
+        <v>174244.9486878474</v>
       </c>
       <c r="E33">
         <v>-23459.315</v>
@@ -3993,37 +4121,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M33">
-        <v>3421.319615722632</v>
+        <v>3300.766908722632</v>
       </c>
       <c r="N33">
-        <v>11871.45589448145</v>
+        <v>11992.00860148145</v>
       </c>
       <c r="O33">
-        <v>2967.863973620363</v>
+        <v>2998.002150370363</v>
       </c>
       <c r="P33">
-        <v>8903.591920861089</v>
+        <v>8994.006451111089</v>
       </c>
       <c r="Q33">
-        <v>12399.59192086109</v>
+        <v>12490.00645111109</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09322452706803572</v>
+        <v>0.09320237934633918</v>
       </c>
       <c r="T33">
         <v>0.9239606034624305</v>
       </c>
       <c r="U33">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.469847084711502</v>
+        <v>4.63309768096356</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4170,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07876303166598819</v>
+        <v>0.07821979115245654</v>
       </c>
       <c r="C34">
-        <v>116526.9412603349</v>
+        <v>117935.0733108424</v>
       </c>
       <c r="D34">
-        <v>173091.2612603349</v>
+        <v>174499.3933108425</v>
       </c>
       <c r="E34">
         <v>-21691.68</v>
@@ -4075,37 +4203,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M34">
-        <v>3531.68476461691</v>
+        <v>3407.24326061691</v>
       </c>
       <c r="N34">
-        <v>11761.09074558717</v>
+        <v>11885.53224958717</v>
       </c>
       <c r="O34">
-        <v>2940.272686396793</v>
+        <v>2971.383062396793</v>
       </c>
       <c r="P34">
-        <v>8820.81805919038</v>
+        <v>8914.14918719038</v>
       </c>
       <c r="Q34">
-        <v>12316.81805919038</v>
+        <v>12410.14918719038</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09379153480438238</v>
+        <v>0.09376912228448289</v>
       </c>
       <c r="T34">
         <v>0.9350074782049274</v>
       </c>
       <c r="U34">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.330164363314267</v>
+        <v>4.488313378433448</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4252,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07903112628099258</v>
+        <v>0.07812492718189987</v>
       </c>
       <c r="C35">
-        <v>114053.6452189531</v>
+        <v>116422.627136132</v>
       </c>
       <c r="D35">
-        <v>172385.6002189531</v>
+        <v>174754.582136132</v>
       </c>
       <c r="E35">
         <v>-19924.045</v>
@@ -4157,45 +4285,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M35">
-        <v>3723.714650511189</v>
+        <v>3513.719612511189</v>
       </c>
       <c r="N35">
-        <v>11569.06085969289</v>
+        <v>11779.0558976929</v>
       </c>
       <c r="O35">
-        <v>2892.265214923224</v>
+        <v>2944.763974423224</v>
       </c>
       <c r="P35">
-        <v>8676.795644769671</v>
+        <v>8834.291923269671</v>
       </c>
       <c r="Q35">
-        <v>12172.79564476967</v>
+        <v>12330.29192326967</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09437546814479911</v>
+        <v>0.09435278292227267</v>
       </c>
       <c r="T35">
         <v>0.946384110402424</v>
       </c>
       <c r="U35">
-        <v>0.0638366166625341</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04787746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.106860204259932</v>
+        <v>4.352303882117283</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4334,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07896322089599697</v>
+        <v>0.07828506321134319</v>
       </c>
       <c r="C36">
-        <v>112464.2016429806</v>
+        <v>114224.650594683</v>
       </c>
       <c r="D36">
-        <v>172563.7916429806</v>
+        <v>174324.240594683</v>
       </c>
       <c r="E36">
         <v>-18156.41</v>
@@ -4239,37 +4367,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M36">
-        <v>3836.554488405468</v>
+        <v>3680.295554405468</v>
       </c>
       <c r="N36">
-        <v>11456.22102179861</v>
+        <v>11612.47995579862</v>
       </c>
       <c r="O36">
-        <v>2864.055255449653</v>
+        <v>2903.119988949654</v>
       </c>
       <c r="P36">
-        <v>8592.16576634896</v>
+        <v>8709.359966848962</v>
       </c>
       <c r="Q36">
-        <v>12088.16576634896</v>
+        <v>12205.35996684896</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09497709643492544</v>
+        <v>0.09495413024605609</v>
       </c>
       <c r="T36">
         <v>0.9581054890301479</v>
       </c>
       <c r="U36">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.986070198252286</v>
+        <v>4.15531179062453</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4416,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07889531551100135</v>
+        <v>0.07819769924078654</v>
       </c>
       <c r="C37">
-        <v>110875.1268337624</v>
+        <v>112691.530063716</v>
       </c>
       <c r="D37">
-        <v>172742.3518337624</v>
+        <v>174558.755063716</v>
       </c>
       <c r="E37">
         <v>-16388.77499999999</v>
@@ -4321,37 +4449,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M37">
-        <v>3949.394326299746</v>
+        <v>3788.539541299746</v>
       </c>
       <c r="N37">
-        <v>11343.38118390434</v>
+        <v>11504.23596890434</v>
       </c>
       <c r="O37">
-        <v>2835.845295976084</v>
+        <v>2876.058992226084</v>
       </c>
       <c r="P37">
-        <v>8507.535887928254</v>
+        <v>8628.176976678253</v>
       </c>
       <c r="Q37">
-        <v>12003.53588792825</v>
+        <v>12124.17697667825</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09559723636474794</v>
+        <v>0.09557398056441746</v>
       </c>
       <c r="T37">
         <v>0.9701875254618016</v>
       </c>
       <c r="U37">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.872182478302221</v>
+        <v>4.036588596606687</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4498,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07882741012600575</v>
+        <v>0.07811033527022987</v>
       </c>
       <c r="C38">
-        <v>109286.421937227</v>
+        <v>111159.0413567792</v>
       </c>
       <c r="D38">
-        <v>172921.281937227</v>
+        <v>174793.9013567792</v>
       </c>
       <c r="E38">
         <v>-14621.14</v>
@@ -4403,37 +4531,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M38">
-        <v>4062.234164194024</v>
+        <v>3896.783528194024</v>
       </c>
       <c r="N38">
-        <v>11230.54134601006</v>
+        <v>11395.99198201006</v>
       </c>
       <c r="O38">
-        <v>2807.635336502515</v>
+        <v>2848.997995502515</v>
       </c>
       <c r="P38">
-        <v>8422.906009507544</v>
+        <v>8546.993986507543</v>
       </c>
       <c r="Q38">
-        <v>11918.90600950754</v>
+        <v>12042.99398650754</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09623675566737741</v>
+        <v>0.09621320120522761</v>
       </c>
       <c r="T38">
         <v>0.9826471255319447</v>
       </c>
       <c r="U38">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.764621853904938</v>
+        <v>3.924461135589834</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4580,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07875950474101012</v>
+        <v>0.0780229712996732</v>
       </c>
       <c r="C39">
-        <v>107698.0881040562</v>
+        <v>109627.1870306877</v>
       </c>
       <c r="D39">
-        <v>173100.5831040562</v>
+        <v>175029.6820306877</v>
       </c>
       <c r="E39">
         <v>-12853.505</v>
@@ -4485,37 +4613,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M39">
-        <v>4175.074002088303</v>
+        <v>4005.027515088303</v>
       </c>
       <c r="N39">
-        <v>11117.70150811578</v>
+        <v>11287.74799511578</v>
       </c>
       <c r="O39">
-        <v>2779.425377028945</v>
+        <v>2821.936998778945</v>
       </c>
       <c r="P39">
-        <v>8338.276131086835</v>
+        <v>8465.810996336835</v>
       </c>
       <c r="Q39">
-        <v>11834.27613108684</v>
+        <v>11961.81099633684</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09689657717009034</v>
+        <v>0.09687271456479363</v>
       </c>
       <c r="T39">
         <v>0.9955022684614572</v>
       </c>
       <c r="U39">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.662875317312912</v>
+        <v>3.818394618411731</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4662,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07869159935601451</v>
+        <v>0.07793560732911653</v>
       </c>
       <c r="C40">
-        <v>106110.1264897088</v>
+        <v>108095.9696560708</v>
       </c>
       <c r="D40">
-        <v>173280.2564897088</v>
+        <v>175266.0996560708</v>
       </c>
       <c r="E40">
         <v>-11085.87</v>
@@ -4567,37 +4695,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M40">
-        <v>4287.913839982582</v>
+        <v>4113.271501982581</v>
       </c>
       <c r="N40">
-        <v>11004.8616702215</v>
+        <v>11179.5040082215</v>
       </c>
       <c r="O40">
-        <v>2751.215417555375</v>
+        <v>2794.876002055375</v>
       </c>
       <c r="P40">
-        <v>8253.646252666125</v>
+        <v>8384.628006166127</v>
       </c>
       <c r="Q40">
-        <v>11749.64625266613</v>
+        <v>11880.62800616613</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09757768323740693</v>
+        <v>0.0975535025488618</v>
       </c>
       <c r="T40">
         <v>1.008772093420954</v>
       </c>
       <c r="U40">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.566483861594151</v>
+        <v>3.71791054950616</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4744,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.0786236939710189</v>
+        <v>0.07784824335855986</v>
       </c>
       <c r="C41">
-        <v>104522.5382544463</v>
+        <v>106565.3918174656</v>
       </c>
       <c r="D41">
-        <v>173460.3032544463</v>
+        <v>175503.1568174656</v>
       </c>
       <c r="E41">
         <v>-9318.235000000001</v>
@@ -4649,37 +4777,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M41">
-        <v>4400.75367787686</v>
+        <v>4221.515488876859</v>
       </c>
       <c r="N41">
-        <v>10892.02183232722</v>
+        <v>11071.26002132722</v>
       </c>
       <c r="O41">
-        <v>2723.005458081806</v>
+        <v>2767.815005331806</v>
       </c>
       <c r="P41">
-        <v>8169.016374245418</v>
+        <v>8303.445015995418</v>
       </c>
       <c r="Q41">
-        <v>11665.01637424542</v>
+        <v>11799.44501599542</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09828112065119292</v>
+        <v>0.0982566114504404</v>
       </c>
       <c r="T41">
         <v>1.022476994608631</v>
       </c>
       <c r="U41">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.475035557450712</v>
+        <v>3.622579509775232</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4826,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07855578858602329</v>
+        <v>0.07776087938800319</v>
       </c>
       <c r="C42">
-        <v>102935.3245633573</v>
+        <v>105035.4561134109</v>
       </c>
       <c r="D42">
-        <v>173640.7245633573</v>
+        <v>175740.8561134109</v>
       </c>
       <c r="E42">
         <v>-7550.599999999991</v>
@@ -4731,37 +4859,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M42">
-        <v>4513.593515771139</v>
+        <v>4329.759475771139</v>
       </c>
       <c r="N42">
-        <v>10779.18199443294</v>
+        <v>10963.01603443295</v>
       </c>
       <c r="O42">
-        <v>2694.795498608236</v>
+        <v>2740.754008608236</v>
       </c>
       <c r="P42">
-        <v>8084.386495824708</v>
+        <v>8222.262025824708</v>
       </c>
       <c r="Q42">
-        <v>11580.38649582471</v>
+        <v>11718.26202582471</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.09900800597877177</v>
+        <v>0.09898315731540494</v>
       </c>
       <c r="T42">
         <v>1.036638725835898</v>
       </c>
       <c r="U42">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.388159668514443</v>
+        <v>3.532015022030851</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4908,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07848788320102768</v>
+        <v>0.07767351541744652</v>
       </c>
       <c r="C43">
-        <v>101348.4865863829</v>
+        <v>103506.1651565425</v>
       </c>
       <c r="D43">
-        <v>173821.5215863829</v>
+        <v>175979.2001565425</v>
       </c>
       <c r="E43">
         <v>-5782.964999999997</v>
@@ -4813,37 +4941,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M43">
-        <v>4626.433353665417</v>
+        <v>4438.003462665417</v>
       </c>
       <c r="N43">
-        <v>10666.34215653867</v>
+        <v>10854.77204753867</v>
       </c>
       <c r="O43">
-        <v>2666.585539134667</v>
+        <v>2713.693011884667</v>
       </c>
       <c r="P43">
-        <v>7999.756617404</v>
+        <v>8141.079035654</v>
       </c>
       <c r="Q43">
-        <v>11495.756617404</v>
+        <v>11637.079035654</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09975953148694652</v>
+        <v>0.09973433185375813</v>
       </c>
       <c r="T43">
         <v>1.051280515748834</v>
       </c>
       <c r="U43">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.30552162781897</v>
+        <v>3.44586831417644</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4990,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07841997781603208</v>
+        <v>0.07758615144688986</v>
       </c>
       <c r="C44">
-        <v>99762.02549834181</v>
+        <v>101977.5215736885</v>
       </c>
       <c r="D44">
-        <v>174002.6954983418</v>
+        <v>176218.1915736885</v>
       </c>
       <c r="E44">
         <v>-4015.330000000002</v>
@@ -4895,37 +5023,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M44">
-        <v>4739.273191559695</v>
+        <v>4546.247449559694</v>
       </c>
       <c r="N44">
-        <v>10553.50231864439</v>
+        <v>10746.52806064439</v>
       </c>
       <c r="O44">
-        <v>2638.375579661097</v>
+        <v>2686.632015161097</v>
       </c>
       <c r="P44">
-        <v>7915.12673898329</v>
+        <v>8059.896045483291</v>
       </c>
       <c r="Q44">
-        <v>11411.12673898329</v>
+        <v>11555.89604548329</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1005369716678169</v>
+        <v>0.1005114089623994</v>
       </c>
       <c r="T44">
         <v>1.066427194969113</v>
       </c>
       <c r="U44">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.226818731918518</v>
+        <v>3.363823830505573</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +5072,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07835207243103645</v>
+        <v>0.07749878747633318</v>
       </c>
       <c r="C45">
-        <v>98175.94247895607</v>
+        <v>100449.5280059664</v>
       </c>
       <c r="D45">
-        <v>174184.2474789561</v>
+        <v>176457.8330059664</v>
       </c>
       <c r="E45">
         <v>-2247.695000000007</v>
@@ -4977,37 +5105,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M45">
-        <v>4852.113029453973</v>
+        <v>4654.491436453973</v>
       </c>
       <c r="N45">
-        <v>10440.66248075011</v>
+        <v>10638.28407375011</v>
       </c>
       <c r="O45">
-        <v>2610.165620187528</v>
+        <v>2659.571018437528</v>
       </c>
       <c r="P45">
-        <v>7830.496860562583</v>
+        <v>7978.713055312583</v>
       </c>
       <c r="Q45">
-        <v>11326.49686056258</v>
+        <v>11474.71305531258</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1013416904515249</v>
+        <v>0.1013157519345017</v>
       </c>
       <c r="T45">
         <v>1.082105336618174</v>
       </c>
       <c r="U45">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.15177643582739</v>
+        <v>3.285595369331025</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5154,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07828416704604085</v>
+        <v>0.07741142350577652</v>
       </c>
       <c r="C46">
-        <v>96590.23871287622</v>
+        <v>98922.18710887953</v>
       </c>
       <c r="D46">
-        <v>174366.1787128762</v>
+        <v>176698.1271088795</v>
       </c>
       <c r="E46">
         <v>-480.0599999999977</v>
@@ -5059,37 +5187,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M46">
-        <v>4964.952867348252</v>
+        <v>4762.735423348252</v>
       </c>
       <c r="N46">
-        <v>10327.82264285583</v>
+        <v>10530.04008685583</v>
       </c>
       <c r="O46">
-        <v>2581.955660713958</v>
+        <v>2632.510021713958</v>
       </c>
       <c r="P46">
-        <v>7745.866982141873</v>
+        <v>7897.530065141874</v>
       </c>
       <c r="Q46">
-        <v>11241.86698214187</v>
+        <v>11393.53006514187</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1021751491917939</v>
+        <v>0.1021488214413219</v>
       </c>
       <c r="T46">
         <v>1.098343411897558</v>
       </c>
       <c r="U46">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.080145153194949</v>
+        <v>3.210922747300774</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5236,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07821626166104523</v>
+        <v>0.07732405953521986</v>
       </c>
       <c r="C47">
-        <v>95004.91538970773</v>
+        <v>97395.50155241606</v>
       </c>
       <c r="D47">
-        <v>174548.4903897077</v>
+        <v>176939.0765524161</v>
       </c>
       <c r="E47">
         <v>1287.574999999997</v>
@@ -5141,37 +5269,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M47">
-        <v>5077.79270524253</v>
+        <v>4870.97941024253</v>
       </c>
       <c r="N47">
-        <v>10214.98280496155</v>
+        <v>10421.79609996155</v>
       </c>
       <c r="O47">
-        <v>2553.745701240388</v>
+        <v>2605.449024990388</v>
       </c>
       <c r="P47">
-        <v>7661.237103721165</v>
+        <v>7816.347074971165</v>
       </c>
       <c r="Q47">
-        <v>11157.23710372117</v>
+        <v>11312.34707497117</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1030389155226181</v>
+        <v>0.1030121843847538</v>
       </c>
       <c r="T47">
         <v>1.115171962641647</v>
       </c>
       <c r="U47">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.01169748312395</v>
+        <v>3.139568908471868</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5318,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07904535627604961</v>
+        <v>0.07723669556466317</v>
       </c>
       <c r="C48">
-        <v>91037.09572868755</v>
+        <v>95869.47402114728</v>
       </c>
       <c r="D48">
-        <v>172348.3057286876</v>
+        <v>177180.6840211473</v>
       </c>
       <c r="E48">
         <v>3055.210000000006</v>
@@ -5223,45 +5351,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M48">
-        <v>5402.041689136809</v>
+        <v>4979.223397136809</v>
       </c>
       <c r="N48">
-        <v>9890.733821067275</v>
+        <v>10313.55211306728</v>
       </c>
       <c r="O48">
-        <v>2472.683455266819</v>
+        <v>2578.388028266819</v>
       </c>
       <c r="P48">
-        <v>7418.050365800456</v>
+        <v>7735.164084800456</v>
       </c>
       <c r="Q48">
-        <v>10914.05036580046</v>
+        <v>11231.16408480046</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1039346731990284</v>
+        <v>0.103907523733498</v>
       </c>
       <c r="T48">
         <v>1.132623793042925</v>
       </c>
       <c r="U48">
-        <v>0.06643661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.83092511873001</v>
+        <v>3.07131741046161</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5400,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07899695089105399</v>
+        <v>0.07714933159410652</v>
       </c>
       <c r="C49">
-        <v>89396.38929169881</v>
+        <v>94344.10721432744</v>
       </c>
       <c r="D49">
-        <v>172475.2342916988</v>
+        <v>177422.9522143274</v>
       </c>
       <c r="E49">
         <v>4822.845000000001</v>
@@ -5305,45 +5433,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M49">
-        <v>5519.477378031087</v>
+        <v>5087.467384031087</v>
       </c>
       <c r="N49">
-        <v>9773.298132172997</v>
+        <v>10205.308126173</v>
       </c>
       <c r="O49">
-        <v>2443.324533043249</v>
+        <v>2551.327031543249</v>
       </c>
       <c r="P49">
-        <v>7329.973599129748</v>
+        <v>7653.981094629748</v>
       </c>
       <c r="Q49">
-        <v>10825.97359912975</v>
+        <v>11149.98109462975</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.104864233051907</v>
+        <v>0.1048366494727608</v>
       </c>
       <c r="T49">
         <v>1.150734183081987</v>
       </c>
       <c r="U49">
-        <v>0.06643661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.770692669395329</v>
+        <v>3.005970231515618</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5482,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07894854550605838</v>
+        <v>0.07796196762354983</v>
       </c>
       <c r="C50">
-        <v>87755.8699494874</v>
+        <v>90348.21821133351</v>
       </c>
       <c r="D50">
-        <v>172602.3499494874</v>
+        <v>175194.6982113335</v>
       </c>
       <c r="E50">
         <v>6590.479999999996</v>
@@ -5387,37 +5515,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M50">
-        <v>5636.913066925365</v>
+        <v>5407.827570925366</v>
       </c>
       <c r="N50">
-        <v>9655.862443278718</v>
+        <v>9884.947939278718</v>
       </c>
       <c r="O50">
-        <v>2413.96561081968</v>
+        <v>2471.236984819679</v>
       </c>
       <c r="P50">
-        <v>7241.896832459039</v>
+        <v>7413.710954459038</v>
       </c>
       <c r="Q50">
-        <v>10737.89683245904</v>
+        <v>10909.71095445904</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1058295452068194</v>
+        <v>0.1058015108173799</v>
       </c>
       <c r="T50">
         <v>1.16954112658409</v>
       </c>
       <c r="U50">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.712969905449593</v>
+        <v>2.827896287304746</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5564,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07890014012106276</v>
+        <v>0.07789335365299316</v>
       </c>
       <c r="C51">
-        <v>86115.53811602965</v>
+        <v>88766.5575845056</v>
       </c>
       <c r="D51">
-        <v>172729.6531160297</v>
+        <v>175380.6725845056</v>
       </c>
       <c r="E51">
         <v>8358.115000000005</v>
@@ -5469,37 +5597,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M51">
-        <v>5754.348755819644</v>
+        <v>5520.490645319644</v>
       </c>
       <c r="N51">
-        <v>9538.42675438444</v>
+        <v>9772.284864884437</v>
       </c>
       <c r="O51">
-        <v>2384.60668859611</v>
+        <v>2443.071216221109</v>
       </c>
       <c r="P51">
-        <v>7153.82006578833</v>
+        <v>7329.213648663328</v>
       </c>
       <c r="Q51">
-        <v>10649.82006578833</v>
+        <v>10825.21364866333</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1068327127403559</v>
+        <v>0.106804209861788</v>
       </c>
       <c r="T51">
         <v>1.189085597282353</v>
       </c>
       <c r="U51">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.657603172685316</v>
+        <v>2.770184118176077</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5646,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.07885173473606716</v>
+        <v>0.0778247396824365</v>
       </c>
       <c r="C52">
-        <v>84475.3942065239</v>
+        <v>87185.29221188807</v>
       </c>
       <c r="D52">
-        <v>172857.1442065239</v>
+        <v>175567.0422118881</v>
       </c>
       <c r="E52">
         <v>10125.75</v>
@@ -5551,37 +5679,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M52">
-        <v>5871.784444713922</v>
+        <v>5633.153719713922</v>
       </c>
       <c r="N52">
-        <v>9420.991065490161</v>
+        <v>9659.62179049016</v>
       </c>
       <c r="O52">
-        <v>2355.24776637254</v>
+        <v>2414.90544762254</v>
       </c>
       <c r="P52">
-        <v>7065.743299117621</v>
+        <v>7244.71634286762</v>
       </c>
       <c r="Q52">
-        <v>10561.74329911762</v>
+        <v>10740.71634286762</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1078760069752337</v>
+        <v>0.1078470168679724</v>
       </c>
       <c r="T52">
         <v>1.209411846808547</v>
       </c>
       <c r="U52">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.604451109231609</v>
+        <v>2.714780435812556</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5728,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.07880332935107154</v>
+        <v>0.07775612571187984</v>
       </c>
       <c r="C53">
-        <v>82835.43863739543</v>
+        <v>85604.42335488119</v>
       </c>
       <c r="D53">
-        <v>172984.8236373954</v>
+        <v>175753.8083548812</v>
       </c>
       <c r="E53">
         <v>11893.38499999999</v>
@@ -5633,37 +5761,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M53">
-        <v>5989.2201336082</v>
+        <v>5745.816794108201</v>
       </c>
       <c r="N53">
-        <v>9303.555376595883</v>
+        <v>9546.958716095882</v>
       </c>
       <c r="O53">
-        <v>2325.888844148971</v>
+        <v>2386.73967902397</v>
       </c>
       <c r="P53">
-        <v>6977.666532446912</v>
+        <v>7160.219037071911</v>
       </c>
       <c r="Q53">
-        <v>10473.66653244691</v>
+        <v>10656.21903707191</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1089618846482699</v>
+        <v>0.1089323874254297</v>
       </c>
       <c r="T53">
         <v>1.230567739172545</v>
       </c>
       <c r="U53">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.553383440423147</v>
+        <v>2.661549446875055</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5810,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.07875492396607592</v>
+        <v>0.07768751174132317</v>
       </c>
       <c r="C54">
-        <v>81195.67182630066</v>
+        <v>84023.95228025843</v>
       </c>
       <c r="D54">
-        <v>173112.6918263007</v>
+        <v>175940.9722802584</v>
       </c>
       <c r="E54">
         <v>13661.02</v>
@@ -5715,37 +5843,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M54">
-        <v>6106.655822502479</v>
+        <v>5858.47986850248</v>
       </c>
       <c r="N54">
-        <v>9186.119687701605</v>
+        <v>9434.295641701603</v>
       </c>
       <c r="O54">
-        <v>2296.529921925401</v>
+        <v>2358.573910425401</v>
       </c>
       <c r="P54">
-        <v>6889.589765776203</v>
+        <v>7075.721731276202</v>
       </c>
       <c r="Q54">
-        <v>10385.5897657762</v>
+        <v>10571.7217312762</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1100930072243492</v>
+        <v>0.1100629817561143</v>
       </c>
       <c r="T54">
         <v>1.25260512705171</v>
       </c>
       <c r="U54">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.504279912722701</v>
+        <v>2.610365803665919</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5892,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.07977976858108031</v>
+        <v>0.0776188977707665</v>
       </c>
       <c r="C55">
-        <v>76760.54177273368</v>
+        <v>82443.880260195</v>
       </c>
       <c r="D55">
-        <v>170445.1967727337</v>
+        <v>176128.535260195</v>
       </c>
       <c r="E55">
         <v>15428.655</v>
@@ -5797,45 +5925,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M55">
-        <v>6477.040079896758</v>
+        <v>5971.142942896758</v>
       </c>
       <c r="N55">
-        <v>8815.735430307324</v>
+        <v>9321.632567307326</v>
       </c>
       <c r="O55">
-        <v>2203.933857576831</v>
+        <v>2330.408141826832</v>
       </c>
       <c r="P55">
-        <v>6611.801572730494</v>
+        <v>6991.224425480495</v>
       </c>
       <c r="Q55">
-        <v>10107.80157273049</v>
+        <v>10487.22442548049</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1112722626760064</v>
+        <v>0.1112416864838494</v>
       </c>
       <c r="T55">
         <v>1.275580276117222</v>
       </c>
       <c r="U55">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.361074707206049</v>
+        <v>2.561113618691091</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5974,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.07975161319608469</v>
+        <v>0.07755028380020981</v>
       </c>
       <c r="C56">
-        <v>75065.09174859169</v>
+        <v>80864.2085722968</v>
       </c>
       <c r="D56">
-        <v>170517.3817485917</v>
+        <v>176316.4985722968</v>
       </c>
       <c r="E56">
         <v>17196.29000000001</v>
@@ -5879,45 +6007,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M56">
-        <v>6599.248383291037</v>
+        <v>6083.806017291037</v>
       </c>
       <c r="N56">
-        <v>8693.527126913046</v>
+        <v>9208.969492913046</v>
       </c>
       <c r="O56">
-        <v>2173.381781728262</v>
+        <v>2302.242373228261</v>
       </c>
       <c r="P56">
-        <v>6520.145345184785</v>
+        <v>6906.727119684784</v>
       </c>
       <c r="Q56">
-        <v>10016.14534518478</v>
+        <v>10402.72711968478</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1125027901038226</v>
+        <v>0.112471639243225</v>
       </c>
       <c r="T56">
         <v>1.299554344707321</v>
       </c>
       <c r="U56">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.317351101517048</v>
+        <v>2.513685588715329</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +6056,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.07972345781108908</v>
+        <v>0.07892541982965315</v>
       </c>
       <c r="C57">
-        <v>73369.70289224478</v>
+        <v>75404.43030640286</v>
       </c>
       <c r="D57">
-        <v>170589.6278922448</v>
+        <v>172624.3553064029</v>
       </c>
       <c r="E57">
         <v>18963.925</v>
@@ -5961,37 +6089,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M57">
-        <v>6721.456686685316</v>
+        <v>6536.738829185314</v>
       </c>
       <c r="N57">
-        <v>8571.318823518766</v>
+        <v>8756.03668101877</v>
       </c>
       <c r="O57">
-        <v>2142.829705879692</v>
+        <v>2189.009170254692</v>
       </c>
       <c r="P57">
-        <v>6428.489117639075</v>
+        <v>6567.027510764077</v>
       </c>
       <c r="Q57">
-        <v>9924.489117639074</v>
+        <v>10063.02751076408</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1137880076395417</v>
+        <v>0.1137562565696841</v>
       </c>
       <c r="T57">
         <v>1.32459392745698</v>
       </c>
       <c r="U57">
-        <v>0.06913661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690056</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.275217445125829</v>
+        <v>2.339511476567598</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6138,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08166930242609347</v>
+        <v>0.07888305585909648</v>
       </c>
       <c r="C58">
-        <v>66749.0580300422</v>
+        <v>73748.22961375907</v>
       </c>
       <c r="D58">
-        <v>165736.6180300422</v>
+        <v>172735.7896137591</v>
       </c>
       <c r="E58">
         <v>20731.56000000001</v>
@@ -6043,45 +6171,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M58">
-        <v>7308.906522079594</v>
+        <v>6655.588626079593</v>
       </c>
       <c r="N58">
-        <v>7983.868988124489</v>
+        <v>8637.18688412449</v>
       </c>
       <c r="O58">
-        <v>1995.967247031122</v>
+        <v>2159.296721031123</v>
       </c>
       <c r="P58">
-        <v>5987.901741093367</v>
+        <v>6477.890163093368</v>
       </c>
       <c r="Q58">
-        <v>9483.901741093367</v>
+        <v>9973.890163093369</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1151316441541572</v>
+        <v>0.1150992655928004</v>
       </c>
       <c r="T58">
         <v>1.350771673058897</v>
       </c>
       <c r="U58">
-        <v>0.07383661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.05537746249690056</v>
+        <v>0.05042746249690056</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.092347940694807</v>
+        <v>2.297734485914605</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6220,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08167639704109785</v>
+        <v>0.0788406918885398</v>
       </c>
       <c r="C59">
-        <v>64964.2339491125</v>
+        <v>72092.17288256221</v>
       </c>
       <c r="D59">
-        <v>165719.4289491125</v>
+        <v>172847.3678825622</v>
       </c>
       <c r="E59">
         <v>22499.19500000001</v>
@@ -6125,45 +6253,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M59">
-        <v>7439.422709973872</v>
+        <v>6774.438422973871</v>
       </c>
       <c r="N59">
-        <v>7853.352800230211</v>
+        <v>8518.337087230211</v>
       </c>
       <c r="O59">
-        <v>1963.338200057553</v>
+        <v>2129.584271807553</v>
       </c>
       <c r="P59">
-        <v>5890.014600172658</v>
+        <v>6388.752815422658</v>
       </c>
       <c r="Q59">
-        <v>9386.014600172657</v>
+        <v>9884.752815422658</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1165377753903826</v>
+        <v>0.1165047401518756</v>
       </c>
       <c r="T59">
         <v>1.378166988223694</v>
       </c>
       <c r="U59">
-        <v>0.07383661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.05537746249690056</v>
+        <v>0.05042746249690056</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.055640082086127</v>
+        <v>2.25742335458277</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6302,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08168349165610224</v>
+        <v>0.08001632791798316</v>
       </c>
       <c r="C60">
-        <v>63179.41343328342</v>
+        <v>67280.70884311126</v>
       </c>
       <c r="D60">
-        <v>165702.2434332834</v>
+        <v>169803.5388431113</v>
       </c>
       <c r="E60">
         <v>24266.82999999999</v>
@@ -6207,37 +6335,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M60">
-        <v>7569.938897868149</v>
+        <v>7180.352143868149</v>
       </c>
       <c r="N60">
-        <v>7722.836612335934</v>
+        <v>8112.423366335934</v>
       </c>
       <c r="O60">
-        <v>1930.709153083983</v>
+        <v>2028.105841583983</v>
       </c>
       <c r="P60">
-        <v>5792.12745925195</v>
+        <v>6084.31752475195</v>
       </c>
       <c r="Q60">
-        <v>9288.127459251951</v>
+        <v>9580.31752475195</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1180108652569045</v>
+        <v>0.1179771420709067</v>
       </c>
       <c r="T60">
         <v>1.406866842205861</v>
       </c>
       <c r="U60">
-        <v>0.07383661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.05537746249690056</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.020198011705332</v>
+        <v>2.129808567016278</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6384,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08580583627110662</v>
+        <v>0.07999496394742647</v>
       </c>
       <c r="C61">
-        <v>51994.57374060585</v>
+        <v>65567.43044611774</v>
       </c>
       <c r="D61">
-        <v>156285.0387406058</v>
+        <v>169857.8954461177</v>
       </c>
       <c r="E61">
         <v>26034.465</v>
@@ -6289,45 +6417,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M61">
-        <v>8670.356410262428</v>
+        <v>7304.151318762429</v>
       </c>
       <c r="N61">
-        <v>6622.419099941655</v>
+        <v>7988.624191441654</v>
       </c>
       <c r="O61">
-        <v>1655.604774985414</v>
+        <v>1997.156047860414</v>
       </c>
       <c r="P61">
-        <v>4966.814324956242</v>
+        <v>5991.468143581241</v>
       </c>
       <c r="Q61">
-        <v>8462.814324956242</v>
+        <v>9487.468143581242</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1195558131656958</v>
+        <v>0.119521368473793</v>
       </c>
       <c r="T61">
         <v>1.436966689065208</v>
       </c>
       <c r="U61">
-        <v>0.08313661666253408</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.06235246249690056</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.763800100778235</v>
+        <v>2.093710116727866</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6466,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08799768088611101</v>
+        <v>0.07997359997686981</v>
       </c>
       <c r="C62">
-        <v>45642.90763802636</v>
+        <v>63854.1868609595</v>
       </c>
       <c r="D62">
-        <v>151701.0076380263</v>
+        <v>169912.2868609595</v>
       </c>
       <c r="E62">
         <v>27802.09999999999</v>
@@ -6371,45 +6499,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M62">
-        <v>9315.784673656706</v>
+        <v>7427.950493656706</v>
       </c>
       <c r="N62">
-        <v>5976.990836547377</v>
+        <v>7864.825016547376</v>
       </c>
       <c r="O62">
-        <v>1494.247709136844</v>
+        <v>1966.206254136844</v>
       </c>
       <c r="P62">
-        <v>4482.743127410533</v>
+        <v>5898.618762410532</v>
       </c>
       <c r="Q62">
-        <v>7978.743127410533</v>
+        <v>9394.618762410533</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1211780084699267</v>
+        <v>0.1211428061968237</v>
       </c>
       <c r="T62">
         <v>1.468571528267522</v>
       </c>
       <c r="U62">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.06587746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.641598216997135</v>
+        <v>2.058814948115735</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6548,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.0881097755011154</v>
+        <v>0.07995223600631314</v>
       </c>
       <c r="C63">
-        <v>43648.05469236938</v>
+        <v>62140.97812108939</v>
       </c>
       <c r="D63">
-        <v>151473.7896923694</v>
+        <v>169966.7131210894</v>
       </c>
       <c r="E63">
         <v>29569.735</v>
@@ -6453,45 +6581,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M63">
-        <v>9471.047751550985</v>
+        <v>7551.749668550986</v>
       </c>
       <c r="N63">
-        <v>5821.727758653098</v>
+        <v>7741.025841653097</v>
       </c>
       <c r="O63">
-        <v>1455.431939663275</v>
+        <v>1935.256460413274</v>
       </c>
       <c r="P63">
-        <v>4366.295818989824</v>
+        <v>5805.769381239823</v>
       </c>
       <c r="Q63">
-        <v>7862.295818989824</v>
+        <v>9301.769381239823</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1228833932769386</v>
+        <v>0.1228473945723174</v>
       </c>
       <c r="T63">
         <v>1.50179712845457</v>
       </c>
       <c r="U63">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.06587746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.614686770816854</v>
+        <v>2.025063883392527</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6630,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08822187011611979</v>
+        <v>0.08355787203575646</v>
       </c>
       <c r="C64">
-        <v>41653.88138335838</v>
+        <v>51656.04745509831</v>
       </c>
       <c r="D64">
-        <v>151247.2513833584</v>
+        <v>161249.4174550983</v>
       </c>
       <c r="E64">
         <v>31337.37</v>
@@ -6535,45 +6663,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M64">
-        <v>9626.310829445263</v>
+        <v>8530.377129445262</v>
       </c>
       <c r="N64">
-        <v>5666.46468075882</v>
+        <v>6762.398380758821</v>
       </c>
       <c r="O64">
-        <v>1416.616170189705</v>
+        <v>1690.599595189705</v>
       </c>
       <c r="P64">
-        <v>4249.848510569114</v>
+        <v>5071.798785569115</v>
       </c>
       <c r="Q64">
-        <v>7745.848510569114</v>
+        <v>8567.798785569115</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1246785351790564</v>
+        <v>0.1246416981254687</v>
       </c>
       <c r="T64">
         <v>1.536771444440936</v>
       </c>
       <c r="U64">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253408</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690056</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.588643435803679</v>
+        <v>1.792743190382086</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6712,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08833396473112418</v>
+        <v>0.0835950080651998</v>
       </c>
       <c r="C65">
-        <v>39660.38466623248</v>
+        <v>49803.2789947667</v>
       </c>
       <c r="D65">
-        <v>151021.3896662325</v>
+        <v>161164.2839947667</v>
       </c>
       <c r="E65">
         <v>33105.005</v>
@@ -6617,45 +6745,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M65">
-        <v>9781.573907339542</v>
+        <v>8667.963857339542</v>
       </c>
       <c r="N65">
-        <v>5511.201602864541</v>
+        <v>6624.811652864541</v>
       </c>
       <c r="O65">
-        <v>1377.800400716135</v>
+        <v>1656.202913216135</v>
       </c>
       <c r="P65">
-        <v>4133.401202148406</v>
+        <v>4968.608739648405</v>
       </c>
       <c r="Q65">
-        <v>7629.401202148406</v>
+        <v>8464.608739648405</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.126570711778586</v>
+        <v>0.1265329910598715</v>
       </c>
       <c r="T65">
         <v>1.573636263994133</v>
       </c>
       <c r="U65">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253408</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690056</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.563426873330604</v>
+        <v>1.76428694926491</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6794,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08844605934612856</v>
+        <v>0.08550414409464313</v>
       </c>
       <c r="C66">
-        <v>37667.56151439114</v>
+        <v>43776.897310099</v>
       </c>
       <c r="D66">
-        <v>150796.2015143911</v>
+        <v>156905.537310099</v>
       </c>
       <c r="E66">
         <v>34872.64</v>
@@ -6699,37 +6827,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M66">
-        <v>9936.83698523382</v>
+        <v>9246.752281233821</v>
       </c>
       <c r="N66">
-        <v>5355.938524970263</v>
+        <v>6046.023228970262</v>
       </c>
       <c r="O66">
-        <v>1338.984631242566</v>
+        <v>1511.505807242565</v>
       </c>
       <c r="P66">
-        <v>4016.953893727697</v>
+        <v>4534.517421727696</v>
       </c>
       <c r="Q66">
-        <v>7512.953893727698</v>
+        <v>8030.517421727696</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1285680093003116</v>
+        <v>0.1285293558239632</v>
       </c>
       <c r="T66">
         <v>1.612549129078063</v>
       </c>
       <c r="U66">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.538998328434814</v>
+        <v>1.653853703990816</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6876,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08855815396113295</v>
+        <v>0.08557053012408647</v>
       </c>
       <c r="C67">
-        <v>35675.40891925873</v>
+        <v>41865.21928934332</v>
       </c>
       <c r="D67">
-        <v>150571.6839192587</v>
+        <v>156761.4942893433</v>
       </c>
       <c r="E67">
         <v>36640.27500000001</v>
@@ -6781,37 +6909,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M67">
-        <v>10092.1000631281</v>
+        <v>9391.232785628101</v>
       </c>
       <c r="N67">
-        <v>5200.675447075982</v>
+        <v>5901.542724575982</v>
       </c>
       <c r="O67">
-        <v>1300.168861768996</v>
+        <v>1475.385681143995</v>
       </c>
       <c r="P67">
-        <v>3900.506585306987</v>
+        <v>4426.157043431986</v>
       </c>
       <c r="Q67">
-        <v>7396.506585306986</v>
+        <v>7922.157043431986</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1306794381089931</v>
+        <v>0.1306397985745746</v>
       </c>
       <c r="T67">
         <v>1.653685586452504</v>
       </c>
       <c r="U67">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.515321431074278</v>
+        <v>1.628409800852495</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6958,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.09673874857613732</v>
+        <v>0.08563691615352979</v>
       </c>
       <c r="C68">
-        <v>19150.50567804967</v>
+        <v>39953.80549586914</v>
       </c>
       <c r="D68">
-        <v>135814.4156780497</v>
+        <v>156617.7154958691</v>
       </c>
       <c r="E68">
         <v>38407.91</v>
@@ -6863,45 +6991,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M68">
-        <v>12148.98487402238</v>
+        <v>9535.713290022379</v>
       </c>
       <c r="N68">
-        <v>3143.790636181704</v>
+        <v>5757.062220181704</v>
       </c>
       <c r="O68">
-        <v>785.947659045426</v>
+        <v>1439.265555045426</v>
       </c>
       <c r="P68">
-        <v>2357.842977136278</v>
+        <v>4317.796665136279</v>
       </c>
       <c r="Q68">
-        <v>5853.842977136278</v>
+        <v>7813.796665136279</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1329150686123028</v>
+        <v>0.1328743850163983</v>
       </c>
       <c r="T68">
         <v>1.697241835437205</v>
       </c>
       <c r="U68">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y68">
-        <v>1.258769820588379</v>
+        <v>1.603736925082003</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +7040,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1150308455316403</v>
+        <v>0.08570330218297312</v>
       </c>
       <c r="C69">
-        <v>-7030.629397176424</v>
+        <v>38042.65520330911</v>
       </c>
       <c r="D69">
-        <v>111400.9156028236</v>
+        <v>156474.2002033091</v>
       </c>
       <c r="E69">
         <v>40175.54500000001</v>
@@ -6945,45 +7073,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M69">
-        <v>16205.77192391666</v>
+        <v>9680.193794416658</v>
       </c>
       <c r="N69">
-        <v>-912.9964137125735</v>
+        <v>5612.581715787424</v>
       </c>
       <c r="O69">
-        <v>-228.2491034281434</v>
+        <v>1403.145428946856</v>
       </c>
       <c r="P69">
-        <v>-684.7473102844301</v>
+        <v>4209.436286840568</v>
       </c>
       <c r="Q69">
-        <v>2811.25268971557</v>
+        <v>7705.436286840568</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1363005374629818</v>
+        <v>0.1352444009395447</v>
       </c>
       <c r="T69">
-        <v>1.763200107151526</v>
+        <v>1.743437857087646</v>
       </c>
       <c r="U69">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V69">
-        <v>0.2359155673361482</v>
+        <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.1045547286102333</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.943662269344593</v>
+        <v>1.579800553065854</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +7122,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1159412116982657</v>
+        <v>0.08576968821241646</v>
       </c>
       <c r="C70">
-        <v>-9786.038326177455</v>
+        <v>36131.76768795615</v>
       </c>
       <c r="D70">
-        <v>110413.1416738226</v>
+        <v>156330.9476879562</v>
       </c>
       <c r="E70">
         <v>41943.18000000001</v>
@@ -7027,45 +7155,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M70">
-        <v>16447.64911681094</v>
+        <v>9824.674298810936</v>
       </c>
       <c r="N70">
-        <v>-1154.873606606852</v>
+        <v>5468.101211393147</v>
       </c>
       <c r="O70">
-        <v>-288.7184016517131</v>
+        <v>1367.025302848287</v>
       </c>
       <c r="P70">
-        <v>-866.1552049551392</v>
+        <v>4101.07590854486</v>
       </c>
       <c r="Q70">
-        <v>2629.844795044861</v>
+        <v>7597.07590854486</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1391286792587</v>
+        <v>0.1377625428578877</v>
       </c>
       <c r="T70">
-        <v>1.818300110500011</v>
+        <v>1.79252113009124</v>
       </c>
       <c r="U70">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V70">
-        <v>0.2324462207576755</v>
+        <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.1050294622580613</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.9297848830307019</v>
+        <v>1.556568191991356</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7204,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.116851577864891</v>
+        <v>0.08583607424185979</v>
       </c>
       <c r="C71">
-        <v>-12524.08434546084</v>
+        <v>34221.14222875079</v>
       </c>
       <c r="D71">
-        <v>109442.7306545392</v>
+        <v>156187.9572287508</v>
       </c>
       <c r="E71">
         <v>43710.81500000002</v>
@@ -7109,45 +7237,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M71">
-        <v>16689.52630970521</v>
+        <v>9969.154803205214</v>
       </c>
       <c r="N71">
-        <v>-1396.750799501129</v>
+        <v>5323.620706998869</v>
       </c>
       <c r="O71">
-        <v>-349.1876998752823</v>
+        <v>1330.905176749717</v>
       </c>
       <c r="P71">
-        <v>-1047.563099625847</v>
+        <v>3992.715530249151</v>
       </c>
       <c r="Q71">
-        <v>2448.436900374153</v>
+        <v>7488.715530249152</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1421392818154323</v>
+        <v>0.1404431455451561</v>
       </c>
       <c r="T71">
-        <v>1.876954952774205</v>
+        <v>1.844771065869259</v>
       </c>
       <c r="U71">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V71">
-        <v>0.2290774349495932</v>
+        <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.1054904355103</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.9163097397983729</v>
+        <v>1.534009232687134</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7286,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1177619440315164</v>
+        <v>0.0859024602713031</v>
       </c>
       <c r="C72">
-        <v>-15245.2212695757</v>
+        <v>32310.77810726943</v>
       </c>
       <c r="D72">
-        <v>108489.2287304243</v>
+        <v>156045.2281072694</v>
       </c>
       <c r="E72">
         <v>45478.45000000001</v>
@@ -7191,45 +7319,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M72">
-        <v>16931.40350259949</v>
+        <v>10113.63530759949</v>
       </c>
       <c r="N72">
-        <v>-1638.62799239541</v>
+        <v>5179.140202604591</v>
       </c>
       <c r="O72">
-        <v>-409.6569980988525</v>
+        <v>1294.785050651148</v>
       </c>
       <c r="P72">
-        <v>-1228.970994296557</v>
+        <v>3884.355151953443</v>
       </c>
       <c r="Q72">
-        <v>2267.029005703443</v>
+        <v>7380.355151953443</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.14535059120928</v>
+        <v>0.1433024550782424</v>
       </c>
       <c r="T72">
-        <v>1.939520117866679</v>
+        <v>1.900504330699146</v>
       </c>
       <c r="U72">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V72">
-        <v>0.225804900164599</v>
+        <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.1059382380981891</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.9032196006583961</v>
+        <v>1.512094815077317</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7368,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1186723101981417</v>
+        <v>0.09353034630074646</v>
       </c>
       <c r="C73">
-        <v>-17949.8872345273</v>
+        <v>15715.21558227265</v>
       </c>
       <c r="D73">
-        <v>107552.1977654727</v>
+        <v>141217.3005822726</v>
       </c>
       <c r="E73">
         <v>47246.08499999999</v>
@@ -7273,45 +7401,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M73">
-        <v>17173.28069549377</v>
+        <v>12040.24541899377</v>
       </c>
       <c r="N73">
-        <v>-1880.505185289683</v>
+        <v>3252.530091210314</v>
       </c>
       <c r="O73">
-        <v>-470.1262963224208</v>
+        <v>813.1325228025785</v>
       </c>
       <c r="P73">
-        <v>-1410.378888967262</v>
+        <v>2439.397568407735</v>
       </c>
       <c r="Q73">
-        <v>2085.621111032738</v>
+        <v>5935.397568407736</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1487833702164966</v>
+        <v>0.1463589583722312</v>
       </c>
       <c r="T73">
-        <v>2.006400121931046</v>
+        <v>1.960081268965577</v>
       </c>
       <c r="U73">
-        <v>0.1368366166625341</v>
+        <v>0.09593661666253409</v>
       </c>
       <c r="V73">
-        <v>0.2226245494580554</v>
+        <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.1063734265286728</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.8904981978322217</v>
+        <v>1.27013818888437</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7450,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.119582676364767</v>
+        <v>0.09370323233018979</v>
       </c>
       <c r="C74">
-        <v>-20638.50536906374</v>
+        <v>13644.09417994591</v>
       </c>
       <c r="D74">
-        <v>106631.2146309363</v>
+        <v>140913.8141799459</v>
       </c>
       <c r="E74">
         <v>49013.72</v>
@@ -7355,45 +7483,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M74">
-        <v>17415.15788838805</v>
+        <v>12209.82634038805</v>
       </c>
       <c r="N74">
-        <v>-2122.382378183964</v>
+        <v>3082.949169816035</v>
       </c>
       <c r="O74">
-        <v>-530.5955945459909</v>
+        <v>770.7372924540086</v>
       </c>
       <c r="P74">
-        <v>-1591.786783637973</v>
+        <v>2312.211877362026</v>
       </c>
       <c r="Q74">
-        <v>1904.213216362027</v>
+        <v>5808.211877362026</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1524613477242286</v>
+        <v>0.1496337833300763</v>
       </c>
       <c r="T74">
-        <v>2.078057269142869</v>
+        <v>2.023913702822467</v>
       </c>
       <c r="U74">
-        <v>0.1368366166625341</v>
+        <v>0.09593661666253409</v>
       </c>
       <c r="V74">
-        <v>0.2195325418266935</v>
+        <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.1067965263916431</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.8781301673067742</v>
+        <v>1.252497380705421</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7532,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1204930425313924</v>
+        <v>0.1109465892306934</v>
       </c>
       <c r="C75">
-        <v>-23311.4844317658</v>
+        <v>-12996.34491523534</v>
       </c>
       <c r="D75">
-        <v>105725.8705682342</v>
+        <v>116041.0100847647</v>
       </c>
       <c r="E75">
         <v>50781.355</v>
@@ -7437,37 +7565,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M75">
-        <v>17657.03508128232</v>
+        <v>16069.87561478233</v>
       </c>
       <c r="N75">
-        <v>-2364.259571078241</v>
+        <v>-777.100104578245</v>
       </c>
       <c r="O75">
-        <v>-591.0648927695602</v>
+        <v>-194.2750261445613</v>
       </c>
       <c r="P75">
-        <v>-1773.194678308681</v>
+        <v>-582.8250784336838</v>
       </c>
       <c r="Q75">
-        <v>1722.805321691319</v>
+        <v>2913.174921566316</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1564117680103111</v>
+        <v>0.1543100891188336</v>
       </c>
       <c r="T75">
-        <v>2.155022353185198</v>
+        <v>2.115063606648733</v>
       </c>
       <c r="U75">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V75">
-        <v>0.2165252467331772</v>
+        <v>0.2379106079722327</v>
       </c>
       <c r="W75">
-        <v>0.1072080344775457</v>
+        <v>0.09490803447754573</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8661009869327088</v>
+        <v>0.9516424318889309</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7614,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1214034086980177</v>
+        <v>0.1117339553973188</v>
       </c>
       <c r="C76">
-        <v>-25969.21941595487</v>
+        <v>-15691.77336157023</v>
       </c>
       <c r="D76">
-        <v>104835.7705840451</v>
+        <v>115113.2166384298</v>
       </c>
       <c r="E76">
         <v>52548.99000000001</v>
@@ -7519,37 +7647,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M76">
-        <v>17898.9122741766</v>
+        <v>16290.01089717661</v>
       </c>
       <c r="N76">
-        <v>-2606.136763972521</v>
+        <v>-997.2353869725248</v>
       </c>
       <c r="O76">
-        <v>-651.5341909931303</v>
+        <v>-249.3088467431312</v>
       </c>
       <c r="P76">
-        <v>-1954.602572979391</v>
+        <v>-747.9265402293936</v>
       </c>
       <c r="Q76">
-        <v>1541.397427020609</v>
+        <v>2748.073459770606</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1606660667799385</v>
+        <v>0.1584835540849426</v>
       </c>
       <c r="T76">
-        <v>2.237907828307705</v>
+        <v>2.196412206904454</v>
       </c>
       <c r="U76">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V76">
-        <v>0.2135992298854315</v>
+        <v>0.2346955997563917</v>
       </c>
       <c r="W76">
-        <v>0.1076084207232888</v>
+        <v>0.09530842072328881</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8543969195417261</v>
+        <v>0.9387823990255669</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7696,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1223137748646431</v>
+        <v>0.1125213215639441</v>
       </c>
       <c r="C77">
-        <v>-28612.09212430015</v>
+        <v>-18372.48334190261</v>
       </c>
       <c r="D77">
-        <v>103960.5328756998</v>
+        <v>114200.1416580974</v>
       </c>
       <c r="E77">
         <v>54316.625</v>
@@ -7601,37 +7729,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M77">
-        <v>18140.78946707088</v>
+        <v>16510.14617957089</v>
       </c>
       <c r="N77">
-        <v>-2848.013956866798</v>
+        <v>-1217.370669366803</v>
       </c>
       <c r="O77">
-        <v>-712.0034892166996</v>
+        <v>-304.3426673417007</v>
       </c>
       <c r="P77">
-        <v>-2136.010467650099</v>
+        <v>-913.0280020251021</v>
       </c>
       <c r="Q77">
-        <v>1359.989532349901</v>
+        <v>2582.971997974898</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.165260709451136</v>
+        <v>0.1629908962483403</v>
       </c>
       <c r="T77">
-        <v>2.327424141440014</v>
+        <v>2.284268695180632</v>
       </c>
       <c r="U77">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V77">
-        <v>0.2107512401536258</v>
+        <v>0.2315663250929732</v>
       </c>
       <c r="W77">
-        <v>0.1079981300024787</v>
+        <v>0.09569813000247875</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8430049606145033</v>
+        <v>0.9262653003718927</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7778,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1232241410312684</v>
+        <v>0.1133086877305695</v>
       </c>
       <c r="C78">
-        <v>-31240.47171488061</v>
+        <v>-21038.82233945042</v>
       </c>
       <c r="D78">
-        <v>103099.7882851194</v>
+        <v>113301.4376605496</v>
       </c>
       <c r="E78">
         <v>56084.26000000001</v>
@@ -7683,37 +7811,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M78">
-        <v>18382.66665996516</v>
+        <v>16730.28146196517</v>
       </c>
       <c r="N78">
-        <v>-3089.891149761079</v>
+        <v>-1437.505951761083</v>
       </c>
       <c r="O78">
-        <v>-772.4727874402697</v>
+        <v>-359.3764879402706</v>
       </c>
       <c r="P78">
-        <v>-2317.418362320809</v>
+        <v>-1078.129463820812</v>
       </c>
       <c r="Q78">
-        <v>1178.581637679191</v>
+        <v>2417.870536179188</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1702382390116</v>
+        <v>0.1678738502586878</v>
       </c>
       <c r="T78">
-        <v>2.424400147333348</v>
+        <v>2.379446557479825</v>
       </c>
       <c r="U78">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V78">
-        <v>0.2079781975200254</v>
+        <v>0.2285193997628024</v>
       </c>
       <c r="W78">
-        <v>0.1083775837743216</v>
+        <v>0.09607758377432159</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8319127900801018</v>
+        <v>0.9140775990512098</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7860,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1241345071978937</v>
+        <v>0.1140960538971948</v>
       </c>
       <c r="C79">
-        <v>-33854.71522034318</v>
+        <v>-23691.12698468808</v>
       </c>
       <c r="D79">
-        <v>102253.1797796568</v>
+        <v>112416.7680153119</v>
       </c>
       <c r="E79">
         <v>57851.89499999999</v>
@@ -7765,37 +7893,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M79">
-        <v>18624.54385285944</v>
+        <v>16950.41674435944</v>
       </c>
       <c r="N79">
-        <v>-3331.768342655356</v>
+        <v>-1657.641234155359</v>
       </c>
       <c r="O79">
-        <v>-832.942085663839</v>
+        <v>-414.4103085388397</v>
       </c>
       <c r="P79">
-        <v>-2498.826256991517</v>
+        <v>-1243.230925616519</v>
       </c>
       <c r="Q79">
-        <v>997.1737430084831</v>
+        <v>2252.769074383481</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1756485972294957</v>
+        <v>0.1731814089655873</v>
       </c>
       <c r="T79">
-        <v>2.52980884939132</v>
+        <v>2.482900755631122</v>
       </c>
       <c r="U79">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V79">
-        <v>0.2052771819678173</v>
+        <v>0.2255516153502986</v>
       </c>
       <c r="W79">
-        <v>0.1087471816040386</v>
+        <v>0.09644718160403863</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8211087278712693</v>
+        <v>0.9022064614011942</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7942,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1250448733645191</v>
+        <v>0.1148834200638202</v>
       </c>
       <c r="C80">
-        <v>-36455.16804169063</v>
+        <v>-26329.7234757611</v>
       </c>
       <c r="D80">
-        <v>101420.3619583094</v>
+        <v>111545.8065242389</v>
       </c>
       <c r="E80">
         <v>59619.53</v>
@@ -7847,37 +7975,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M80">
-        <v>18866.42104575372</v>
+        <v>17170.55202675372</v>
       </c>
       <c r="N80">
-        <v>-3573.645535549633</v>
+        <v>-1877.776516549638</v>
       </c>
       <c r="O80">
-        <v>-893.4113838874082</v>
+        <v>-469.4441291374096</v>
       </c>
       <c r="P80">
-        <v>-2680.234151662225</v>
+        <v>-1408.332387412229</v>
       </c>
       <c r="Q80">
-        <v>815.7658483377754</v>
+        <v>2087.667612587771</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1815508061944728</v>
+        <v>0.1789714730094776</v>
       </c>
       <c r="T80">
-        <v>2.644800160727288</v>
+        <v>2.595759880887082</v>
       </c>
       <c r="U80">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V80">
-        <v>0.2026454232246402</v>
+        <v>0.2226599279740127</v>
       </c>
       <c r="W80">
-        <v>0.109107302566327</v>
+        <v>0.09680730256632702</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8105816928985607</v>
+        <v>0.8906397118960506</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +8024,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1259552395311444</v>
+        <v>0.1156707862304455</v>
       </c>
       <c r="C81">
-        <v>-39042.16441813397</v>
+        <v>-28954.92797950703</v>
       </c>
       <c r="D81">
-        <v>100601.000581866</v>
+        <v>110688.237020493</v>
       </c>
       <c r="E81">
         <v>61387.16500000001</v>
@@ -7929,37 +8057,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M81">
-        <v>19108.298238648</v>
+        <v>17390.687309148</v>
       </c>
       <c r="N81">
-        <v>-3815.522728443913</v>
+        <v>-2097.911798943918</v>
       </c>
       <c r="O81">
-        <v>-953.8806821109783</v>
+        <v>-524.4779497359796</v>
       </c>
       <c r="P81">
-        <v>-2861.642046332935</v>
+        <v>-1573.433849207939</v>
       </c>
       <c r="Q81">
-        <v>634.357953667065</v>
+        <v>1922.566150792061</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1880151302989715</v>
+        <v>0.1853129717242146</v>
       </c>
       <c r="T81">
-        <v>2.770743025523827</v>
+        <v>2.719367494262657</v>
       </c>
       <c r="U81">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V81">
-        <v>0.2000802912850878</v>
+        <v>0.2198414478730758</v>
       </c>
       <c r="W81">
-        <v>0.1094583065422284</v>
+        <v>0.09715830654222839</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8003211651403511</v>
+        <v>0.8793657914923031</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +8106,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1969323850049628</v>
+        <v>0.1164581523970708</v>
       </c>
       <c r="C82">
-        <v>-79687.57242461499</v>
+        <v>-31567.04701411948</v>
       </c>
       <c r="D82">
-        <v>61723.22757538503</v>
+        <v>109843.7529858805</v>
       </c>
       <c r="E82">
         <v>63154.80000000002</v>
@@ -8011,45 +8139,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M82">
-        <v>31355.95235154228</v>
+        <v>17610.82259154228</v>
       </c>
       <c r="N82">
-        <v>-16063.1768413382</v>
+        <v>-2318.047081338198</v>
       </c>
       <c r="O82">
-        <v>-4015.794210334549</v>
+        <v>-579.5117703345495</v>
       </c>
       <c r="P82">
-        <v>-12047.38263100365</v>
+        <v>-1738.535311003649</v>
       </c>
       <c r="Q82">
-        <v>-8551.382631003649</v>
+        <v>1757.464688996351</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2058597833498852</v>
+        <v>0.1922886203104254</v>
       </c>
       <c r="T82">
-        <v>3.118406089782673</v>
+        <v>2.855335868975791</v>
       </c>
       <c r="U82">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V82">
-        <v>0.1219288074776964</v>
+        <v>0.2170934297746623</v>
       </c>
       <c r="W82">
-        <v>0.1947005354187322</v>
+        <v>0.09750053541873221</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.4877152299107856</v>
+        <v>0.8683737190986492</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8188,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1986917511715882</v>
+        <v>0.1172455185636962</v>
       </c>
       <c r="C83">
-        <v>-82040.86659529341</v>
+        <v>-34166.37781442782</v>
       </c>
       <c r="D83">
-        <v>61137.56840470659</v>
+        <v>109012.0571855722</v>
       </c>
       <c r="E83">
         <v>64922.435</v>
@@ -8093,45 +8221,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M83">
-        <v>31747.90175593656</v>
+        <v>17830.95787393656</v>
       </c>
       <c r="N83">
-        <v>-16455.12624573247</v>
+        <v>-2538.182363732474</v>
       </c>
       <c r="O83">
-        <v>-4113.781561433118</v>
+        <v>-634.5455909331185</v>
       </c>
       <c r="P83">
-        <v>-12341.34468429935</v>
+        <v>-1903.636772799356</v>
       </c>
       <c r="Q83">
-        <v>-8845.344684299354</v>
+        <v>1592.363227200644</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2142839824735634</v>
+        <v>0.1999985476951846</v>
       </c>
       <c r="T83">
-        <v>3.282532726087025</v>
+        <v>3.005616704185043</v>
       </c>
       <c r="U83">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V83">
-        <v>0.1204235135582187</v>
+        <v>0.2144132639749751</v>
       </c>
       <c r="W83">
-        <v>0.1950343141995199</v>
+        <v>0.09783431419951988</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.4816940542328747</v>
+        <v>0.8576530558999006</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8270,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2004511173382135</v>
+        <v>0.1180328847303215</v>
       </c>
       <c r="C84">
-        <v>-84383.15120755693</v>
+        <v>-36753.20868070677</v>
       </c>
       <c r="D84">
-        <v>60562.91879244307</v>
+        <v>108192.8613192932</v>
       </c>
       <c r="E84">
         <v>66690.07000000001</v>
@@ -8175,45 +8303,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M84">
-        <v>32139.85116033084</v>
+        <v>18051.09315633083</v>
       </c>
       <c r="N84">
-        <v>-16847.07565012675</v>
+        <v>-2758.31764612675</v>
       </c>
       <c r="O84">
-        <v>-4211.768912531688</v>
+        <v>-689.5794115316876</v>
       </c>
       <c r="P84">
-        <v>-12635.30673759506</v>
+        <v>-2068.738234595063</v>
       </c>
       <c r="Q84">
-        <v>-9139.306737595065</v>
+        <v>1427.261765404937</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2236442037220946</v>
+        <v>0.2085651336782504</v>
       </c>
       <c r="T84">
-        <v>3.464895655314082</v>
+        <v>3.172595409973101</v>
       </c>
       <c r="U84">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V84">
-        <v>0.1189549341245819</v>
+        <v>0.2117984680728413</v>
       </c>
       <c r="W84">
-        <v>0.1953599520344347</v>
+        <v>0.0981599520344347</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.4758197364983274</v>
+        <v>0.8471938722913653</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8352,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2022104835048388</v>
+        <v>0.1188202508969469</v>
       </c>
       <c r="C85">
-        <v>-86714.73381663584</v>
+        <v>-39327.81931187629</v>
       </c>
       <c r="D85">
-        <v>59998.97118336418</v>
+        <v>107385.8856881237</v>
       </c>
       <c r="E85">
         <v>68457.70500000002</v>
@@ -8257,45 +8385,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M85">
-        <v>32531.80056472512</v>
+        <v>18271.22843872511</v>
       </c>
       <c r="N85">
-        <v>-17239.02505452103</v>
+        <v>-2978.45292852103</v>
       </c>
       <c r="O85">
-        <v>-4309.756263630258</v>
+        <v>-744.6132321302575</v>
       </c>
       <c r="P85">
-        <v>-12929.26879089078</v>
+        <v>-2233.839696390773</v>
       </c>
       <c r="Q85">
-        <v>-9433.268790890776</v>
+        <v>1262.160303609227</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2341056274704532</v>
+        <v>0.2181395533063828</v>
       </c>
       <c r="T85">
-        <v>3.668713046803146</v>
+        <v>3.359218669383283</v>
       </c>
       <c r="U85">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V85">
-        <v>0.1175217421471773</v>
+        <v>0.2092466793008794</v>
       </c>
       <c r="W85">
-        <v>0.1956777431745323</v>
+        <v>0.09847774317453228</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.470086968588709</v>
+        <v>0.8369867172035175</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8434,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2039698496714642</v>
+        <v>0.1196076170635722</v>
       </c>
       <c r="C86">
-        <v>-89035.91062792043</v>
+        <v>-41890.48112390035</v>
       </c>
       <c r="D86">
-        <v>59445.42937207957</v>
+        <v>106590.8588760996</v>
       </c>
       <c r="E86">
         <v>70225.34</v>
@@ -8339,45 +8467,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M86">
-        <v>32923.74996911939</v>
+        <v>18491.36372111939</v>
       </c>
       <c r="N86">
-        <v>-17630.97445891531</v>
+        <v>-3198.588210915306</v>
       </c>
       <c r="O86">
-        <v>-4407.743614728826</v>
+        <v>-799.6470527288266</v>
       </c>
       <c r="P86">
-        <v>-13223.23084418648</v>
+        <v>-2398.94115818648</v>
       </c>
       <c r="Q86">
-        <v>-9727.230844186479</v>
+        <v>1097.05884181352</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2458747291873564</v>
+        <v>0.2289107753880316</v>
       </c>
       <c r="T86">
-        <v>3.898007612228341</v>
+        <v>3.569169836219737</v>
       </c>
       <c r="U86">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V86">
-        <v>0.1161226737882823</v>
+        <v>0.2067556474044404</v>
       </c>
       <c r="W86">
-        <v>0.1959879678589133</v>
+        <v>0.09878796785891325</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.4644906951531292</v>
+        <v>0.8270225896177614</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8516,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2057292158380895</v>
+        <v>0.1203949832301975</v>
       </c>
       <c r="C87">
-        <v>-91346.967015735</v>
+        <v>-44441.45755414625</v>
       </c>
       <c r="D87">
-        <v>58902.007984265</v>
+        <v>105807.5174458538</v>
       </c>
       <c r="E87">
         <v>71992.97500000001</v>
@@ -8421,45 +8549,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M87">
-        <v>33315.69937351367</v>
+        <v>18711.49900351367</v>
       </c>
       <c r="N87">
-        <v>-18022.92386330959</v>
+        <v>-3418.723493309586</v>
       </c>
       <c r="O87">
-        <v>-4505.730965827397</v>
+        <v>-854.6808733273965</v>
       </c>
       <c r="P87">
-        <v>-13517.19289748219</v>
+        <v>-2564.04261998219</v>
       </c>
       <c r="Q87">
-        <v>-10021.19289748219</v>
+        <v>931.9573800178105</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2592130444665136</v>
+        <v>0.2411181604139004</v>
       </c>
       <c r="T87">
-        <v>4.157874786376897</v>
+        <v>3.807114491967719</v>
       </c>
       <c r="U87">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V87">
-        <v>0.1147565246848907</v>
+        <v>0.2043232280232117</v>
       </c>
       <c r="W87">
-        <v>0.1962908931389559</v>
+        <v>0.09909089313895585</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.459026098739563</v>
+        <v>0.8172929120928465</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8598,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2074885820047148</v>
+        <v>0.1211823493968229</v>
       </c>
       <c r="C88">
-        <v>-93648.17801391485</v>
+        <v>-46981.00435242117</v>
       </c>
       <c r="D88">
-        <v>58368.43198608514</v>
+        <v>105035.6056475788</v>
       </c>
       <c r="E88">
         <v>73760.60999999999</v>
@@ -8503,45 +8631,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M88">
-        <v>33707.64877790795</v>
+        <v>18931.63428590795</v>
       </c>
       <c r="N88">
-        <v>-18414.87326770386</v>
+        <v>-3638.858775703862</v>
       </c>
       <c r="O88">
-        <v>-4603.718316925966</v>
+        <v>-909.7146939259655</v>
       </c>
       <c r="P88">
-        <v>-13811.1549507779</v>
+        <v>-2729.144081777897</v>
       </c>
       <c r="Q88">
-        <v>-10315.1549507779</v>
+        <v>766.8559182221034</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2744568333569787</v>
+        <v>0.2550694575863219</v>
       </c>
       <c r="T88">
-        <v>4.454865842546675</v>
+        <v>4.079051241393985</v>
       </c>
       <c r="U88">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V88">
-        <v>0.1134221464908804</v>
+        <v>0.2019473765345697</v>
       </c>
       <c r="W88">
-        <v>0.196586773645044</v>
+        <v>0.09938677364504397</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.4536885859635216</v>
+        <v>0.8077895061382787</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8680,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2092479481713402</v>
+        <v>0.1476406239405827</v>
       </c>
       <c r="C89">
-        <v>-95939.80877995913</v>
+        <v>-69428.61400623845</v>
       </c>
       <c r="D89">
-        <v>57844.43622004087</v>
+        <v>84355.63099376154</v>
       </c>
       <c r="E89">
         <v>75528.245</v>
@@ -8585,45 +8713,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M89">
-        <v>34099.59818230222</v>
+        <v>23488.48527730222</v>
       </c>
       <c r="N89">
-        <v>-18806.82267209814</v>
+        <v>-8195.709767098142</v>
       </c>
       <c r="O89">
-        <v>-4701.705668024535</v>
+        <v>-2048.927441774536</v>
       </c>
       <c r="P89">
-        <v>-14105.11700407361</v>
+        <v>-6146.782325323607</v>
       </c>
       <c r="Q89">
-        <v>-10609.11700407361</v>
+        <v>-2650.782325323607</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2920458205382848</v>
+        <v>0.2799125572247658</v>
       </c>
       <c r="T89">
-        <v>4.797547830434881</v>
+        <v>4.563289493784297</v>
       </c>
       <c r="U89">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V89">
-        <v>0.1121184436576519</v>
+        <v>0.1627688559911316</v>
       </c>
       <c r="W89">
-        <v>0.1968758523004174</v>
+        <v>0.1278758523004174</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.4484737746306076</v>
+        <v>0.6510754239645264</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8762,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2110073143379655</v>
+        <v>0.197541434185251</v>
       </c>
       <c r="C90">
-        <v>-98222.11503440447</v>
+        <v>-94038.12523215439</v>
       </c>
       <c r="D90">
-        <v>57329.76496559553</v>
+        <v>61513.75476784561</v>
       </c>
       <c r="E90">
         <v>77295.88</v>
@@ -8667,37 +8795,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M90">
-        <v>34491.54758669651</v>
+        <v>32158.26938669651</v>
       </c>
       <c r="N90">
-        <v>-19198.77207649242</v>
+        <v>-16865.49387649242</v>
       </c>
       <c r="O90">
-        <v>-4799.693019123106</v>
+        <v>-4216.373469123106</v>
       </c>
       <c r="P90">
-        <v>-14399.07905736932</v>
+        <v>-12649.12040736932</v>
       </c>
       <c r="Q90">
-        <v>-10903.07905736932</v>
+        <v>-9153.120407369317</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3125663055831419</v>
+        <v>0.3103506376438545</v>
       </c>
       <c r="T90">
-        <v>5.197343482971122</v>
+        <v>5.156584335521626</v>
       </c>
       <c r="U90">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.1108443704342695</v>
+        <v>0.1188868042486338</v>
       </c>
       <c r="W90">
-        <v>0.1971583609863506</v>
+        <v>0.1821583609863505</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4433774817370779</v>
+        <v>0.4755472169945353</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8844,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2127666805045909</v>
+        <v>0.1991508003518764</v>
       </c>
       <c r="C91">
-        <v>-100495.3434769498</v>
+        <v>-96338.31093275723</v>
       </c>
       <c r="D91">
-        <v>56824.17152305018</v>
+        <v>60981.20406724278</v>
       </c>
       <c r="E91">
         <v>79063.51500000001</v>
@@ -8749,37 +8877,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M91">
-        <v>34883.49699109079</v>
+        <v>32523.70426609079</v>
       </c>
       <c r="N91">
-        <v>-19590.72148088671</v>
+        <v>-17230.9287558867</v>
       </c>
       <c r="O91">
-        <v>-4897.680370221677</v>
+        <v>-4307.732188971676</v>
       </c>
       <c r="P91">
-        <v>-14693.04111066503</v>
+        <v>-12923.19656691503</v>
       </c>
       <c r="Q91">
-        <v>-11197.04111066503</v>
+        <v>-9427.196566915027</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3368177879088821</v>
+        <v>0.3344006956114776</v>
       </c>
       <c r="T91">
-        <v>5.669829254150315</v>
+        <v>5.625364729659956</v>
       </c>
       <c r="U91">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.1095989280698395</v>
+        <v>0.1175509974593233</v>
       </c>
       <c r="W91">
-        <v>0.1974345211624875</v>
+        <v>0.1824345211624875</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4383957122793578</v>
+        <v>0.4702039898372933</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8926,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2145260466712162</v>
+        <v>0.2007601665185017</v>
       </c>
       <c r="C92">
-        <v>-102759.7321807547</v>
+        <v>-98629.35474339343</v>
       </c>
       <c r="D92">
-        <v>56327.41781924531</v>
+        <v>60457.79525660657</v>
       </c>
       <c r="E92">
         <v>80831.14999999999</v>
@@ -8831,37 +8959,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M92">
-        <v>35275.44639548507</v>
+        <v>32889.13914548506</v>
       </c>
       <c r="N92">
-        <v>-19982.67088528098</v>
+        <v>-17596.36363528098</v>
       </c>
       <c r="O92">
-        <v>-4995.667721320246</v>
+        <v>-4399.090908820244</v>
       </c>
       <c r="P92">
-        <v>-14987.00316396074</v>
+        <v>-13197.27272646073</v>
       </c>
       <c r="Q92">
-        <v>-11491.00316396074</v>
+        <v>-9701.272726460733</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3659195666997703</v>
+        <v>0.3632607651726253</v>
       </c>
       <c r="T92">
-        <v>6.236812179565346</v>
+        <v>6.187901202625952</v>
       </c>
       <c r="U92">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.1083811622023968</v>
+        <v>0.1162448752653309</v>
       </c>
       <c r="W92">
-        <v>0.1977045444458213</v>
+        <v>0.1827045444458213</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4335246488095872</v>
+        <v>0.4649795010613234</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +9008,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2162854128378416</v>
+        <v>0.202369532685127</v>
       </c>
       <c r="C93">
-        <v>-105015.5109662351</v>
+        <v>-100911.4900585451</v>
       </c>
       <c r="D93">
-        <v>55839.27403376494</v>
+        <v>59943.29494145492</v>
       </c>
       <c r="E93">
         <v>82598.785</v>
@@ -8913,37 +9041,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M93">
-        <v>35667.39579987934</v>
+        <v>33254.57402487934</v>
       </c>
       <c r="N93">
-        <v>-20374.62028967526</v>
+        <v>-17961.79851467525</v>
       </c>
       <c r="O93">
-        <v>-5093.655072418815</v>
+        <v>-4490.449628668814</v>
       </c>
       <c r="P93">
-        <v>-15280.96521725644</v>
+        <v>-13471.34888600644</v>
       </c>
       <c r="Q93">
-        <v>-11784.96521725644</v>
+        <v>-9975.348886006441</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4014884074441893</v>
+        <v>0.3985341835251393</v>
       </c>
       <c r="T93">
-        <v>6.929791310628164</v>
+        <v>6.875445780695503</v>
       </c>
       <c r="U93">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.1071901604199529</v>
+        <v>0.1149674590536239</v>
       </c>
       <c r="W93">
-        <v>0.1979686331514995</v>
+        <v>0.1829686331514995</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4287606416798115</v>
+        <v>0.4598698362144956</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +9090,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2180447790044669</v>
+        <v>0.2039788988517524</v>
       </c>
       <c r="C94">
-        <v>-107262.90175559</v>
+        <v>-103184.9423949173</v>
       </c>
       <c r="D94">
-        <v>55359.51824441003</v>
+        <v>59437.47760508268</v>
       </c>
       <c r="E94">
         <v>84366.42000000001</v>
@@ -8995,37 +9123,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M94">
-        <v>36059.34520427362</v>
+        <v>33620.00890427362</v>
       </c>
       <c r="N94">
-        <v>-20766.56969406954</v>
+        <v>-18327.23339406954</v>
       </c>
       <c r="O94">
-        <v>-5191.642423517385</v>
+        <v>-4581.808348517385</v>
       </c>
       <c r="P94">
-        <v>-15574.92727055216</v>
+        <v>-13745.42504555215</v>
       </c>
       <c r="Q94">
-        <v>-12078.92727055216</v>
+        <v>-10249.42504555215</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4459494583747131</v>
+        <v>0.4426259564657819</v>
       </c>
       <c r="T94">
-        <v>7.796015224456686</v>
+        <v>7.734876503282444</v>
       </c>
       <c r="U94">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.1060250499806056</v>
+        <v>0.1137178127595628</v>
       </c>
       <c r="W94">
-        <v>0.1982269807983585</v>
+        <v>0.1832269807983586</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4241001999224223</v>
+        <v>0.4548712510382511</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9172,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2198041451710922</v>
+        <v>0.2055882650183777</v>
       </c>
       <c r="C95">
-        <v>-109502.1189092078</v>
+        <v>-105449.929721031</v>
       </c>
       <c r="D95">
-        <v>54887.93609079219</v>
+        <v>58940.12527896897</v>
       </c>
       <c r="E95">
         <v>86134.05500000002</v>
@@ -9077,37 +9205,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M95">
-        <v>36451.2946086679</v>
+        <v>33985.4437836679</v>
       </c>
       <c r="N95">
-        <v>-21158.51909846382</v>
+        <v>-18692.66827346382</v>
       </c>
       <c r="O95">
-        <v>-5289.629774615954</v>
+        <v>-4673.167068365954</v>
       </c>
       <c r="P95">
-        <v>-15868.88932384786</v>
+        <v>-14019.50120509786</v>
       </c>
       <c r="Q95">
-        <v>-12372.88932384786</v>
+        <v>-10523.50120509786</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5031136667139579</v>
+        <v>0.4993153788180366</v>
       </c>
       <c r="T95">
-        <v>8.909731685093357</v>
+        <v>8.839858860894223</v>
       </c>
       <c r="U95">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.1048849956797388</v>
+        <v>0.1124950405793524</v>
       </c>
       <c r="W95">
-        <v>0.1984797725818443</v>
+        <v>0.1834797725818443</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4195399827189554</v>
+        <v>0.4499801623174097</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9254,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2215635113377176</v>
+        <v>0.2071976311850031</v>
       </c>
       <c r="C96">
-        <v>-111733.3695450237</v>
+        <v>-107706.6627704054</v>
       </c>
       <c r="D96">
-        <v>54424.32045497627</v>
+        <v>58451.02722959465</v>
       </c>
       <c r="E96">
         <v>87901.69</v>
@@ -9159,37 +9287,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M96">
-        <v>36843.24401306218</v>
+        <v>34350.87866306218</v>
       </c>
       <c r="N96">
-        <v>-21550.46850285809</v>
+        <v>-19058.10315285809</v>
       </c>
       <c r="O96">
-        <v>-5387.617125714523</v>
+        <v>-4764.525788214523</v>
       </c>
       <c r="P96">
-        <v>-16162.85137714357</v>
+        <v>-14293.57736464357</v>
       </c>
       <c r="Q96">
-        <v>-12666.85137714357</v>
+        <v>-10797.57736464357</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5793326111662842</v>
+        <v>0.5749012752877094</v>
       </c>
       <c r="T96">
-        <v>10.39468696594225</v>
+        <v>10.31316867104326</v>
       </c>
       <c r="U96">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.1037691978533587</v>
+        <v>0.1112982848285082</v>
       </c>
       <c r="W96">
-        <v>0.1987271858167453</v>
+        <v>0.1837271858167452</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4150767914134347</v>
+        <v>0.445193139314033</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9336,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2233228775043429</v>
+        <v>0.2088069973516284</v>
       </c>
       <c r="C97">
-        <v>-113956.8538418277</v>
+        <v>-109955.3453392751</v>
       </c>
       <c r="D97">
-        <v>53968.47115817229</v>
+        <v>57969.97966072486</v>
       </c>
       <c r="E97">
         <v>89669.32500000001</v>
@@ -9241,37 +9369,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M97">
-        <v>37235.19341745646</v>
+        <v>34716.31354245645</v>
       </c>
       <c r="N97">
-        <v>-21942.41790725238</v>
+        <v>-19423.53803225237</v>
       </c>
       <c r="O97">
-        <v>-5485.604476813094</v>
+        <v>-4855.884508063093</v>
       </c>
       <c r="P97">
-        <v>-16456.81343043928</v>
+        <v>-14567.65352418928</v>
       </c>
       <c r="Q97">
-        <v>-12960.81343043928</v>
+        <v>-11071.65352418928</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6860391333995415</v>
+        <v>0.6807215303452515</v>
       </c>
       <c r="T97">
-        <v>12.47362435913071</v>
+        <v>12.37580240525192</v>
       </c>
       <c r="U97">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.1026768905075338</v>
+        <v>0.1101267239355766</v>
       </c>
       <c r="W97">
-        <v>0.1989693903519641</v>
+        <v>0.1839693903519641</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4107075620301353</v>
+        <v>0.4405068957423064</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9418,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2250822436709683</v>
+        <v>0.2104163635182538</v>
       </c>
       <c r="C98">
-        <v>-116172.7653274565</v>
+        <v>-112196.1745697275</v>
       </c>
       <c r="D98">
-        <v>53520.19467254352</v>
+        <v>57496.78543027244</v>
       </c>
       <c r="E98">
         <v>91436.95999999999</v>
@@ -9323,37 +9451,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M98">
-        <v>37627.14282185074</v>
+        <v>35081.74842185073</v>
       </c>
       <c r="N98">
-        <v>-22334.36731164665</v>
+        <v>-19788.97291164665</v>
       </c>
       <c r="O98">
-        <v>-5583.591827911663</v>
+        <v>-4947.243227911662</v>
       </c>
       <c r="P98">
-        <v>-16750.77548373499</v>
+        <v>-14841.72968373499</v>
       </c>
       <c r="Q98">
-        <v>-13254.77548373499</v>
+        <v>-11345.72968373499</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8460989167494251</v>
+        <v>0.8394519129315626</v>
       </c>
       <c r="T98">
-        <v>15.59203044891335</v>
+        <v>15.46975300656486</v>
       </c>
       <c r="U98">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.101607339564747</v>
+        <v>0.1089795705612477</v>
       </c>
       <c r="W98">
-        <v>0.1992065489593659</v>
+        <v>0.1842065489593659</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4064293582589881</v>
+        <v>0.4359182822449906</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9500,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2268416098375936</v>
+        <v>0.2120257296848791</v>
       </c>
       <c r="C99">
-        <v>-118381.291152741</v>
+        <v>-114429.3412190836</v>
       </c>
       <c r="D99">
-        <v>53079.30384725898</v>
+        <v>57031.25378091636</v>
       </c>
       <c r="E99">
         <v>93204.595</v>
@@ -9405,37 +9533,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M99">
-        <v>38019.09222624501</v>
+        <v>35447.18330124501</v>
       </c>
       <c r="N99">
-        <v>-22726.31671604093</v>
+        <v>-20154.40779104093</v>
       </c>
       <c r="O99">
-        <v>-5681.579179010232</v>
+        <v>-5038.601947760231</v>
       </c>
       <c r="P99">
-        <v>-17044.7375370307</v>
+        <v>-15115.80584328069</v>
       </c>
       <c r="Q99">
-        <v>-13548.7375370307</v>
+        <v>-11619.80584328069</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.112865222332567</v>
+        <v>1.104002550575417</v>
       </c>
       <c r="T99">
-        <v>20.78937393188447</v>
+        <v>20.62633734208649</v>
       </c>
       <c r="U99">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.1005598412187187</v>
+        <v>0.1078560698338121</v>
       </c>
       <c r="W99">
-        <v>0.1994388176985738</v>
+        <v>0.1844388176985738</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4022393648748748</v>
+        <v>0.4314242793352485</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9582,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2286009760042189</v>
+        <v>0.2136350958515044</v>
       </c>
       <c r="C100">
-        <v>-120582.6123520242</v>
+        <v>-116655.0299162987</v>
       </c>
       <c r="D100">
-        <v>52645.61764797581</v>
+        <v>56573.20008370128</v>
       </c>
       <c r="E100">
         <v>94972.23000000001</v>
@@ -9487,37 +9615,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M100">
-        <v>38411.04163063929</v>
+        <v>35812.61818063929</v>
       </c>
       <c r="N100">
-        <v>-23118.26612043521</v>
+        <v>-20519.84267043521</v>
       </c>
       <c r="O100">
-        <v>-5779.566530108803</v>
+        <v>-5129.960667608802</v>
       </c>
       <c r="P100">
-        <v>-17338.69959032641</v>
+        <v>-15389.88200282641</v>
       </c>
       <c r="Q100">
-        <v>-13842.69959032641</v>
+        <v>-11893.88200282641</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.64639783349885</v>
+        <v>1.633103825863125</v>
       </c>
       <c r="T100">
-        <v>31.1840608978267</v>
+        <v>30.93950601312973</v>
       </c>
       <c r="U100">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.09953372038995625</v>
+        <v>0.1067554976926508</v>
       </c>
       <c r="W100">
-        <v>0.1996663462594305</v>
+        <v>0.1846663462594305</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9653,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.398134881559825</v>
+        <v>0.4270219907706031</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9664,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2303603421708443</v>
+        <v>0.2152444620181298</v>
       </c>
       <c r="C101">
-        <v>-122776.9040910105</v>
+        <v>-118873.4194061051</v>
       </c>
       <c r="D101">
-        <v>52218.96090898949</v>
+        <v>56122.4455938949</v>
       </c>
       <c r="E101">
         <v>96739.86499999999</v>
@@ -9569,37 +9697,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M101">
-        <v>38802.99103503357</v>
+        <v>36178.05306003356</v>
       </c>
       <c r="N101">
-        <v>-23510.21552482949</v>
+        <v>-20885.27754982948</v>
       </c>
       <c r="O101">
-        <v>-5877.553881207372</v>
+        <v>-5221.31938745737</v>
       </c>
       <c r="P101">
-        <v>-17632.66164362212</v>
+        <v>-15663.95816237211</v>
       </c>
       <c r="Q101">
-        <v>-14136.66164362212</v>
+        <v>-12167.95816237211</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.2469956669977</v>
+        <v>3.220407651726251</v>
       </c>
       <c r="T101">
-        <v>62.36812179565341</v>
+        <v>61.87901202625946</v>
       </c>
       <c r="U101">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V101">
-        <v>0.09852832927490619</v>
+        <v>0.105677159332119</v>
       </c>
       <c r="W101">
-        <v>0.1998892782837043</v>
+        <v>0.1848892782837043</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9735,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3941133170996248</v>
+        <v>0.4227086373284759</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/belgium/belgium_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_beverage_alcoholic.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08125543821026995</v>
+        <v>0.08113057423971329</v>
       </c>
       <c r="C2">
-        <v>166709.2961049704</v>
+        <v>165248.3463270674</v>
       </c>
       <c r="D2">
-        <v>166709.2961049704</v>
+        <v>167015.9813270674</v>
       </c>
       <c r="E2">
-        <v>-78256</v>
+        <v>-76488.36500000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1767.635</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1579,28 +1579,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>99.40581189427844</v>
       </c>
       <c r="N2">
-        <v>15292.77551020408</v>
+        <v>15193.36969830981</v>
       </c>
       <c r="O2">
-        <v>3823.193877551021</v>
+        <v>3798.342424577451</v>
       </c>
       <c r="P2">
-        <v>11469.58163265306</v>
+        <v>11395.02727373235</v>
       </c>
       <c r="Q2">
-        <v>14965.58163265306</v>
+        <v>14891.02727373235</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08125543821026995</v>
+        <v>0.08152404001489322</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905984</v>
+        <v>0.6963280330109817</v>
       </c>
       <c r="U2">
         <v>0.05623661666253409</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>153.8418651664803</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08113057423971329</v>
+        <v>0.08100571026915664</v>
       </c>
       <c r="C3">
-        <v>165248.3463270674</v>
+        <v>163788.5270100983</v>
       </c>
       <c r="D3">
-        <v>167015.9813270674</v>
+        <v>167323.7970100983</v>
       </c>
       <c r="E3">
-        <v>-76488.36500000001</v>
+        <v>-74720.73</v>
       </c>
       <c r="F3">
-        <v>1767.635</v>
+        <v>3535.27</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1661,28 +1661,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M3">
-        <v>99.40581189427844</v>
+        <v>198.8116237885569</v>
       </c>
       <c r="N3">
-        <v>15193.36969830981</v>
+        <v>15093.96388641553</v>
       </c>
       <c r="O3">
-        <v>3798.342424577451</v>
+        <v>3773.490971603881</v>
       </c>
       <c r="P3">
-        <v>11395.02727373235</v>
+        <v>11320.47291481164</v>
       </c>
       <c r="Q3">
-        <v>14891.02727373235</v>
+        <v>14816.47291481164</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08152404001489322</v>
+        <v>0.08179812348899859</v>
       </c>
       <c r="T3">
-        <v>0.6963280330109817</v>
+        <v>0.7016704300725974</v>
       </c>
       <c r="U3">
         <v>0.05623661666253409</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>153.8418651664803</v>
+        <v>76.92093258324013</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08100571026915664</v>
+        <v>0.08088084629859994</v>
       </c>
       <c r="C4">
-        <v>163788.5270100983</v>
+        <v>162329.8444160288</v>
       </c>
       <c r="D4">
-        <v>167323.7970100983</v>
+        <v>167632.7494160288</v>
       </c>
       <c r="E4">
-        <v>-74720.73</v>
+        <v>-72953.095</v>
       </c>
       <c r="F4">
-        <v>3535.27</v>
+        <v>5302.905</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1743,28 +1743,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M4">
-        <v>198.8116237885569</v>
+        <v>298.2174356828353</v>
       </c>
       <c r="N4">
-        <v>15093.96388641553</v>
+        <v>14994.55807452125</v>
       </c>
       <c r="O4">
-        <v>3773.490971603881</v>
+        <v>3748.639518630312</v>
       </c>
       <c r="P4">
-        <v>11320.47291481164</v>
+        <v>11245.91855589094</v>
       </c>
       <c r="Q4">
-        <v>14816.47291481164</v>
+        <v>14741.91855589094</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08179812348899859</v>
+        <v>0.0820778581687556</v>
       </c>
       <c r="T4">
-        <v>0.7016704300725974</v>
+        <v>0.7071229796509473</v>
       </c>
       <c r="U4">
         <v>0.05623661666253409</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>76.92093258324013</v>
+        <v>51.28062172216009</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08088084629859994</v>
+        <v>0.08075598232804329</v>
       </c>
       <c r="C5">
-        <v>162329.8444160288</v>
+        <v>160872.3048531594</v>
       </c>
       <c r="D5">
-        <v>167632.7494160288</v>
+        <v>167942.8448531594</v>
       </c>
       <c r="E5">
-        <v>-72953.095</v>
+        <v>-71185.46000000001</v>
       </c>
       <c r="F5">
-        <v>5302.905</v>
+        <v>7070.54</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1825,28 +1825,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M5">
-        <v>298.2174356828353</v>
+        <v>397.6232475771138</v>
       </c>
       <c r="N5">
-        <v>14994.55807452125</v>
+        <v>14895.15226262697</v>
       </c>
       <c r="O5">
-        <v>3748.639518630312</v>
+        <v>3723.788065656742</v>
       </c>
       <c r="P5">
-        <v>11245.91855589094</v>
+        <v>11171.36419697023</v>
       </c>
       <c r="Q5">
-        <v>14741.91855589094</v>
+        <v>14667.36419697023</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0820778581687556</v>
+        <v>0.08236342065434091</v>
       </c>
       <c r="T5">
-        <v>0.7071229796509473</v>
+        <v>0.7126891240121797</v>
       </c>
       <c r="U5">
         <v>0.05623661666253409</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.28062172216009</v>
+        <v>38.46046629162007</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08075598232804329</v>
+        <v>0.08063111835748661</v>
       </c>
       <c r="C6">
-        <v>160872.3048531594</v>
+        <v>159415.9146765548</v>
       </c>
       <c r="D6">
-        <v>167942.8448531594</v>
+        <v>168254.0896765548</v>
       </c>
       <c r="E6">
-        <v>-71185.46000000001</v>
+        <v>-69417.825</v>
       </c>
       <c r="F6">
-        <v>7070.54</v>
+        <v>8838.175000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1907,28 +1907,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M6">
-        <v>397.6232475771138</v>
+        <v>497.0290594713923</v>
       </c>
       <c r="N6">
-        <v>14895.15226262697</v>
+        <v>14795.74645073269</v>
       </c>
       <c r="O6">
-        <v>3723.788065656742</v>
+        <v>3698.936612683173</v>
       </c>
       <c r="P6">
-        <v>11171.36419697023</v>
+        <v>11096.80983804952</v>
       </c>
       <c r="Q6">
-        <v>14667.36419697023</v>
+        <v>14592.80983804952</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08236342065434091</v>
+        <v>0.08265499498172799</v>
       </c>
       <c r="T6">
-        <v>0.7126891240121797</v>
+        <v>0.7183724503599641</v>
       </c>
       <c r="U6">
         <v>0.05623661666253409</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.46046629162007</v>
+        <v>30.76837303329605</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08063111835748661</v>
+        <v>0.08050625438692993</v>
       </c>
       <c r="C7">
-        <v>159415.9146765548</v>
+        <v>157960.6802884777</v>
       </c>
       <c r="D7">
-        <v>168254.0896765548</v>
+        <v>168566.4902884777</v>
       </c>
       <c r="E7">
-        <v>-69417.825</v>
+        <v>-67650.19</v>
       </c>
       <c r="F7">
-        <v>8838.175000000001</v>
+        <v>10605.81</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1989,28 +1989,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M7">
-        <v>497.0290594713923</v>
+        <v>596.4348713656707</v>
       </c>
       <c r="N7">
-        <v>14795.74645073269</v>
+        <v>14696.34063883841</v>
       </c>
       <c r="O7">
-        <v>3698.936612683173</v>
+        <v>3674.085159709603</v>
       </c>
       <c r="P7">
-        <v>11096.80983804952</v>
+        <v>11022.25547912881</v>
       </c>
       <c r="Q7">
-        <v>14592.80983804952</v>
+        <v>14518.25547912881</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08265499498172799</v>
+        <v>0.08295277301820841</v>
       </c>
       <c r="T7">
-        <v>0.7183724503599641</v>
+        <v>0.7241766985449356</v>
       </c>
       <c r="U7">
         <v>0.05623661666253409</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.76837303329605</v>
+        <v>25.64031086108004</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08050625438692993</v>
+        <v>0.08038139041637328</v>
       </c>
       <c r="C8">
-        <v>157960.6802884777</v>
+        <v>156506.6081388284</v>
       </c>
       <c r="D8">
-        <v>168566.4902884777</v>
+        <v>168880.0531388284</v>
       </c>
       <c r="E8">
-        <v>-67650.19</v>
+        <v>-65882.55500000001</v>
       </c>
       <c r="F8">
-        <v>10605.81</v>
+        <v>12373.445</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2071,28 +2071,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M8">
-        <v>596.4348713656706</v>
+        <v>695.8406832599489</v>
       </c>
       <c r="N8">
-        <v>14696.34063883841</v>
+        <v>14596.93482694413</v>
       </c>
       <c r="O8">
-        <v>3674.085159709603</v>
+        <v>3649.233706736034</v>
       </c>
       <c r="P8">
-        <v>11022.25547912881</v>
+        <v>10947.7011202081</v>
       </c>
       <c r="Q8">
-        <v>14518.25547912881</v>
+        <v>14443.7011202081</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08295277301820841</v>
+        <v>0.08325695488343036</v>
       </c>
       <c r="T8">
-        <v>0.7241766985449356</v>
+        <v>0.7301057692715193</v>
       </c>
       <c r="U8">
         <v>0.05623661666253409</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.64031086108005</v>
+        <v>21.97740930949718</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08038139041637327</v>
+        <v>0.08025652644581661</v>
       </c>
       <c r="C9">
-        <v>156506.6081388285</v>
+        <v>155053.7047255883</v>
       </c>
       <c r="D9">
-        <v>168880.0531388285</v>
+        <v>169194.7847255883</v>
       </c>
       <c r="E9">
-        <v>-65882.55499999999</v>
+        <v>-64114.92</v>
       </c>
       <c r="F9">
-        <v>12373.445</v>
+        <v>14141.08</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2153,28 +2153,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M9">
-        <v>695.8406832599492</v>
+        <v>795.2464951542275</v>
       </c>
       <c r="N9">
-        <v>14596.93482694413</v>
+        <v>14497.52901504985</v>
       </c>
       <c r="O9">
-        <v>3649.233706736034</v>
+        <v>3624.382253762464</v>
       </c>
       <c r="P9">
-        <v>10947.7011202081</v>
+        <v>10873.14676128739</v>
       </c>
       <c r="Q9">
-        <v>14443.7011202081</v>
+        <v>14369.14676128739</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08325695488343036</v>
+        <v>0.08356774939789627</v>
       </c>
       <c r="T9">
-        <v>0.7301057692715193</v>
+        <v>0.7361637328399853</v>
       </c>
       <c r="U9">
         <v>0.05623661666253409</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.97740930949718</v>
+        <v>19.23023314581003</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08025652644581661</v>
+        <v>0.08013166247525993</v>
       </c>
       <c r="C10">
-        <v>155053.7047255883</v>
+        <v>153601.9765952687</v>
       </c>
       <c r="D10">
-        <v>169194.7847255883</v>
+        <v>169510.6915952687</v>
       </c>
       <c r="E10">
-        <v>-64114.92</v>
+        <v>-62347.285</v>
       </c>
       <c r="F10">
-        <v>14141.08</v>
+        <v>15908.715</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2235,28 +2235,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M10">
-        <v>795.2464951542275</v>
+        <v>894.6523070485059</v>
       </c>
       <c r="N10">
-        <v>14497.52901504985</v>
+        <v>14398.12320315558</v>
       </c>
       <c r="O10">
-        <v>3624.382253762464</v>
+        <v>3599.530800788894</v>
       </c>
       <c r="P10">
-        <v>10873.14676128739</v>
+        <v>10798.59240236668</v>
       </c>
       <c r="Q10">
-        <v>14369.14676128739</v>
+        <v>14294.59240236668</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08356774939789627</v>
+        <v>0.08388537456103175</v>
       </c>
       <c r="T10">
-        <v>0.7361637328399853</v>
+        <v>0.742354838464901</v>
       </c>
       <c r="U10">
         <v>0.05623661666253409</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.23023314581003</v>
+        <v>17.09354057405336</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08013166247525993</v>
+        <v>0.08000679850470327</v>
       </c>
       <c r="C11">
-        <v>153601.9765952687</v>
+        <v>152151.4303433649</v>
       </c>
       <c r="D11">
-        <v>169510.6915952687</v>
+        <v>169827.7803433649</v>
       </c>
       <c r="E11">
-        <v>-62347.285</v>
+        <v>-60579.65</v>
       </c>
       <c r="F11">
-        <v>15908.715</v>
+        <v>17676.35</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2317,28 +2317,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M11">
-        <v>894.6523070485059</v>
+        <v>994.0581189427843</v>
       </c>
       <c r="N11">
-        <v>14398.12320315558</v>
+        <v>14298.7173912613</v>
       </c>
       <c r="O11">
-        <v>3599.530800788894</v>
+        <v>3574.679347815324</v>
       </c>
       <c r="P11">
-        <v>10798.59240236668</v>
+        <v>10724.03804344597</v>
       </c>
       <c r="Q11">
-        <v>14294.59240236668</v>
+        <v>14220.03804344597</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08388537456103175</v>
+        <v>0.08421005806112579</v>
       </c>
       <c r="T11">
-        <v>0.742354838464901</v>
+        <v>0.7486835242148149</v>
       </c>
       <c r="U11">
         <v>0.05623661666253409</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.09354057405336</v>
+        <v>15.38418651664803</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08000679850470327</v>
+        <v>0.0798819345341466</v>
       </c>
       <c r="C12">
-        <v>152151.4303433649</v>
+        <v>150702.0726148151</v>
       </c>
       <c r="D12">
-        <v>169827.7803433649</v>
+        <v>170146.0576148151</v>
       </c>
       <c r="E12">
-        <v>-60579.64999999999</v>
+        <v>-58812.015</v>
       </c>
       <c r="F12">
-        <v>17676.35</v>
+        <v>19443.985</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2399,28 +2399,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M12">
-        <v>994.0581189427845</v>
+        <v>1093.463930837063</v>
       </c>
       <c r="N12">
-        <v>14298.7173912613</v>
+        <v>14199.31157936702</v>
       </c>
       <c r="O12">
-        <v>3574.679347815324</v>
+        <v>3549.827894841755</v>
       </c>
       <c r="P12">
-        <v>10724.03804344597</v>
+        <v>10649.48368452526</v>
       </c>
       <c r="Q12">
-        <v>14220.03804344597</v>
+        <v>14145.48368452526</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08421005806112579</v>
+        <v>0.08454203781964892</v>
       </c>
       <c r="T12">
-        <v>0.7486835242148149</v>
+        <v>0.7551544276220303</v>
       </c>
       <c r="U12">
         <v>0.05623661666253409</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.38418651664802</v>
+        <v>13.98562410604366</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0798819345341466</v>
+        <v>0.07975707056358994</v>
       </c>
       <c r="C13">
-        <v>150702.0726148151</v>
+        <v>149253.9101044647</v>
       </c>
       <c r="D13">
-        <v>170146.0576148151</v>
+        <v>170465.5301044647</v>
       </c>
       <c r="E13">
-        <v>-58812.015</v>
+        <v>-57044.38</v>
       </c>
       <c r="F13">
-        <v>19443.985</v>
+        <v>21211.62</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2481,28 +2481,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M13">
-        <v>1093.463930837063</v>
+        <v>1192.869742731341</v>
       </c>
       <c r="N13">
-        <v>14199.31157936702</v>
+        <v>14099.90576747274</v>
       </c>
       <c r="O13">
-        <v>3549.827894841755</v>
+        <v>3524.976441868185</v>
       </c>
       <c r="P13">
-        <v>10649.48368452526</v>
+        <v>10574.92932560456</v>
       </c>
       <c r="Q13">
-        <v>14145.48368452526</v>
+        <v>14070.92932560456</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08454203781964892</v>
+        <v>0.08488156257268394</v>
       </c>
       <c r="T13">
-        <v>0.7551544276220303</v>
+        <v>0.7617723970157733</v>
       </c>
       <c r="U13">
         <v>0.05623661666253409</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>13.98562410604366</v>
+        <v>12.82015543054002</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07975707056358994</v>
+        <v>0.07963220659303326</v>
       </c>
       <c r="C14">
-        <v>149253.9101044647</v>
+        <v>147806.9495575356</v>
       </c>
       <c r="D14">
-        <v>170465.5301044647</v>
+        <v>170786.2045575356</v>
       </c>
       <c r="E14">
-        <v>-57044.38</v>
+        <v>-55276.745</v>
       </c>
       <c r="F14">
-        <v>21211.62</v>
+        <v>22979.255</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2563,28 +2563,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M14">
-        <v>1192.869742731341</v>
+        <v>1292.27555462562</v>
       </c>
       <c r="N14">
-        <v>14099.90576747274</v>
+        <v>14000.49995557846</v>
       </c>
       <c r="O14">
-        <v>3524.976441868185</v>
+        <v>3500.124988894616</v>
       </c>
       <c r="P14">
-        <v>10574.92932560456</v>
+        <v>10500.37496668385</v>
       </c>
       <c r="Q14">
-        <v>14070.92932560456</v>
+        <v>13996.37496668385</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08488156257268394</v>
+        <v>0.08522889249245538</v>
       </c>
       <c r="T14">
-        <v>0.7617723970157733</v>
+        <v>0.7685425036369585</v>
       </c>
       <c r="U14">
         <v>0.05623661666253409</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.82015543054002</v>
+        <v>11.83398962819079</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07963220659303326</v>
+        <v>0.07950734262247659</v>
       </c>
       <c r="C15">
-        <v>147806.9495575356</v>
+        <v>146361.197770101</v>
       </c>
       <c r="D15">
-        <v>170786.2045575356</v>
+        <v>171108.087770101</v>
       </c>
       <c r="E15">
-        <v>-55276.745</v>
+        <v>-53509.11</v>
       </c>
       <c r="F15">
-        <v>22979.255</v>
+        <v>24746.89</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2645,28 +2645,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M15">
-        <v>1292.27555462562</v>
+        <v>1391.681366519898</v>
       </c>
       <c r="N15">
-        <v>14000.49995557846</v>
+        <v>13901.09414368418</v>
       </c>
       <c r="O15">
-        <v>3500.124988894616</v>
+        <v>3475.273535921046</v>
       </c>
       <c r="P15">
-        <v>10500.37496668385</v>
+        <v>10425.82060776314</v>
       </c>
       <c r="Q15">
-        <v>13996.37496668385</v>
+        <v>13921.82060776314</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08522889249245538</v>
+        <v>0.08558429985222152</v>
       </c>
       <c r="T15">
-        <v>0.7685425036369585</v>
+        <v>0.7754700545981714</v>
       </c>
       <c r="U15">
         <v>0.05623661666253409</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.83398962819079</v>
+        <v>10.98870465474859</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07950734262247659</v>
+        <v>0.07938247865191993</v>
       </c>
       <c r="C16">
-        <v>146361.197770101</v>
+        <v>144916.6615895655</v>
       </c>
       <c r="D16">
-        <v>171108.087770101</v>
+        <v>171431.1865895654</v>
       </c>
       <c r="E16">
-        <v>-53509.11</v>
+        <v>-51741.47499999999</v>
       </c>
       <c r="F16">
-        <v>24746.89</v>
+        <v>26514.52500000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2727,28 +2727,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M16">
-        <v>1391.681366519898</v>
+        <v>1491.087178414177</v>
       </c>
       <c r="N16">
-        <v>13901.09414368418</v>
+        <v>13801.68833178991</v>
       </c>
       <c r="O16">
-        <v>3475.273535921046</v>
+        <v>3450.422082947477</v>
       </c>
       <c r="P16">
-        <v>10425.82060776314</v>
+        <v>10351.26624884243</v>
       </c>
       <c r="Q16">
-        <v>13921.82060776314</v>
+        <v>13847.26624884243</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08558429985222152</v>
+        <v>0.08594806973809982</v>
       </c>
       <c r="T16">
-        <v>0.7754700545981714</v>
+        <v>0.7825606067584717</v>
       </c>
       <c r="U16">
         <v>0.05623661666253409</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.98870465474859</v>
+        <v>10.25612434443202</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07938247865191993</v>
+        <v>0.07925761468136325</v>
       </c>
       <c r="C17">
-        <v>144916.6615895655</v>
+        <v>143473.3479151504</v>
       </c>
       <c r="D17">
-        <v>171431.1865895654</v>
+        <v>171755.5079151504</v>
       </c>
       <c r="E17">
-        <v>-51741.47500000001</v>
+        <v>-49973.84</v>
       </c>
       <c r="F17">
-        <v>26514.525</v>
+        <v>28282.16</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2809,28 +2809,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M17">
-        <v>1491.087178414176</v>
+        <v>1590.492990308455</v>
       </c>
       <c r="N17">
-        <v>13801.68833178991</v>
+        <v>13702.28251989563</v>
       </c>
       <c r="O17">
-        <v>3450.422082947477</v>
+        <v>3425.570629973907</v>
       </c>
       <c r="P17">
-        <v>10351.26624884243</v>
+        <v>10276.71188992172</v>
       </c>
       <c r="Q17">
-        <v>13847.26624884243</v>
+        <v>13772.71188992172</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08594806973809982</v>
+        <v>0.08632050081173709</v>
       </c>
       <c r="T17">
-        <v>0.7825606067584717</v>
+        <v>0.7898199815892553</v>
       </c>
       <c r="U17">
         <v>0.05623661666253409</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.25612434443202</v>
+        <v>9.615116572905015</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07925761468136325</v>
+        <v>0.07913275071080658</v>
       </c>
       <c r="C18">
-        <v>143473.3479151504</v>
+        <v>142031.2636983852</v>
       </c>
       <c r="D18">
-        <v>171755.5079151504</v>
+        <v>172081.0586983852</v>
       </c>
       <c r="E18">
-        <v>-49973.84</v>
+        <v>-48206.205</v>
       </c>
       <c r="F18">
-        <v>28282.16</v>
+        <v>30049.795</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2891,28 +2891,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M18">
-        <v>1590.492990308455</v>
+        <v>1689.898802202734</v>
       </c>
       <c r="N18">
-        <v>13702.28251989563</v>
+        <v>13602.87670800135</v>
       </c>
       <c r="O18">
-        <v>3425.570629973907</v>
+        <v>3400.719177000337</v>
       </c>
       <c r="P18">
-        <v>10276.71188992172</v>
+        <v>10202.15753100101</v>
       </c>
       <c r="Q18">
-        <v>13772.71188992172</v>
+        <v>13698.15753100101</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08632050081173709</v>
+        <v>0.08670190612811264</v>
       </c>
       <c r="T18">
-        <v>0.7898199815892553</v>
+        <v>0.7972542811147567</v>
       </c>
       <c r="U18">
         <v>0.05623661666253409</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.615116572905015</v>
+        <v>9.049521480381191</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07913275071080658</v>
+        <v>0.07921038674024991</v>
       </c>
       <c r="C19">
-        <v>142031.2636983852</v>
+        <v>140061.0677154826</v>
       </c>
       <c r="D19">
-        <v>172081.0586983852</v>
+        <v>171878.4977154826</v>
       </c>
       <c r="E19">
-        <v>-48206.205</v>
+        <v>-46438.56999999999</v>
       </c>
       <c r="F19">
-        <v>30049.795</v>
+        <v>31817.43</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2973,45 +2973,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M19">
-        <v>1689.898802202734</v>
+        <v>1837.030759097012</v>
       </c>
       <c r="N19">
-        <v>13602.87670800135</v>
+        <v>13455.74475110707</v>
       </c>
       <c r="O19">
-        <v>3400.719177000337</v>
+        <v>3363.936187776768</v>
       </c>
       <c r="P19">
-        <v>10202.15753100101</v>
+        <v>10091.8085633303</v>
       </c>
       <c r="Q19">
-        <v>13698.15753100101</v>
+        <v>13587.8085633303</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08670190612811264</v>
+        <v>0.08709261401318026</v>
       </c>
       <c r="T19">
-        <v>0.7972542811147567</v>
+        <v>0.8048699050189286</v>
       </c>
       <c r="U19">
-        <v>0.05623661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04217746249690056</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.049521480381191</v>
+        <v>8.324724795419979</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07921038674024992</v>
+        <v>0.07909677276969325</v>
       </c>
       <c r="C20">
-        <v>140061.0677154825</v>
+        <v>138590.0261065706</v>
       </c>
       <c r="D20">
-        <v>171878.4977154825</v>
+        <v>172175.0911065706</v>
       </c>
       <c r="E20">
-        <v>-46438.57</v>
+        <v>-44670.935</v>
       </c>
       <c r="F20">
-        <v>31817.43</v>
+        <v>33585.065</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3055,28 +3055,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M20">
-        <v>1837.030759097012</v>
+        <v>1939.088023491291</v>
       </c>
       <c r="N20">
-        <v>13455.74475110707</v>
+        <v>13353.68748671279</v>
       </c>
       <c r="O20">
-        <v>3363.936187776768</v>
+        <v>3338.421871678198</v>
       </c>
       <c r="P20">
-        <v>10091.8085633303</v>
+        <v>10015.26561503459</v>
       </c>
       <c r="Q20">
-        <v>13587.8085633303</v>
+        <v>13511.26561503459</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08709261401318026</v>
+        <v>0.08749296900652116</v>
       </c>
       <c r="T20">
-        <v>0.8048699050189286</v>
+        <v>0.8126735690195001</v>
       </c>
       <c r="U20">
         <v>0.05773661666253409</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.32472479541998</v>
+        <v>7.886581385134717</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07909677276969325</v>
+        <v>0.07898315879913657</v>
       </c>
       <c r="C21">
-        <v>138590.0261065706</v>
+        <v>137120.0098696521</v>
       </c>
       <c r="D21">
-        <v>172175.0911065706</v>
+        <v>172472.7098696521</v>
       </c>
       <c r="E21">
-        <v>-44670.935</v>
+        <v>-42903.3</v>
       </c>
       <c r="F21">
-        <v>33585.065</v>
+        <v>35352.7</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3137,28 +3137,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M21">
-        <v>1939.088023491291</v>
+        <v>2041.145287885569</v>
       </c>
       <c r="N21">
-        <v>13353.68748671279</v>
+        <v>13251.63022231851</v>
       </c>
       <c r="O21">
-        <v>3338.421871678198</v>
+        <v>3312.907555579628</v>
       </c>
       <c r="P21">
-        <v>10015.26561503459</v>
+        <v>9938.722666738886</v>
       </c>
       <c r="Q21">
-        <v>13511.26561503459</v>
+        <v>13434.72266673889</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08749296900652116</v>
+        <v>0.08790333287469558</v>
       </c>
       <c r="T21">
-        <v>0.8126735690195001</v>
+        <v>0.8206723246200857</v>
       </c>
       <c r="U21">
         <v>0.05773661666253409</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.886581385134717</v>
+        <v>7.49225231587798</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07898315879913657</v>
+        <v>0.07886954482857991</v>
       </c>
       <c r="C22">
-        <v>137120.0098696521</v>
+        <v>135651.0243312531</v>
       </c>
       <c r="D22">
-        <v>172472.7098696521</v>
+        <v>172771.3593312531</v>
       </c>
       <c r="E22">
-        <v>-42903.3</v>
+        <v>-41135.66499999999</v>
       </c>
       <c r="F22">
-        <v>35352.7</v>
+        <v>37120.33500000001</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3219,28 +3219,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M22">
-        <v>2041.145287885569</v>
+        <v>2143.202552279848</v>
       </c>
       <c r="N22">
-        <v>13251.63022231851</v>
+        <v>13149.57295792424</v>
       </c>
       <c r="O22">
-        <v>3312.907555579628</v>
+        <v>3287.393239481059</v>
       </c>
       <c r="P22">
-        <v>9938.722666738886</v>
+        <v>9862.179718443178</v>
       </c>
       <c r="Q22">
-        <v>13434.72266673889</v>
+        <v>13358.17971844318</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08790333287469558</v>
+        <v>0.08832408570155796</v>
       </c>
       <c r="T22">
-        <v>0.8206723246200857</v>
+        <v>0.8288735803624582</v>
       </c>
       <c r="U22">
         <v>0.05773661666253409</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.49225231587798</v>
+        <v>7.135478396074268</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07886954482857991</v>
+        <v>0.07875593085802322</v>
       </c>
       <c r="C23">
-        <v>135651.0243312531</v>
+        <v>134183.0748548567</v>
       </c>
       <c r="D23">
-        <v>172771.3593312531</v>
+        <v>173071.0448548567</v>
       </c>
       <c r="E23">
-        <v>-41135.665</v>
+        <v>-39368.03</v>
       </c>
       <c r="F23">
-        <v>37120.335</v>
+        <v>38887.97</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3301,28 +3301,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M23">
-        <v>2143.202552279847</v>
+        <v>2245.259816674126</v>
       </c>
       <c r="N23">
-        <v>13149.57295792424</v>
+        <v>13047.51569352996</v>
       </c>
       <c r="O23">
-        <v>3287.393239481059</v>
+        <v>3261.878923382489</v>
       </c>
       <c r="P23">
-        <v>9862.179718443178</v>
+        <v>9785.636770147466</v>
       </c>
       <c r="Q23">
-        <v>13358.17971844318</v>
+        <v>13281.63677014747</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08832408570155796</v>
+        <v>0.08875562706244244</v>
       </c>
       <c r="T23">
-        <v>0.8288735803624582</v>
+        <v>0.8372851247136095</v>
       </c>
       <c r="U23">
         <v>0.05773661666253409</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.135478396074268</v>
+        <v>6.811138468979983</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07875593085802322</v>
+        <v>0.07893556688746656</v>
       </c>
       <c r="C24">
-        <v>134183.0748548567</v>
+        <v>131942.0807965528</v>
       </c>
       <c r="D24">
-        <v>173071.0448548567</v>
+        <v>172597.6857965528</v>
       </c>
       <c r="E24">
-        <v>-39368.03</v>
+        <v>-37600.395</v>
       </c>
       <c r="F24">
-        <v>38887.97</v>
+        <v>40655.605</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3383,45 +3383,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M24">
-        <v>2245.259816674126</v>
+        <v>2416.431609568404</v>
       </c>
       <c r="N24">
-        <v>13047.51569352996</v>
+        <v>12876.34390063568</v>
       </c>
       <c r="O24">
-        <v>3261.878923382489</v>
+        <v>3219.08597515892</v>
       </c>
       <c r="P24">
-        <v>9785.636770147466</v>
+        <v>9657.257925476759</v>
       </c>
       <c r="Q24">
-        <v>13281.63677014747</v>
+        <v>13153.25792547676</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08875562706244244</v>
+        <v>0.08919837728984342</v>
       </c>
       <c r="T24">
-        <v>0.8372851247136095</v>
+        <v>0.8459151507362195</v>
       </c>
       <c r="U24">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04330246249690056</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.811138468979983</v>
+        <v>6.328660595917095</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07893556688746656</v>
+        <v>0.07883470291690992</v>
       </c>
       <c r="C25">
-        <v>131942.0807965528</v>
+        <v>130439.913272642</v>
       </c>
       <c r="D25">
-        <v>172597.6857965528</v>
+        <v>172863.153272642</v>
       </c>
       <c r="E25">
-        <v>-37600.395</v>
+        <v>-35832.75999999999</v>
       </c>
       <c r="F25">
-        <v>40655.605</v>
+        <v>42423.24000000001</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3465,28 +3465,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M25">
-        <v>2416.431609568404</v>
+        <v>2521.493853462683</v>
       </c>
       <c r="N25">
-        <v>12876.34390063568</v>
+        <v>12771.2816567414</v>
       </c>
       <c r="O25">
-        <v>3219.08597515892</v>
+        <v>3192.82041418535</v>
       </c>
       <c r="P25">
-        <v>9657.257925476759</v>
+        <v>9578.46124255605</v>
       </c>
       <c r="Q25">
-        <v>13153.25792547676</v>
+        <v>13074.46124255605</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08919837728984342</v>
+        <v>0.08965277883901812</v>
       </c>
       <c r="T25">
-        <v>0.8459151507362195</v>
+        <v>0.8547722827067928</v>
       </c>
       <c r="U25">
         <v>0.05943661666253409</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.328660595917095</v>
+        <v>6.064966404420549</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0788347029169099</v>
+        <v>0.07873383894635323</v>
       </c>
       <c r="C26">
-        <v>130439.9132726421</v>
+        <v>128938.5636222729</v>
       </c>
       <c r="D26">
-        <v>172863.1532726421</v>
+        <v>173129.4386222729</v>
       </c>
       <c r="E26">
-        <v>-35832.76</v>
+        <v>-34065.125</v>
       </c>
       <c r="F26">
-        <v>42423.24</v>
+        <v>44190.875</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3547,28 +3547,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M26">
-        <v>2521.493853462683</v>
+        <v>2626.556097356961</v>
       </c>
       <c r="N26">
-        <v>12771.2816567414</v>
+        <v>12666.21941284712</v>
       </c>
       <c r="O26">
-        <v>3192.82041418535</v>
+        <v>3166.55485321178</v>
       </c>
       <c r="P26">
-        <v>9578.461242556052</v>
+        <v>9499.664559635341</v>
       </c>
       <c r="Q26">
-        <v>13074.46124255605</v>
+        <v>12995.66455963534</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08965277883901812</v>
+        <v>0.09011929776283745</v>
       </c>
       <c r="T26">
-        <v>0.8547722827067928</v>
+        <v>0.863865604863248</v>
       </c>
       <c r="U26">
         <v>0.05943661666253409</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.06496640442055</v>
+        <v>5.822367748243728</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07873383894635323</v>
+        <v>0.07863297497579656</v>
       </c>
       <c r="C27">
-        <v>128938.5636222729</v>
+        <v>127438.0356309325</v>
       </c>
       <c r="D27">
-        <v>173129.4386222729</v>
+        <v>173396.5456309325</v>
       </c>
       <c r="E27">
-        <v>-34065.125</v>
+        <v>-32297.49</v>
       </c>
       <c r="F27">
-        <v>44190.875</v>
+        <v>45958.51</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3629,28 +3629,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M27">
-        <v>2626.556097356961</v>
+        <v>2731.61834125124</v>
       </c>
       <c r="N27">
-        <v>12666.21941284712</v>
+        <v>12561.15716895284</v>
       </c>
       <c r="O27">
-        <v>3166.55485321178</v>
+        <v>3140.289292238211</v>
       </c>
       <c r="P27">
-        <v>9499.664559635341</v>
+        <v>9420.867876714632</v>
       </c>
       <c r="Q27">
-        <v>12995.66455963534</v>
+        <v>12916.86787671463</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09011929776283745</v>
+        <v>0.09059842530621948</v>
       </c>
       <c r="T27">
-        <v>0.863865604863248</v>
+        <v>0.8732046924833913</v>
       </c>
       <c r="U27">
         <v>0.05943661666253409</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.822367748243728</v>
+        <v>5.59843052715743</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07863297497579656</v>
+        <v>0.07869411100523989</v>
       </c>
       <c r="C28">
-        <v>127438.0356309325</v>
+        <v>125508.4024872746</v>
       </c>
       <c r="D28">
-        <v>173396.5456309325</v>
+        <v>173234.5474872746</v>
       </c>
       <c r="E28">
-        <v>-32297.49</v>
+        <v>-30529.855</v>
       </c>
       <c r="F28">
-        <v>45958.51</v>
+        <v>47726.145</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3711,45 +3711,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M28">
-        <v>2731.61834125124</v>
+        <v>2874.861501145518</v>
       </c>
       <c r="N28">
-        <v>12561.15716895284</v>
+        <v>12417.91400905856</v>
       </c>
       <c r="O28">
-        <v>3140.289292238211</v>
+        <v>3104.478502264641</v>
       </c>
       <c r="P28">
-        <v>9420.867876714632</v>
+        <v>9313.435506793923</v>
       </c>
       <c r="Q28">
-        <v>12916.86787671463</v>
+        <v>12809.43550679392</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09059842530621948</v>
+        <v>0.09109067963161198</v>
       </c>
       <c r="T28">
-        <v>0.8732046924833913</v>
+        <v>0.882799645517785</v>
       </c>
       <c r="U28">
-        <v>0.05943661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04457746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>5.59843052715743</v>
+        <v>5.319482522587791</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07869411100523989</v>
+        <v>0.07859924703468323</v>
       </c>
       <c r="C29">
-        <v>125508.4024872746</v>
+        <v>123992.2676198721</v>
       </c>
       <c r="D29">
-        <v>173234.5474872746</v>
+        <v>173486.0476198721</v>
       </c>
       <c r="E29">
-        <v>-30529.855</v>
+        <v>-28762.21999999999</v>
       </c>
       <c r="F29">
-        <v>47726.145</v>
+        <v>49493.78000000001</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3793,28 +3793,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M29">
-        <v>2874.861501145518</v>
+        <v>2981.337853039797</v>
       </c>
       <c r="N29">
-        <v>12417.91400905856</v>
+        <v>12311.43765716429</v>
       </c>
       <c r="O29">
-        <v>3104.478502264641</v>
+        <v>3077.859414291072</v>
       </c>
       <c r="P29">
-        <v>9313.435506793923</v>
+        <v>9233.578242873215</v>
       </c>
       <c r="Q29">
-        <v>12809.43550679392</v>
+        <v>12729.57824287321</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09109067963161198</v>
+        <v>0.09159660768826537</v>
       </c>
       <c r="T29">
-        <v>0.882799645517785</v>
+        <v>0.8926611250253563</v>
       </c>
       <c r="U29">
         <v>0.06023661666253409</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.319482522587791</v>
+        <v>5.129501003923941</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07859924703468323</v>
+        <v>0.07850438306412655</v>
       </c>
       <c r="C30">
-        <v>123992.2676198721</v>
+        <v>122476.8640647879</v>
       </c>
       <c r="D30">
-        <v>173486.0476198721</v>
+        <v>173738.2790647879</v>
       </c>
       <c r="E30">
-        <v>-28762.21999999999</v>
+        <v>-26994.58499999999</v>
       </c>
       <c r="F30">
-        <v>49493.78000000001</v>
+        <v>51261.41500000001</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3875,28 +3875,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M30">
-        <v>2981.337853039797</v>
+        <v>3087.814204934075</v>
       </c>
       <c r="N30">
-        <v>12311.43765716429</v>
+        <v>12204.96130527001</v>
       </c>
       <c r="O30">
-        <v>3077.859414291072</v>
+        <v>3051.240326317502</v>
       </c>
       <c r="P30">
-        <v>9233.578242873215</v>
+        <v>9153.720978952506</v>
       </c>
       <c r="Q30">
-        <v>12729.57824287321</v>
+        <v>12649.72097895251</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09159660768826537</v>
+        <v>0.09211678723947238</v>
       </c>
       <c r="T30">
-        <v>0.8926611250253563</v>
+        <v>0.9028003926880704</v>
       </c>
       <c r="U30">
         <v>0.06023661666253409</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.129501003923941</v>
+        <v>4.952621658961046</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07850438306412655</v>
+        <v>0.07840951909356988</v>
       </c>
       <c r="C31">
-        <v>122476.8640647879</v>
+        <v>120962.1950164324</v>
       </c>
       <c r="D31">
-        <v>173738.2790647879</v>
+        <v>173991.2450164324</v>
       </c>
       <c r="E31">
-        <v>-26994.58500000001</v>
+        <v>-25226.95</v>
       </c>
       <c r="F31">
-        <v>51261.41499999999</v>
+        <v>53029.05</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3957,28 +3957,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M31">
-        <v>3087.814204934074</v>
+        <v>3194.290556828353</v>
       </c>
       <c r="N31">
-        <v>12204.96130527001</v>
+        <v>12098.48495337573</v>
       </c>
       <c r="O31">
-        <v>3051.240326317502</v>
+        <v>3024.621238343932</v>
       </c>
       <c r="P31">
-        <v>9153.720978952506</v>
+        <v>9073.863715031797</v>
       </c>
       <c r="Q31">
-        <v>12649.72097895251</v>
+        <v>12569.8637150318</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09211678723947238</v>
+        <v>0.09265182906357103</v>
       </c>
       <c r="T31">
-        <v>0.9028003926880704</v>
+        <v>0.9132293537125764</v>
       </c>
       <c r="U31">
         <v>0.06023661666253409</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.952621658961046</v>
+        <v>4.787534270329012</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07840951909356988</v>
+        <v>0.07831465512301321</v>
       </c>
       <c r="C32">
-        <v>120962.1950164324</v>
+        <v>119448.2636878474</v>
       </c>
       <c r="D32">
-        <v>173991.2450164324</v>
+        <v>174244.9486878474</v>
       </c>
       <c r="E32">
-        <v>-25226.95</v>
+        <v>-23459.315</v>
       </c>
       <c r="F32">
-        <v>53029.05</v>
+        <v>54796.685</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4039,28 +4039,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M32">
-        <v>3194.290556828353</v>
+        <v>3300.766908722632</v>
       </c>
       <c r="N32">
-        <v>12098.48495337573</v>
+        <v>11992.00860148145</v>
       </c>
       <c r="O32">
-        <v>3024.621238343932</v>
+        <v>2998.002150370363</v>
       </c>
       <c r="P32">
-        <v>9073.863715031797</v>
+        <v>8994.006451111089</v>
       </c>
       <c r="Q32">
-        <v>12569.8637150318</v>
+        <v>12490.00645111109</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09265182906357103</v>
+        <v>0.09320237934633918</v>
       </c>
       <c r="T32">
-        <v>0.9132293537125764</v>
+        <v>0.9239606034624305</v>
       </c>
       <c r="U32">
         <v>0.06023661666253409</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.787534270329012</v>
+        <v>4.63309768096356</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07831465512301321</v>
+        <v>0.07821979115245654</v>
       </c>
       <c r="C33">
-        <v>119448.2636878474</v>
+        <v>117935.0733108424</v>
       </c>
       <c r="D33">
-        <v>174244.9486878474</v>
+        <v>174499.3933108425</v>
       </c>
       <c r="E33">
-        <v>-23459.315</v>
+        <v>-21691.68</v>
       </c>
       <c r="F33">
-        <v>54796.685</v>
+        <v>56564.32</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4121,28 +4121,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M33">
-        <v>3300.766908722632</v>
+        <v>3407.24326061691</v>
       </c>
       <c r="N33">
-        <v>11992.00860148145</v>
+        <v>11885.53224958717</v>
       </c>
       <c r="O33">
-        <v>2998.002150370363</v>
+        <v>2971.383062396793</v>
       </c>
       <c r="P33">
-        <v>8994.006451111089</v>
+        <v>8914.14918719038</v>
       </c>
       <c r="Q33">
-        <v>12490.00645111109</v>
+        <v>12410.14918719038</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09320237934633918</v>
+        <v>0.09376912228448289</v>
       </c>
       <c r="T33">
-        <v>0.9239606034624305</v>
+        <v>0.9350074782049274</v>
       </c>
       <c r="U33">
         <v>0.06023661666253409</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.63309768096356</v>
+        <v>4.488313378433448</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07821979115245654</v>
+        <v>0.07812492718189987</v>
       </c>
       <c r="C34">
-        <v>117935.0733108424</v>
+        <v>116422.627136132</v>
       </c>
       <c r="D34">
-        <v>174499.3933108425</v>
+        <v>174754.582136132</v>
       </c>
       <c r="E34">
-        <v>-21691.68</v>
+        <v>-19924.045</v>
       </c>
       <c r="F34">
-        <v>56564.32</v>
+        <v>58331.955</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4203,28 +4203,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M34">
-        <v>3407.24326061691</v>
+        <v>3513.719612511189</v>
       </c>
       <c r="N34">
-        <v>11885.53224958717</v>
+        <v>11779.0558976929</v>
       </c>
       <c r="O34">
-        <v>2971.383062396793</v>
+        <v>2944.763974423224</v>
       </c>
       <c r="P34">
-        <v>8914.14918719038</v>
+        <v>8834.291923269671</v>
       </c>
       <c r="Q34">
-        <v>12410.14918719038</v>
+        <v>12330.29192326967</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09376912228448289</v>
+        <v>0.09435278292227267</v>
       </c>
       <c r="T34">
-        <v>0.9350074782049274</v>
+        <v>0.946384110402424</v>
       </c>
       <c r="U34">
         <v>0.06023661666253409</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.488313378433448</v>
+        <v>4.352303882117283</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07812492718189987</v>
+        <v>0.07828506321134319</v>
       </c>
       <c r="C35">
-        <v>116422.627136132</v>
+        <v>114224.650594683</v>
       </c>
       <c r="D35">
-        <v>174754.582136132</v>
+        <v>174324.240594683</v>
       </c>
       <c r="E35">
-        <v>-19924.045</v>
+        <v>-18156.41</v>
       </c>
       <c r="F35">
-        <v>58331.955</v>
+        <v>60099.59</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4285,45 +4285,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M35">
-        <v>3513.719612511189</v>
+        <v>3680.295554405468</v>
       </c>
       <c r="N35">
-        <v>11779.0558976929</v>
+        <v>11612.47995579862</v>
       </c>
       <c r="O35">
-        <v>2944.763974423224</v>
+        <v>2903.119988949654</v>
       </c>
       <c r="P35">
-        <v>8834.291923269671</v>
+        <v>8709.359966848962</v>
       </c>
       <c r="Q35">
-        <v>12330.29192326967</v>
+        <v>12205.35996684896</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09435278292227267</v>
+        <v>0.09495413024605609</v>
       </c>
       <c r="T35">
-        <v>0.946384110402424</v>
+        <v>0.9581054890301479</v>
       </c>
       <c r="U35">
-        <v>0.06023661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04517746249690056</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.352303882117283</v>
+        <v>4.15531179062453</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07828506321134319</v>
+        <v>0.07819769924078654</v>
       </c>
       <c r="C36">
-        <v>114224.650594683</v>
+        <v>112691.530063716</v>
       </c>
       <c r="D36">
-        <v>174324.240594683</v>
+        <v>174558.755063716</v>
       </c>
       <c r="E36">
-        <v>-18156.41</v>
+        <v>-16388.77499999999</v>
       </c>
       <c r="F36">
-        <v>60099.59</v>
+        <v>61867.22500000001</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4367,28 +4367,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M36">
-        <v>3680.295554405468</v>
+        <v>3788.539541299746</v>
       </c>
       <c r="N36">
-        <v>11612.47995579862</v>
+        <v>11504.23596890434</v>
       </c>
       <c r="O36">
-        <v>2903.119988949654</v>
+        <v>2876.058992226084</v>
       </c>
       <c r="P36">
-        <v>8709.359966848962</v>
+        <v>8628.176976678253</v>
       </c>
       <c r="Q36">
-        <v>12205.35996684896</v>
+        <v>12124.17697667825</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09495413024605609</v>
+        <v>0.09557398056441746</v>
       </c>
       <c r="T36">
-        <v>0.9581054890301479</v>
+        <v>0.9701875254618016</v>
       </c>
       <c r="U36">
         <v>0.06123661666253409</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.15531179062453</v>
+        <v>4.036588596606687</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07819769924078654</v>
+        <v>0.07811033527022987</v>
       </c>
       <c r="C37">
-        <v>112691.530063716</v>
+        <v>111159.0413567792</v>
       </c>
       <c r="D37">
-        <v>174558.755063716</v>
+        <v>174793.9013567792</v>
       </c>
       <c r="E37">
-        <v>-16388.77499999999</v>
+        <v>-14621.13999999999</v>
       </c>
       <c r="F37">
-        <v>61867.22500000001</v>
+        <v>63634.86000000001</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4449,28 +4449,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M37">
-        <v>3788.539541299746</v>
+        <v>3896.783528194025</v>
       </c>
       <c r="N37">
-        <v>11504.23596890434</v>
+        <v>11395.99198201006</v>
       </c>
       <c r="O37">
-        <v>2876.058992226084</v>
+        <v>2848.997995502515</v>
       </c>
       <c r="P37">
-        <v>8628.176976678253</v>
+        <v>8546.993986507543</v>
       </c>
       <c r="Q37">
-        <v>12124.17697667825</v>
+        <v>12042.99398650754</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09557398056441746</v>
+        <v>0.09621320120522761</v>
       </c>
       <c r="T37">
-        <v>0.9701875254618016</v>
+        <v>0.9826471255319447</v>
       </c>
       <c r="U37">
         <v>0.06123661666253409</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.036588596606687</v>
+        <v>3.924461135589834</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07811033527022987</v>
+        <v>0.0780229712996732</v>
       </c>
       <c r="C38">
-        <v>111159.0413567792</v>
+        <v>109627.1870306877</v>
       </c>
       <c r="D38">
-        <v>174793.9013567792</v>
+        <v>175029.6820306877</v>
       </c>
       <c r="E38">
-        <v>-14621.14</v>
+        <v>-12853.505</v>
       </c>
       <c r="F38">
-        <v>63634.86</v>
+        <v>65402.495</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4531,28 +4531,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M38">
-        <v>3896.783528194024</v>
+        <v>4005.027515088303</v>
       </c>
       <c r="N38">
-        <v>11395.99198201006</v>
+        <v>11287.74799511578</v>
       </c>
       <c r="O38">
-        <v>2848.997995502515</v>
+        <v>2821.936998778945</v>
       </c>
       <c r="P38">
-        <v>8546.993986507543</v>
+        <v>8465.810996336835</v>
       </c>
       <c r="Q38">
-        <v>12042.99398650754</v>
+        <v>11961.81099633684</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09621320120522761</v>
+        <v>0.09687271456479363</v>
       </c>
       <c r="T38">
-        <v>0.9826471255319447</v>
+        <v>0.9955022684614572</v>
       </c>
       <c r="U38">
         <v>0.06123661666253409</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.924461135589834</v>
+        <v>3.818394618411731</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0780229712996732</v>
+        <v>0.07793560732911653</v>
       </c>
       <c r="C39">
-        <v>109627.1870306877</v>
+        <v>108095.9696560708</v>
       </c>
       <c r="D39">
-        <v>175029.6820306877</v>
+        <v>175266.0996560708</v>
       </c>
       <c r="E39">
-        <v>-12853.505</v>
+        <v>-11085.87</v>
       </c>
       <c r="F39">
-        <v>65402.495</v>
+        <v>67170.13</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4613,28 +4613,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M39">
-        <v>4005.027515088303</v>
+        <v>4113.271501982581</v>
       </c>
       <c r="N39">
-        <v>11287.74799511578</v>
+        <v>11179.5040082215</v>
       </c>
       <c r="O39">
-        <v>2821.936998778945</v>
+        <v>2794.876002055375</v>
       </c>
       <c r="P39">
-        <v>8465.810996336835</v>
+        <v>8384.628006166127</v>
       </c>
       <c r="Q39">
-        <v>11961.81099633684</v>
+        <v>11880.62800616613</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09687271456479363</v>
+        <v>0.0975535025488618</v>
       </c>
       <c r="T39">
-        <v>0.9955022684614572</v>
+        <v>1.008772093420954</v>
       </c>
       <c r="U39">
         <v>0.06123661666253409</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.818394618411731</v>
+        <v>3.71791054950616</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07793560732911653</v>
+        <v>0.07784824335855986</v>
       </c>
       <c r="C40">
-        <v>108095.9696560708</v>
+        <v>106565.3918174656</v>
       </c>
       <c r="D40">
-        <v>175266.0996560708</v>
+        <v>175503.1568174656</v>
       </c>
       <c r="E40">
-        <v>-11085.87</v>
+        <v>-9318.235000000001</v>
       </c>
       <c r="F40">
-        <v>67170.13</v>
+        <v>68937.765</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4695,28 +4695,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M40">
-        <v>4113.271501982581</v>
+        <v>4221.515488876859</v>
       </c>
       <c r="N40">
-        <v>11179.5040082215</v>
+        <v>11071.26002132722</v>
       </c>
       <c r="O40">
-        <v>2794.876002055375</v>
+        <v>2767.815005331806</v>
       </c>
       <c r="P40">
-        <v>8384.628006166127</v>
+        <v>8303.445015995418</v>
       </c>
       <c r="Q40">
-        <v>11880.62800616613</v>
+        <v>11799.44501599542</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0975535025488618</v>
+        <v>0.0982566114504404</v>
       </c>
       <c r="T40">
-        <v>1.008772093420954</v>
+        <v>1.022476994608631</v>
       </c>
       <c r="U40">
         <v>0.06123661666253409</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.71791054950616</v>
+        <v>3.622579509775232</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07784824335855986</v>
+        <v>0.07776087938800319</v>
       </c>
       <c r="C41">
-        <v>106565.3918174656</v>
+        <v>105035.4561134109</v>
       </c>
       <c r="D41">
-        <v>175503.1568174656</v>
+        <v>175740.8561134109</v>
       </c>
       <c r="E41">
-        <v>-9318.235000000001</v>
+        <v>-7550.599999999991</v>
       </c>
       <c r="F41">
-        <v>68937.765</v>
+        <v>70705.40000000001</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4777,28 +4777,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M41">
-        <v>4221.515488876859</v>
+        <v>4329.759475771139</v>
       </c>
       <c r="N41">
-        <v>11071.26002132722</v>
+        <v>10963.01603443295</v>
       </c>
       <c r="O41">
-        <v>2767.815005331806</v>
+        <v>2740.754008608236</v>
       </c>
       <c r="P41">
-        <v>8303.445015995418</v>
+        <v>8222.262025824708</v>
       </c>
       <c r="Q41">
-        <v>11799.44501599542</v>
+        <v>11718.26202582471</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0982566114504404</v>
+        <v>0.09898315731540494</v>
       </c>
       <c r="T41">
-        <v>1.022476994608631</v>
+        <v>1.036638725835898</v>
       </c>
       <c r="U41">
         <v>0.06123661666253409</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.622579509775232</v>
+        <v>3.532015022030851</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07776087938800319</v>
+        <v>0.07767351541744652</v>
       </c>
       <c r="C42">
-        <v>105035.4561134109</v>
+        <v>103506.1651565425</v>
       </c>
       <c r="D42">
-        <v>175740.8561134109</v>
+        <v>175979.2001565425</v>
       </c>
       <c r="E42">
-        <v>-7550.599999999991</v>
+        <v>-5782.964999999997</v>
       </c>
       <c r="F42">
-        <v>70705.40000000001</v>
+        <v>72473.035</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4859,28 +4859,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M42">
-        <v>4329.759475771139</v>
+        <v>4438.003462665417</v>
       </c>
       <c r="N42">
-        <v>10963.01603443295</v>
+        <v>10854.77204753867</v>
       </c>
       <c r="O42">
-        <v>2740.754008608236</v>
+        <v>2713.693011884667</v>
       </c>
       <c r="P42">
-        <v>8222.262025824708</v>
+        <v>8141.079035654</v>
       </c>
       <c r="Q42">
-        <v>11718.26202582471</v>
+        <v>11637.079035654</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09898315731540494</v>
+        <v>0.09973433185375813</v>
       </c>
       <c r="T42">
-        <v>1.036638725835898</v>
+        <v>1.051280515748834</v>
       </c>
       <c r="U42">
         <v>0.06123661666253409</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.532015022030851</v>
+        <v>3.44586831417644</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07767351541744652</v>
+        <v>0.07758615144688985</v>
       </c>
       <c r="C43">
-        <v>103506.1651565425</v>
+        <v>101977.5215736885</v>
       </c>
       <c r="D43">
-        <v>175979.2001565425</v>
+        <v>176218.1915736886</v>
       </c>
       <c r="E43">
-        <v>-5782.964999999997</v>
+        <v>-4015.329999999987</v>
       </c>
       <c r="F43">
-        <v>72473.035</v>
+        <v>74240.67000000001</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4941,28 +4941,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M43">
-        <v>4438.003462665417</v>
+        <v>4546.247449559695</v>
       </c>
       <c r="N43">
-        <v>10854.77204753867</v>
+        <v>10746.52806064439</v>
       </c>
       <c r="O43">
-        <v>2713.693011884667</v>
+        <v>2686.632015161097</v>
       </c>
       <c r="P43">
-        <v>8141.079035654</v>
+        <v>8059.896045483291</v>
       </c>
       <c r="Q43">
-        <v>11637.079035654</v>
+        <v>11555.89604548329</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09973433185375813</v>
+        <v>0.1005114089623994</v>
       </c>
       <c r="T43">
-        <v>1.051280515748834</v>
+        <v>1.066427194969113</v>
       </c>
       <c r="U43">
         <v>0.06123661666253409</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.44586831417644</v>
+        <v>3.363823830505572</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07758615144688986</v>
+        <v>0.07749878747633318</v>
       </c>
       <c r="C44">
-        <v>101977.5215736885</v>
+        <v>100449.5280059664</v>
       </c>
       <c r="D44">
-        <v>176218.1915736885</v>
+        <v>176457.8330059664</v>
       </c>
       <c r="E44">
-        <v>-4015.330000000002</v>
+        <v>-2247.695000000007</v>
       </c>
       <c r="F44">
-        <v>74240.67</v>
+        <v>76008.30499999999</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -5023,28 +5023,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M44">
-        <v>4546.247449559694</v>
+        <v>4654.491436453973</v>
       </c>
       <c r="N44">
-        <v>10746.52806064439</v>
+        <v>10638.28407375011</v>
       </c>
       <c r="O44">
-        <v>2686.632015161097</v>
+        <v>2659.571018437528</v>
       </c>
       <c r="P44">
-        <v>8059.896045483291</v>
+        <v>7978.713055312583</v>
       </c>
       <c r="Q44">
-        <v>11555.89604548329</v>
+        <v>11474.71305531258</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1005114089623994</v>
+        <v>0.1013157519345017</v>
       </c>
       <c r="T44">
-        <v>1.066427194969113</v>
+        <v>1.082105336618174</v>
       </c>
       <c r="U44">
         <v>0.06123661666253409</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.363823830505573</v>
+        <v>3.285595369331025</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07749878747633318</v>
+        <v>0.07741142350577652</v>
       </c>
       <c r="C45">
-        <v>100449.5280059664</v>
+        <v>98922.18710887953</v>
       </c>
       <c r="D45">
-        <v>176457.8330059664</v>
+        <v>176698.1271088795</v>
       </c>
       <c r="E45">
-        <v>-2247.695000000007</v>
+        <v>-480.0599999999977</v>
       </c>
       <c r="F45">
-        <v>76008.30499999999</v>
+        <v>77775.94</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -5105,28 +5105,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M45">
-        <v>4654.491436453973</v>
+        <v>4762.735423348252</v>
       </c>
       <c r="N45">
-        <v>10638.28407375011</v>
+        <v>10530.04008685583</v>
       </c>
       <c r="O45">
-        <v>2659.571018437528</v>
+        <v>2632.510021713958</v>
       </c>
       <c r="P45">
-        <v>7978.713055312583</v>
+        <v>7897.530065141874</v>
       </c>
       <c r="Q45">
-        <v>11474.71305531258</v>
+        <v>11393.53006514187</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1013157519345017</v>
+        <v>0.1021488214413219</v>
       </c>
       <c r="T45">
-        <v>1.082105336618174</v>
+        <v>1.098343411897558</v>
       </c>
       <c r="U45">
         <v>0.06123661666253409</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.285595369331025</v>
+        <v>3.210922747300774</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07741142350577652</v>
+        <v>0.07732405953521986</v>
       </c>
       <c r="C46">
-        <v>98922.18710887953</v>
+        <v>97395.50155241606</v>
       </c>
       <c r="D46">
-        <v>176698.1271088795</v>
+        <v>176939.0765524161</v>
       </c>
       <c r="E46">
-        <v>-480.0599999999977</v>
+        <v>1287.574999999997</v>
       </c>
       <c r="F46">
-        <v>77775.94</v>
+        <v>79543.575</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5187,28 +5187,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M46">
-        <v>4762.735423348252</v>
+        <v>4870.97941024253</v>
       </c>
       <c r="N46">
-        <v>10530.04008685583</v>
+        <v>10421.79609996155</v>
       </c>
       <c r="O46">
-        <v>2632.510021713958</v>
+        <v>2605.449024990388</v>
       </c>
       <c r="P46">
-        <v>7897.530065141874</v>
+        <v>7816.347074971165</v>
       </c>
       <c r="Q46">
-        <v>11393.53006514187</v>
+        <v>11312.34707497117</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1021488214413219</v>
+        <v>0.1030121843847538</v>
       </c>
       <c r="T46">
-        <v>1.098343411897558</v>
+        <v>1.115171962641647</v>
       </c>
       <c r="U46">
         <v>0.06123661666253409</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.210922747300774</v>
+        <v>3.139568908471868</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07732405953521986</v>
+        <v>0.07723669556466317</v>
       </c>
       <c r="C47">
-        <v>97395.50155241606</v>
+        <v>95869.47402114728</v>
       </c>
       <c r="D47">
-        <v>176939.0765524161</v>
+        <v>177180.6840211473</v>
       </c>
       <c r="E47">
-        <v>1287.574999999997</v>
+        <v>3055.210000000006</v>
       </c>
       <c r="F47">
-        <v>79543.575</v>
+        <v>81311.21000000001</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5269,28 +5269,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M47">
-        <v>4870.97941024253</v>
+        <v>4979.223397136809</v>
       </c>
       <c r="N47">
-        <v>10421.79609996155</v>
+        <v>10313.55211306728</v>
       </c>
       <c r="O47">
-        <v>2605.449024990388</v>
+        <v>2578.388028266819</v>
       </c>
       <c r="P47">
-        <v>7816.347074971165</v>
+        <v>7735.164084800456</v>
       </c>
       <c r="Q47">
-        <v>11312.34707497117</v>
+        <v>11231.16408480046</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1030121843847538</v>
+        <v>0.103907523733498</v>
       </c>
       <c r="T47">
-        <v>1.115171962641647</v>
+        <v>1.132623793042925</v>
       </c>
       <c r="U47">
         <v>0.06123661666253409</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.139568908471868</v>
+        <v>3.07131741046161</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07723669556466317</v>
+        <v>0.07714933159410652</v>
       </c>
       <c r="C48">
-        <v>95869.47402114728</v>
+        <v>94344.10721432744</v>
       </c>
       <c r="D48">
-        <v>177180.6840211473</v>
+        <v>177422.9522143274</v>
       </c>
       <c r="E48">
-        <v>3055.210000000006</v>
+        <v>4822.845000000001</v>
       </c>
       <c r="F48">
-        <v>81311.21000000001</v>
+        <v>83078.845</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5351,28 +5351,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M48">
-        <v>4979.223397136809</v>
+        <v>5087.467384031087</v>
       </c>
       <c r="N48">
-        <v>10313.55211306728</v>
+        <v>10205.308126173</v>
       </c>
       <c r="O48">
-        <v>2578.388028266819</v>
+        <v>2551.327031543249</v>
       </c>
       <c r="P48">
-        <v>7735.164084800456</v>
+        <v>7653.981094629748</v>
       </c>
       <c r="Q48">
-        <v>11231.16408480046</v>
+        <v>11149.98109462975</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.103907523733498</v>
+        <v>0.1048366494727608</v>
       </c>
       <c r="T48">
-        <v>1.132623793042925</v>
+        <v>1.150734183081987</v>
       </c>
       <c r="U48">
         <v>0.06123661666253409</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.07131741046161</v>
+        <v>3.005970231515618</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07714933159410652</v>
+        <v>0.07796196762354984</v>
       </c>
       <c r="C49">
-        <v>94344.10721432744</v>
+        <v>90348.21821133347</v>
       </c>
       <c r="D49">
-        <v>177422.9522143274</v>
+        <v>175194.6982113335</v>
       </c>
       <c r="E49">
-        <v>4822.845000000001</v>
+        <v>6590.48000000001</v>
       </c>
       <c r="F49">
-        <v>83078.845</v>
+        <v>84846.48000000001</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5433,45 +5433,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M49">
-        <v>5087.467384031087</v>
+        <v>5407.827570925367</v>
       </c>
       <c r="N49">
-        <v>10205.308126173</v>
+        <v>9884.947939278716</v>
       </c>
       <c r="O49">
-        <v>2551.327031543249</v>
+        <v>2471.236984819679</v>
       </c>
       <c r="P49">
-        <v>7653.981094629748</v>
+        <v>7413.710954459037</v>
       </c>
       <c r="Q49">
-        <v>11149.98109462975</v>
+        <v>10909.71095445904</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1048366494727608</v>
+        <v>0.1058015108173799</v>
       </c>
       <c r="T49">
-        <v>1.150734183081987</v>
+        <v>1.16954112658409</v>
       </c>
       <c r="U49">
-        <v>0.06123661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.04592746249690056</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.005970231515618</v>
+        <v>2.827896287304745</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07796196762354983</v>
+        <v>0.07789335365299316</v>
       </c>
       <c r="C50">
-        <v>90348.21821133351</v>
+        <v>88766.5575845056</v>
       </c>
       <c r="D50">
-        <v>175194.6982113335</v>
+        <v>175380.6725845056</v>
       </c>
       <c r="E50">
-        <v>6590.479999999996</v>
+        <v>8358.115000000005</v>
       </c>
       <c r="F50">
-        <v>84846.48</v>
+        <v>86614.11500000001</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5515,28 +5515,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M50">
-        <v>5407.827570925366</v>
+        <v>5520.490645319644</v>
       </c>
       <c r="N50">
-        <v>9884.947939278718</v>
+        <v>9772.284864884437</v>
       </c>
       <c r="O50">
-        <v>2471.236984819679</v>
+        <v>2443.071216221109</v>
       </c>
       <c r="P50">
-        <v>7413.710954459038</v>
+        <v>7329.213648663328</v>
       </c>
       <c r="Q50">
-        <v>10909.71095445904</v>
+        <v>10825.21364866333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1058015108173799</v>
+        <v>0.106804209861788</v>
       </c>
       <c r="T50">
-        <v>1.16954112658409</v>
+        <v>1.189085597282353</v>
       </c>
       <c r="U50">
         <v>0.06373661666253409</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.827896287304746</v>
+        <v>2.770184118176077</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07789335365299316</v>
+        <v>0.0778247396824365</v>
       </c>
       <c r="C51">
-        <v>88766.5575845056</v>
+        <v>87185.29221188807</v>
       </c>
       <c r="D51">
-        <v>175380.6725845056</v>
+        <v>175567.0422118881</v>
       </c>
       <c r="E51">
-        <v>8358.115000000005</v>
+        <v>10125.75</v>
       </c>
       <c r="F51">
-        <v>86614.11500000001</v>
+        <v>88381.75</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5597,28 +5597,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M51">
-        <v>5520.490645319644</v>
+        <v>5633.153719713922</v>
       </c>
       <c r="N51">
-        <v>9772.284864884437</v>
+        <v>9659.62179049016</v>
       </c>
       <c r="O51">
-        <v>2443.071216221109</v>
+        <v>2414.90544762254</v>
       </c>
       <c r="P51">
-        <v>7329.213648663328</v>
+        <v>7244.71634286762</v>
       </c>
       <c r="Q51">
-        <v>10825.21364866333</v>
+        <v>10740.71634286762</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.106804209861788</v>
+        <v>0.1078470168679724</v>
       </c>
       <c r="T51">
-        <v>1.189085597282353</v>
+        <v>1.209411846808547</v>
       </c>
       <c r="U51">
         <v>0.06373661666253409</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.770184118176077</v>
+        <v>2.714780435812556</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0778247396824365</v>
+        <v>0.07775612571187984</v>
       </c>
       <c r="C52">
-        <v>87185.29221188807</v>
+        <v>85604.42335488119</v>
       </c>
       <c r="D52">
-        <v>175567.0422118881</v>
+        <v>175753.8083548812</v>
       </c>
       <c r="E52">
-        <v>10125.75</v>
+        <v>11893.38499999999</v>
       </c>
       <c r="F52">
-        <v>88381.75</v>
+        <v>90149.38499999999</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5679,28 +5679,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M52">
-        <v>5633.153719713922</v>
+        <v>5745.816794108201</v>
       </c>
       <c r="N52">
-        <v>9659.62179049016</v>
+        <v>9546.958716095882</v>
       </c>
       <c r="O52">
-        <v>2414.90544762254</v>
+        <v>2386.73967902397</v>
       </c>
       <c r="P52">
-        <v>7244.71634286762</v>
+        <v>7160.219037071911</v>
       </c>
       <c r="Q52">
-        <v>10740.71634286762</v>
+        <v>10656.21903707191</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1078470168679724</v>
+        <v>0.1089323874254297</v>
       </c>
       <c r="T52">
-        <v>1.209411846808547</v>
+        <v>1.230567739172545</v>
       </c>
       <c r="U52">
         <v>0.06373661666253409</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.714780435812556</v>
+        <v>2.661549446875055</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07775612571187984</v>
+        <v>0.07768751174132317</v>
       </c>
       <c r="C53">
-        <v>85604.42335488119</v>
+        <v>84023.95228025843</v>
       </c>
       <c r="D53">
-        <v>175753.8083548812</v>
+        <v>175940.9722802584</v>
       </c>
       <c r="E53">
-        <v>11893.38499999999</v>
+        <v>13661.02</v>
       </c>
       <c r="F53">
-        <v>90149.38499999999</v>
+        <v>91917.02</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5761,28 +5761,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M53">
-        <v>5745.816794108201</v>
+        <v>5858.47986850248</v>
       </c>
       <c r="N53">
-        <v>9546.958716095882</v>
+        <v>9434.295641701603</v>
       </c>
       <c r="O53">
-        <v>2386.73967902397</v>
+        <v>2358.573910425401</v>
       </c>
       <c r="P53">
-        <v>7160.219037071911</v>
+        <v>7075.721731276202</v>
       </c>
       <c r="Q53">
-        <v>10656.21903707191</v>
+        <v>10571.7217312762</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1089323874254297</v>
+        <v>0.1100629817561143</v>
       </c>
       <c r="T53">
-        <v>1.230567739172545</v>
+        <v>1.25260512705171</v>
       </c>
       <c r="U53">
         <v>0.06373661666253409</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.661549446875055</v>
+        <v>2.610365803665919</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07768751174132317</v>
+        <v>0.0776188977707665</v>
       </c>
       <c r="C54">
-        <v>84023.95228025843</v>
+        <v>82443.880260195</v>
       </c>
       <c r="D54">
-        <v>175940.9722802584</v>
+        <v>176128.535260195</v>
       </c>
       <c r="E54">
-        <v>13661.02</v>
+        <v>15428.655</v>
       </c>
       <c r="F54">
-        <v>91917.02</v>
+        <v>93684.655</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5843,28 +5843,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M54">
-        <v>5858.47986850248</v>
+        <v>5971.142942896758</v>
       </c>
       <c r="N54">
-        <v>9434.295641701603</v>
+        <v>9321.632567307326</v>
       </c>
       <c r="O54">
-        <v>2358.573910425401</v>
+        <v>2330.408141826832</v>
       </c>
       <c r="P54">
-        <v>7075.721731276202</v>
+        <v>6991.224425480495</v>
       </c>
       <c r="Q54">
-        <v>10571.7217312762</v>
+        <v>10487.22442548049</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1100629817561143</v>
+        <v>0.1112416864838494</v>
       </c>
       <c r="T54">
-        <v>1.25260512705171</v>
+        <v>1.275580276117222</v>
       </c>
       <c r="U54">
         <v>0.06373661666253409</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.610365803665919</v>
+        <v>2.561113618691091</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0776188977707665</v>
+        <v>0.07755028380020981</v>
       </c>
       <c r="C55">
-        <v>82443.880260195</v>
+        <v>80864.2085722968</v>
       </c>
       <c r="D55">
-        <v>176128.535260195</v>
+        <v>176316.4985722968</v>
       </c>
       <c r="E55">
-        <v>15428.655</v>
+        <v>17196.29000000001</v>
       </c>
       <c r="F55">
-        <v>93684.655</v>
+        <v>95452.29000000001</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5925,28 +5925,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M55">
-        <v>5971.142942896758</v>
+        <v>6083.806017291037</v>
       </c>
       <c r="N55">
-        <v>9321.632567307326</v>
+        <v>9208.969492913046</v>
       </c>
       <c r="O55">
-        <v>2330.408141826832</v>
+        <v>2302.242373228261</v>
       </c>
       <c r="P55">
-        <v>6991.224425480495</v>
+        <v>6906.727119684784</v>
       </c>
       <c r="Q55">
-        <v>10487.22442548049</v>
+        <v>10402.72711968478</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1112416864838494</v>
+        <v>0.112471639243225</v>
       </c>
       <c r="T55">
-        <v>1.275580276117222</v>
+        <v>1.299554344707321</v>
       </c>
       <c r="U55">
         <v>0.06373661666253409</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.561113618691091</v>
+        <v>2.513685588715329</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07755028380020981</v>
+        <v>0.07892541982965315</v>
       </c>
       <c r="C56">
-        <v>80864.2085722968</v>
+        <v>75404.43030640286</v>
       </c>
       <c r="D56">
-        <v>176316.4985722968</v>
+        <v>172624.3553064029</v>
       </c>
       <c r="E56">
-        <v>17196.29000000001</v>
+        <v>18963.925</v>
       </c>
       <c r="F56">
-        <v>95452.29000000001</v>
+        <v>97219.925</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -6007,45 +6007,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M56">
-        <v>6083.806017291037</v>
+        <v>6536.738829185314</v>
       </c>
       <c r="N56">
-        <v>9208.969492913046</v>
+        <v>8756.03668101877</v>
       </c>
       <c r="O56">
-        <v>2302.242373228261</v>
+        <v>2189.009170254692</v>
       </c>
       <c r="P56">
-        <v>6906.727119684784</v>
+        <v>6567.027510764077</v>
       </c>
       <c r="Q56">
-        <v>10402.72711968478</v>
+        <v>10063.02751076408</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.112471639243225</v>
+        <v>0.1137562565696841</v>
       </c>
       <c r="T56">
-        <v>1.299554344707321</v>
+        <v>1.32459392745698</v>
       </c>
       <c r="U56">
-        <v>0.06373661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.04780246249690057</v>
+        <v>0.05042746249690056</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.513685588715329</v>
+        <v>2.339511476567598</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07892541982965315</v>
+        <v>0.07888305585909648</v>
       </c>
       <c r="C57">
-        <v>75404.43030640286</v>
+        <v>73748.22961375907</v>
       </c>
       <c r="D57">
-        <v>172624.3553064029</v>
+        <v>172735.7896137591</v>
       </c>
       <c r="E57">
-        <v>18963.925</v>
+        <v>20731.56000000001</v>
       </c>
       <c r="F57">
-        <v>97219.925</v>
+        <v>98987.56000000001</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -6089,28 +6089,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M57">
-        <v>6536.738829185314</v>
+        <v>6655.588626079593</v>
       </c>
       <c r="N57">
-        <v>8756.03668101877</v>
+        <v>8637.18688412449</v>
       </c>
       <c r="O57">
-        <v>2189.009170254692</v>
+        <v>2159.296721031123</v>
       </c>
       <c r="P57">
-        <v>6567.027510764077</v>
+        <v>6477.890163093368</v>
       </c>
       <c r="Q57">
-        <v>10063.02751076408</v>
+        <v>9973.890163093369</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1137562565696841</v>
+        <v>0.1150992655928004</v>
       </c>
       <c r="T57">
-        <v>1.32459392745698</v>
+        <v>1.350771673058897</v>
       </c>
       <c r="U57">
         <v>0.06723661666253408</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.339511476567598</v>
+        <v>2.297734485914605</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07888305585909648</v>
+        <v>0.0788406918885398</v>
       </c>
       <c r="C58">
-        <v>73748.22961375907</v>
+        <v>72092.17288256221</v>
       </c>
       <c r="D58">
-        <v>172735.7896137591</v>
+        <v>172847.3678825622</v>
       </c>
       <c r="E58">
-        <v>20731.56000000001</v>
+        <v>22499.19500000001</v>
       </c>
       <c r="F58">
-        <v>98987.56000000001</v>
+        <v>100755.195</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6171,28 +6171,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M58">
-        <v>6655.588626079593</v>
+        <v>6774.438422973871</v>
       </c>
       <c r="N58">
-        <v>8637.18688412449</v>
+        <v>8518.337087230211</v>
       </c>
       <c r="O58">
-        <v>2159.296721031123</v>
+        <v>2129.584271807553</v>
       </c>
       <c r="P58">
-        <v>6477.890163093368</v>
+        <v>6388.752815422658</v>
       </c>
       <c r="Q58">
-        <v>9973.890163093369</v>
+        <v>9884.752815422658</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1150992655928004</v>
+        <v>0.1165047401518756</v>
       </c>
       <c r="T58">
-        <v>1.350771673058897</v>
+        <v>1.378166988223694</v>
       </c>
       <c r="U58">
         <v>0.06723661666253408</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.297734485914605</v>
+        <v>2.25742335458277</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0788406918885398</v>
+        <v>0.08001632791798316</v>
       </c>
       <c r="C59">
-        <v>72092.17288256221</v>
+        <v>67280.70884311124</v>
       </c>
       <c r="D59">
-        <v>172847.3678825622</v>
+        <v>169803.5388431113</v>
       </c>
       <c r="E59">
-        <v>22499.19500000001</v>
+        <v>24266.83000000002</v>
       </c>
       <c r="F59">
-        <v>100755.195</v>
+        <v>102522.83</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6253,45 +6253,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M59">
-        <v>6774.438422973871</v>
+        <v>7180.352143868151</v>
       </c>
       <c r="N59">
-        <v>8518.337087230211</v>
+        <v>8112.423366335932</v>
       </c>
       <c r="O59">
-        <v>2129.584271807553</v>
+        <v>2028.105841583983</v>
       </c>
       <c r="P59">
-        <v>6388.752815422658</v>
+        <v>6084.317524751948</v>
       </c>
       <c r="Q59">
-        <v>9884.752815422658</v>
+        <v>9580.317524751948</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1165047401518756</v>
+        <v>0.1179771420709067</v>
       </c>
       <c r="T59">
-        <v>1.378166988223694</v>
+        <v>1.406866842205861</v>
       </c>
       <c r="U59">
-        <v>0.06723661666253408</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.05042746249690056</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.25742335458277</v>
+        <v>2.129808567016278</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08001632791798316</v>
+        <v>0.07999496394742647</v>
       </c>
       <c r="C60">
-        <v>67280.70884311126</v>
+        <v>65567.43044611774</v>
       </c>
       <c r="D60">
-        <v>169803.5388431113</v>
+        <v>169857.8954461177</v>
       </c>
       <c r="E60">
-        <v>24266.82999999999</v>
+        <v>26034.465</v>
       </c>
       <c r="F60">
-        <v>102522.83</v>
+        <v>104290.465</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6335,28 +6335,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M60">
-        <v>7180.352143868149</v>
+        <v>7304.151318762429</v>
       </c>
       <c r="N60">
-        <v>8112.423366335934</v>
+        <v>7988.624191441654</v>
       </c>
       <c r="O60">
-        <v>2028.105841583983</v>
+        <v>1997.156047860414</v>
       </c>
       <c r="P60">
-        <v>6084.31752475195</v>
+        <v>5991.468143581241</v>
       </c>
       <c r="Q60">
-        <v>9580.31752475195</v>
+        <v>9487.468143581242</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1179771420709067</v>
+        <v>0.119521368473793</v>
       </c>
       <c r="T60">
-        <v>1.406866842205861</v>
+        <v>1.436966689065208</v>
       </c>
       <c r="U60">
         <v>0.07003661666253409</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.129808567016278</v>
+        <v>2.093710116727866</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07999496394742647</v>
+        <v>0.07997359997686981</v>
       </c>
       <c r="C61">
-        <v>65567.43044611774</v>
+        <v>63854.1868609595</v>
       </c>
       <c r="D61">
-        <v>169857.8954461177</v>
+        <v>169912.2868609595</v>
       </c>
       <c r="E61">
-        <v>26034.465</v>
+        <v>27802.09999999999</v>
       </c>
       <c r="F61">
-        <v>104290.465</v>
+        <v>106058.1</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6417,28 +6417,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M61">
-        <v>7304.151318762429</v>
+        <v>7427.950493656706</v>
       </c>
       <c r="N61">
-        <v>7988.624191441654</v>
+        <v>7864.825016547376</v>
       </c>
       <c r="O61">
-        <v>1997.156047860414</v>
+        <v>1966.206254136844</v>
       </c>
       <c r="P61">
-        <v>5991.468143581241</v>
+        <v>5898.618762410532</v>
       </c>
       <c r="Q61">
-        <v>9487.468143581242</v>
+        <v>9394.618762410533</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.119521368473793</v>
+        <v>0.1211428061968237</v>
       </c>
       <c r="T61">
-        <v>1.436966689065208</v>
+        <v>1.468571528267522</v>
       </c>
       <c r="U61">
         <v>0.07003661666253409</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.093710116727866</v>
+        <v>2.058814948115735</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07997359997686981</v>
+        <v>0.07995223600631314</v>
       </c>
       <c r="C62">
-        <v>63854.1868609595</v>
+        <v>62140.97812108939</v>
       </c>
       <c r="D62">
-        <v>169912.2868609595</v>
+        <v>169966.7131210894</v>
       </c>
       <c r="E62">
-        <v>27802.09999999999</v>
+        <v>29569.735</v>
       </c>
       <c r="F62">
-        <v>106058.1</v>
+        <v>107825.735</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6499,28 +6499,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M62">
-        <v>7427.950493656706</v>
+        <v>7551.749668550986</v>
       </c>
       <c r="N62">
-        <v>7864.825016547376</v>
+        <v>7741.025841653097</v>
       </c>
       <c r="O62">
-        <v>1966.206254136844</v>
+        <v>1935.256460413274</v>
       </c>
       <c r="P62">
-        <v>5898.618762410532</v>
+        <v>5805.769381239823</v>
       </c>
       <c r="Q62">
-        <v>9394.618762410533</v>
+        <v>9301.769381239823</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1211428061968237</v>
+        <v>0.1228473945723174</v>
       </c>
       <c r="T62">
-        <v>1.468571528267522</v>
+        <v>1.50179712845457</v>
       </c>
       <c r="U62">
         <v>0.07003661666253409</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.058814948115735</v>
+        <v>2.025063883392527</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07995223600631314</v>
+        <v>0.08355787203575646</v>
       </c>
       <c r="C63">
-        <v>62140.97812108939</v>
+        <v>51656.04745509831</v>
       </c>
       <c r="D63">
-        <v>169966.7131210894</v>
+        <v>161249.4174550983</v>
       </c>
       <c r="E63">
-        <v>29569.735</v>
+        <v>31337.37</v>
       </c>
       <c r="F63">
-        <v>107825.735</v>
+        <v>109593.37</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6581,45 +6581,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M63">
-        <v>7551.749668550986</v>
+        <v>8530.377129445262</v>
       </c>
       <c r="N63">
-        <v>7741.025841653097</v>
+        <v>6762.398380758821</v>
       </c>
       <c r="O63">
-        <v>1935.256460413274</v>
+        <v>1690.599595189705</v>
       </c>
       <c r="P63">
-        <v>5805.769381239823</v>
+        <v>5071.798785569115</v>
       </c>
       <c r="Q63">
-        <v>9301.769381239823</v>
+        <v>8567.798785569115</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1228473945723174</v>
+        <v>0.1246416981254687</v>
       </c>
       <c r="T63">
-        <v>1.50179712845457</v>
+        <v>1.536771444440936</v>
       </c>
       <c r="U63">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253408</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.05252746249690057</v>
+        <v>0.05837746249690056</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.025063883392527</v>
+        <v>1.792743190382086</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08355787203575646</v>
+        <v>0.0835950080651998</v>
       </c>
       <c r="C64">
-        <v>51656.04745509831</v>
+        <v>49803.2789947667</v>
       </c>
       <c r="D64">
-        <v>161249.4174550983</v>
+        <v>161164.2839947667</v>
       </c>
       <c r="E64">
-        <v>31337.37</v>
+        <v>33105.005</v>
       </c>
       <c r="F64">
-        <v>109593.37</v>
+        <v>111361.005</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6663,28 +6663,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M64">
-        <v>8530.377129445262</v>
+        <v>8667.963857339542</v>
       </c>
       <c r="N64">
-        <v>6762.398380758821</v>
+        <v>6624.811652864541</v>
       </c>
       <c r="O64">
-        <v>1690.599595189705</v>
+        <v>1656.202913216135</v>
       </c>
       <c r="P64">
-        <v>5071.798785569115</v>
+        <v>4968.608739648405</v>
       </c>
       <c r="Q64">
-        <v>8567.798785569115</v>
+        <v>8464.608739648405</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1246416981254687</v>
+        <v>0.1265329910598715</v>
       </c>
       <c r="T64">
-        <v>1.536771444440936</v>
+        <v>1.573636263994133</v>
       </c>
       <c r="U64">
         <v>0.07783661666253408</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.792743190382086</v>
+        <v>1.76428694926491</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0835950080651998</v>
+        <v>0.08550414409464313</v>
       </c>
       <c r="C65">
-        <v>49803.2789947667</v>
+        <v>43776.897310099</v>
       </c>
       <c r="D65">
-        <v>161164.2839947667</v>
+        <v>156905.537310099</v>
       </c>
       <c r="E65">
-        <v>33105.005</v>
+        <v>34872.64</v>
       </c>
       <c r="F65">
-        <v>111361.005</v>
+        <v>113128.64</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6745,45 +6745,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M65">
-        <v>8667.963857339542</v>
+        <v>9246.752281233821</v>
       </c>
       <c r="N65">
-        <v>6624.811652864541</v>
+        <v>6046.023228970262</v>
       </c>
       <c r="O65">
-        <v>1656.202913216135</v>
+        <v>1511.505807242565</v>
       </c>
       <c r="P65">
-        <v>4968.608739648405</v>
+        <v>4534.517421727696</v>
       </c>
       <c r="Q65">
-        <v>8464.608739648405</v>
+        <v>8030.517421727696</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1265329910598715</v>
+        <v>0.1285293558239632</v>
       </c>
       <c r="T65">
-        <v>1.573636263994133</v>
+        <v>1.612549129078063</v>
       </c>
       <c r="U65">
-        <v>0.07783661666253408</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.05837746249690056</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.76428694926491</v>
+        <v>1.653853703990816</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08550414409464313</v>
+        <v>0.08557053012408647</v>
       </c>
       <c r="C66">
-        <v>43776.897310099</v>
+        <v>41865.21928934332</v>
       </c>
       <c r="D66">
-        <v>156905.537310099</v>
+        <v>156761.4942893433</v>
       </c>
       <c r="E66">
-        <v>34872.64</v>
+        <v>36640.27500000001</v>
       </c>
       <c r="F66">
-        <v>113128.64</v>
+        <v>114896.275</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6827,28 +6827,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M66">
-        <v>9246.752281233821</v>
+        <v>9391.232785628101</v>
       </c>
       <c r="N66">
-        <v>6046.023228970262</v>
+        <v>5901.542724575982</v>
       </c>
       <c r="O66">
-        <v>1511.505807242565</v>
+        <v>1475.385681143995</v>
       </c>
       <c r="P66">
-        <v>4534.517421727696</v>
+        <v>4426.157043431986</v>
       </c>
       <c r="Q66">
-        <v>8030.517421727696</v>
+        <v>7922.157043431986</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1285293558239632</v>
+        <v>0.1306397985745746</v>
       </c>
       <c r="T66">
-        <v>1.612549129078063</v>
+        <v>1.653685586452504</v>
       </c>
       <c r="U66">
         <v>0.0817366166625341</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.653853703990816</v>
+        <v>1.628409800852495</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08557053012408647</v>
+        <v>0.08563691615352979</v>
       </c>
       <c r="C67">
-        <v>41865.21928934332</v>
+        <v>39953.80549586914</v>
       </c>
       <c r="D67">
-        <v>156761.4942893433</v>
+        <v>156617.7154958691</v>
       </c>
       <c r="E67">
-        <v>36640.27500000001</v>
+        <v>38407.91</v>
       </c>
       <c r="F67">
-        <v>114896.275</v>
+        <v>116663.91</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6909,28 +6909,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M67">
-        <v>9391.232785628101</v>
+        <v>9535.713290022379</v>
       </c>
       <c r="N67">
-        <v>5901.542724575982</v>
+        <v>5757.062220181704</v>
       </c>
       <c r="O67">
-        <v>1475.385681143995</v>
+        <v>1439.265555045426</v>
       </c>
       <c r="P67">
-        <v>4426.157043431986</v>
+        <v>4317.796665136279</v>
       </c>
       <c r="Q67">
-        <v>7922.157043431986</v>
+        <v>7813.796665136279</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1306397985745746</v>
+        <v>0.1328743850163983</v>
       </c>
       <c r="T67">
-        <v>1.653685586452504</v>
+        <v>1.697241835437205</v>
       </c>
       <c r="U67">
         <v>0.0817366166625341</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.628409800852495</v>
+        <v>1.603736925082003</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08563691615352979</v>
+        <v>0.08570330218297312</v>
       </c>
       <c r="C68">
-        <v>39953.80549586914</v>
+        <v>38042.65520330911</v>
       </c>
       <c r="D68">
-        <v>156617.7154958691</v>
+        <v>156474.2002033091</v>
       </c>
       <c r="E68">
-        <v>38407.91</v>
+        <v>40175.54500000001</v>
       </c>
       <c r="F68">
-        <v>116663.91</v>
+        <v>118431.545</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6991,28 +6991,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M68">
-        <v>9535.713290022379</v>
+        <v>9680.193794416658</v>
       </c>
       <c r="N68">
-        <v>5757.062220181704</v>
+        <v>5612.581715787424</v>
       </c>
       <c r="O68">
-        <v>1439.265555045426</v>
+        <v>1403.145428946856</v>
       </c>
       <c r="P68">
-        <v>4317.796665136279</v>
+        <v>4209.436286840568</v>
       </c>
       <c r="Q68">
-        <v>7813.796665136279</v>
+        <v>7705.436286840568</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1328743850163983</v>
+        <v>0.1352444009395447</v>
       </c>
       <c r="T68">
-        <v>1.697241835437205</v>
+        <v>1.743437857087646</v>
       </c>
       <c r="U68">
         <v>0.0817366166625341</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.603736925082003</v>
+        <v>1.579800553065854</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08570330218297312</v>
+        <v>0.08576968821241646</v>
       </c>
       <c r="C69">
-        <v>38042.65520330911</v>
+        <v>36131.76768795615</v>
       </c>
       <c r="D69">
-        <v>156474.2002033091</v>
+        <v>156330.9476879562</v>
       </c>
       <c r="E69">
-        <v>40175.54500000001</v>
+        <v>41943.18000000001</v>
       </c>
       <c r="F69">
-        <v>118431.545</v>
+        <v>120199.18</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -7073,28 +7073,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M69">
-        <v>9680.193794416658</v>
+        <v>9824.674298810936</v>
       </c>
       <c r="N69">
-        <v>5612.581715787424</v>
+        <v>5468.101211393147</v>
       </c>
       <c r="O69">
-        <v>1403.145428946856</v>
+        <v>1367.025302848287</v>
       </c>
       <c r="P69">
-        <v>4209.436286840568</v>
+        <v>4101.07590854486</v>
       </c>
       <c r="Q69">
-        <v>7705.436286840568</v>
+        <v>7597.07590854486</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1352444009395447</v>
+        <v>0.1377625428578877</v>
       </c>
       <c r="T69">
-        <v>1.743437857087646</v>
+        <v>1.79252113009124</v>
       </c>
       <c r="U69">
         <v>0.0817366166625341</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.579800553065854</v>
+        <v>1.556568191991356</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08576968821241646</v>
+        <v>0.08583607424185979</v>
       </c>
       <c r="C70">
-        <v>36131.76768795615</v>
+        <v>34221.14222875079</v>
       </c>
       <c r="D70">
-        <v>156330.9476879562</v>
+        <v>156187.9572287508</v>
       </c>
       <c r="E70">
-        <v>41943.18000000001</v>
+        <v>43710.81500000002</v>
       </c>
       <c r="F70">
-        <v>120199.18</v>
+        <v>121966.815</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7155,28 +7155,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M70">
-        <v>9824.674298810936</v>
+        <v>9969.154803205214</v>
       </c>
       <c r="N70">
-        <v>5468.101211393147</v>
+        <v>5323.620706998869</v>
       </c>
       <c r="O70">
-        <v>1367.025302848287</v>
+        <v>1330.905176749717</v>
       </c>
       <c r="P70">
-        <v>4101.07590854486</v>
+        <v>3992.715530249151</v>
       </c>
       <c r="Q70">
-        <v>7597.07590854486</v>
+        <v>7488.715530249152</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1377625428578877</v>
+        <v>0.1404431455451561</v>
       </c>
       <c r="T70">
-        <v>1.79252113009124</v>
+        <v>1.844771065869259</v>
       </c>
       <c r="U70">
         <v>0.0817366166625341</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.556568191991356</v>
+        <v>1.534009232687134</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08583607424185979</v>
+        <v>0.0859024602713031</v>
       </c>
       <c r="C71">
-        <v>34221.14222875079</v>
+        <v>32310.77810726943</v>
       </c>
       <c r="D71">
-        <v>156187.9572287508</v>
+        <v>156045.2281072694</v>
       </c>
       <c r="E71">
-        <v>43710.81500000002</v>
+        <v>45478.45000000001</v>
       </c>
       <c r="F71">
-        <v>121966.815</v>
+        <v>123734.45</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7237,28 +7237,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M71">
-        <v>9969.154803205214</v>
+        <v>10113.63530759949</v>
       </c>
       <c r="N71">
-        <v>5323.620706998869</v>
+        <v>5179.140202604591</v>
       </c>
       <c r="O71">
-        <v>1330.905176749717</v>
+        <v>1294.785050651148</v>
       </c>
       <c r="P71">
-        <v>3992.715530249151</v>
+        <v>3884.355151953443</v>
       </c>
       <c r="Q71">
-        <v>7488.715530249152</v>
+        <v>7380.355151953443</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1404431455451561</v>
+        <v>0.1433024550782424</v>
       </c>
       <c r="T71">
-        <v>1.844771065869259</v>
+        <v>1.900504330699146</v>
       </c>
       <c r="U71">
         <v>0.0817366166625341</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.534009232687134</v>
+        <v>1.512094815077317</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0859024602713031</v>
+        <v>0.09353034630074646</v>
       </c>
       <c r="C72">
-        <v>32310.77810726943</v>
+        <v>15715.21558227263</v>
       </c>
       <c r="D72">
-        <v>156045.2281072694</v>
+        <v>141217.3005822726</v>
       </c>
       <c r="E72">
-        <v>45478.45000000001</v>
+        <v>47246.08500000001</v>
       </c>
       <c r="F72">
-        <v>123734.45</v>
+        <v>125502.085</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7319,45 +7319,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M72">
-        <v>10113.63530759949</v>
+        <v>12040.24541899377</v>
       </c>
       <c r="N72">
-        <v>5179.140202604591</v>
+        <v>3252.530091210314</v>
       </c>
       <c r="O72">
-        <v>1294.785050651148</v>
+        <v>813.1325228025785</v>
       </c>
       <c r="P72">
-        <v>3884.355151953443</v>
+        <v>2439.397568407735</v>
       </c>
       <c r="Q72">
-        <v>7380.355151953443</v>
+        <v>5935.397568407736</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1433024550782424</v>
+        <v>0.1463589583722312</v>
       </c>
       <c r="T72">
-        <v>1.900504330699146</v>
+        <v>1.960081268965577</v>
       </c>
       <c r="U72">
-        <v>0.0817366166625341</v>
+        <v>0.09593661666253409</v>
       </c>
       <c r="V72">
         <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.06130246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.512094815077317</v>
+        <v>1.27013818888437</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09353034630074646</v>
+        <v>0.09370323233018979</v>
       </c>
       <c r="C73">
-        <v>15715.21558227265</v>
+        <v>13644.09417994591</v>
       </c>
       <c r="D73">
-        <v>141217.3005822726</v>
+        <v>140913.8141799459</v>
       </c>
       <c r="E73">
-        <v>47246.08499999999</v>
+        <v>49013.72</v>
       </c>
       <c r="F73">
-        <v>125502.085</v>
+        <v>127269.72</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7401,28 +7401,28 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M73">
-        <v>12040.24541899377</v>
+        <v>12209.82634038805</v>
       </c>
       <c r="N73">
-        <v>3252.530091210314</v>
+        <v>3082.949169816035</v>
       </c>
       <c r="O73">
-        <v>813.1325228025785</v>
+        <v>770.7372924540086</v>
       </c>
       <c r="P73">
-        <v>2439.397568407735</v>
+        <v>2312.211877362026</v>
       </c>
       <c r="Q73">
-        <v>5935.397568407736</v>
+        <v>5808.211877362026</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1463589583722312</v>
+        <v>0.1496337833300763</v>
       </c>
       <c r="T73">
-        <v>1.960081268965577</v>
+        <v>2.023913702822467</v>
       </c>
       <c r="U73">
         <v>0.09593661666253409</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.27013818888437</v>
+        <v>1.252497380705421</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09370323233018979</v>
+        <v>0.1109465892306934</v>
       </c>
       <c r="C74">
-        <v>13644.09417994591</v>
+        <v>-12996.34491523534</v>
       </c>
       <c r="D74">
-        <v>140913.8141799459</v>
+        <v>116041.0100847647</v>
       </c>
       <c r="E74">
-        <v>49013.72</v>
+        <v>50781.355</v>
       </c>
       <c r="F74">
-        <v>127269.72</v>
+        <v>129037.355</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7483,45 +7483,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M74">
-        <v>12209.82634038805</v>
+        <v>16069.87561478233</v>
       </c>
       <c r="N74">
-        <v>3082.949169816035</v>
+        <v>-777.100104578245</v>
       </c>
       <c r="O74">
-        <v>770.7372924540086</v>
+        <v>-194.2750261445613</v>
       </c>
       <c r="P74">
-        <v>2312.211877362026</v>
+        <v>-582.8250784336838</v>
       </c>
       <c r="Q74">
-        <v>5808.211877362026</v>
+        <v>2913.174921566316</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1496337833300763</v>
+        <v>0.1543100891188336</v>
       </c>
       <c r="T74">
-        <v>2.023913702822467</v>
+        <v>2.115063606648733</v>
       </c>
       <c r="U74">
-        <v>0.09593661666253409</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V74">
-        <v>0.25</v>
+        <v>0.2379106079722327</v>
       </c>
       <c r="W74">
-        <v>0.07195246249690057</v>
+        <v>0.09490803447754573</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.252497380705421</v>
+        <v>0.9516424318889309</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1109465892306934</v>
+        <v>0.1117339553973188</v>
       </c>
       <c r="C75">
-        <v>-12996.34491523534</v>
+        <v>-15691.77336157023</v>
       </c>
       <c r="D75">
-        <v>116041.0100847647</v>
+        <v>115113.2166384298</v>
       </c>
       <c r="E75">
-        <v>50781.355</v>
+        <v>52548.99000000001</v>
       </c>
       <c r="F75">
-        <v>129037.355</v>
+        <v>130804.99</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7565,37 +7565,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M75">
-        <v>16069.87561478233</v>
+        <v>16290.01089717661</v>
       </c>
       <c r="N75">
-        <v>-777.100104578245</v>
+        <v>-997.2353869725248</v>
       </c>
       <c r="O75">
-        <v>-194.2750261445613</v>
+        <v>-249.3088467431312</v>
       </c>
       <c r="P75">
-        <v>-582.8250784336838</v>
+        <v>-747.9265402293936</v>
       </c>
       <c r="Q75">
-        <v>2913.174921566316</v>
+        <v>2748.073459770606</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1543100891188336</v>
+        <v>0.1584835540849426</v>
       </c>
       <c r="T75">
-        <v>2.115063606648733</v>
+        <v>2.196412206904454</v>
       </c>
       <c r="U75">
         <v>0.1245366166625341</v>
       </c>
       <c r="V75">
-        <v>0.2379106079722327</v>
+        <v>0.2346955997563917</v>
       </c>
       <c r="W75">
-        <v>0.09490803447754573</v>
+        <v>0.09530842072328881</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9516424318889309</v>
+        <v>0.9387823990255669</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1117339553973188</v>
+        <v>0.1125213215639441</v>
       </c>
       <c r="C76">
-        <v>-15691.77336157023</v>
+        <v>-18372.48334190261</v>
       </c>
       <c r="D76">
-        <v>115113.2166384298</v>
+        <v>114200.1416580974</v>
       </c>
       <c r="E76">
-        <v>52548.99000000001</v>
+        <v>54316.625</v>
       </c>
       <c r="F76">
-        <v>130804.99</v>
+        <v>132572.625</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7647,37 +7647,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M76">
-        <v>16290.01089717661</v>
+        <v>16510.14617957089</v>
       </c>
       <c r="N76">
-        <v>-997.2353869725248</v>
+        <v>-1217.370669366803</v>
       </c>
       <c r="O76">
-        <v>-249.3088467431312</v>
+        <v>-304.3426673417007</v>
       </c>
       <c r="P76">
-        <v>-747.9265402293936</v>
+        <v>-913.0280020251021</v>
       </c>
       <c r="Q76">
-        <v>2748.073459770606</v>
+        <v>2582.971997974898</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1584835540849426</v>
+        <v>0.1629908962483403</v>
       </c>
       <c r="T76">
-        <v>2.196412206904454</v>
+        <v>2.284268695180632</v>
       </c>
       <c r="U76">
         <v>0.1245366166625341</v>
       </c>
       <c r="V76">
-        <v>0.2346955997563917</v>
+        <v>0.2315663250929732</v>
       </c>
       <c r="W76">
-        <v>0.09530842072328881</v>
+        <v>0.09569813000247875</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9387823990255669</v>
+        <v>0.9262653003718927</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1125213215639441</v>
+        <v>0.1133086877305695</v>
       </c>
       <c r="C77">
-        <v>-18372.48334190261</v>
+        <v>-21038.82233945042</v>
       </c>
       <c r="D77">
-        <v>114200.1416580974</v>
+        <v>113301.4376605496</v>
       </c>
       <c r="E77">
-        <v>54316.625</v>
+        <v>56084.26000000001</v>
       </c>
       <c r="F77">
-        <v>132572.625</v>
+        <v>134340.26</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7729,37 +7729,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M77">
-        <v>16510.14617957089</v>
+        <v>16730.28146196517</v>
       </c>
       <c r="N77">
-        <v>-1217.370669366803</v>
+        <v>-1437.505951761083</v>
       </c>
       <c r="O77">
-        <v>-304.3426673417007</v>
+        <v>-359.3764879402706</v>
       </c>
       <c r="P77">
-        <v>-913.0280020251021</v>
+        <v>-1078.129463820812</v>
       </c>
       <c r="Q77">
-        <v>2582.971997974898</v>
+        <v>2417.870536179188</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1629908962483403</v>
+        <v>0.1678738502586878</v>
       </c>
       <c r="T77">
-        <v>2.284268695180632</v>
+        <v>2.379446557479825</v>
       </c>
       <c r="U77">
         <v>0.1245366166625341</v>
       </c>
       <c r="V77">
-        <v>0.2315663250929732</v>
+        <v>0.2285193997628024</v>
       </c>
       <c r="W77">
-        <v>0.09569813000247875</v>
+        <v>0.09607758377432159</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9262653003718927</v>
+        <v>0.9140775990512098</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1133086877305695</v>
+        <v>0.1140960538971948</v>
       </c>
       <c r="C78">
-        <v>-21038.82233945042</v>
+        <v>-23691.12698468808</v>
       </c>
       <c r="D78">
-        <v>113301.4376605496</v>
+        <v>112416.7680153119</v>
       </c>
       <c r="E78">
-        <v>56084.26000000001</v>
+        <v>57851.89499999999</v>
       </c>
       <c r="F78">
-        <v>134340.26</v>
+        <v>136107.895</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7811,37 +7811,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M78">
-        <v>16730.28146196517</v>
+        <v>16950.41674435944</v>
       </c>
       <c r="N78">
-        <v>-1437.505951761083</v>
+        <v>-1657.641234155359</v>
       </c>
       <c r="O78">
-        <v>-359.3764879402706</v>
+        <v>-414.4103085388397</v>
       </c>
       <c r="P78">
-        <v>-1078.129463820812</v>
+        <v>-1243.230925616519</v>
       </c>
       <c r="Q78">
-        <v>2417.870536179188</v>
+        <v>2252.769074383481</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1678738502586878</v>
+        <v>0.1731814089655873</v>
       </c>
       <c r="T78">
-        <v>2.379446557479825</v>
+        <v>2.482900755631122</v>
       </c>
       <c r="U78">
         <v>0.1245366166625341</v>
       </c>
       <c r="V78">
-        <v>0.2285193997628024</v>
+        <v>0.2255516153502986</v>
       </c>
       <c r="W78">
-        <v>0.09607758377432159</v>
+        <v>0.09644718160403863</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9140775990512098</v>
+        <v>0.9022064614011942</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1140960538971948</v>
+        <v>0.1148834200638202</v>
       </c>
       <c r="C79">
-        <v>-23691.12698468808</v>
+        <v>-26329.7234757611</v>
       </c>
       <c r="D79">
-        <v>112416.7680153119</v>
+        <v>111545.8065242389</v>
       </c>
       <c r="E79">
-        <v>57851.89499999999</v>
+        <v>59619.53</v>
       </c>
       <c r="F79">
-        <v>136107.895</v>
+        <v>137875.53</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7893,37 +7893,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M79">
-        <v>16950.41674435944</v>
+        <v>17170.55202675372</v>
       </c>
       <c r="N79">
-        <v>-1657.641234155359</v>
+        <v>-1877.776516549638</v>
       </c>
       <c r="O79">
-        <v>-414.4103085388397</v>
+        <v>-469.4441291374096</v>
       </c>
       <c r="P79">
-        <v>-1243.230925616519</v>
+        <v>-1408.332387412229</v>
       </c>
       <c r="Q79">
-        <v>2252.769074383481</v>
+        <v>2087.667612587771</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1731814089655873</v>
+        <v>0.1789714730094776</v>
       </c>
       <c r="T79">
-        <v>2.482900755631122</v>
+        <v>2.595759880887082</v>
       </c>
       <c r="U79">
         <v>0.1245366166625341</v>
       </c>
       <c r="V79">
-        <v>0.2255516153502986</v>
+        <v>0.2226599279740127</v>
       </c>
       <c r="W79">
-        <v>0.09644718160403863</v>
+        <v>0.09680730256632702</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9022064614011942</v>
+        <v>0.8906397118960506</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1148834200638202</v>
+        <v>0.1156707862304455</v>
       </c>
       <c r="C80">
-        <v>-26329.7234757611</v>
+        <v>-28954.92797950703</v>
       </c>
       <c r="D80">
-        <v>111545.8065242389</v>
+        <v>110688.237020493</v>
       </c>
       <c r="E80">
-        <v>59619.53</v>
+        <v>61387.16500000001</v>
       </c>
       <c r="F80">
-        <v>137875.53</v>
+        <v>139643.165</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7975,37 +7975,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M80">
-        <v>17170.55202675372</v>
+        <v>17390.687309148</v>
       </c>
       <c r="N80">
-        <v>-1877.776516549638</v>
+        <v>-2097.911798943918</v>
       </c>
       <c r="O80">
-        <v>-469.4441291374096</v>
+        <v>-524.4779497359796</v>
       </c>
       <c r="P80">
-        <v>-1408.332387412229</v>
+        <v>-1573.433849207939</v>
       </c>
       <c r="Q80">
-        <v>2087.667612587771</v>
+        <v>1922.566150792061</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1789714730094776</v>
+        <v>0.1853129717242146</v>
       </c>
       <c r="T80">
-        <v>2.595759880887082</v>
+        <v>2.719367494262657</v>
       </c>
       <c r="U80">
         <v>0.1245366166625341</v>
       </c>
       <c r="V80">
-        <v>0.2226599279740127</v>
+        <v>0.2198414478730758</v>
       </c>
       <c r="W80">
-        <v>0.09680730256632702</v>
+        <v>0.09715830654222839</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8906397118960506</v>
+        <v>0.8793657914923031</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1156707862304455</v>
+        <v>0.1164581523970708</v>
       </c>
       <c r="C81">
-        <v>-28954.92797950703</v>
+        <v>-31567.04701411948</v>
       </c>
       <c r="D81">
-        <v>110688.237020493</v>
+        <v>109843.7529858805</v>
       </c>
       <c r="E81">
-        <v>61387.16500000001</v>
+        <v>63154.80000000002</v>
       </c>
       <c r="F81">
-        <v>139643.165</v>
+        <v>141410.8</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -8057,37 +8057,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M81">
-        <v>17390.687309148</v>
+        <v>17610.82259154228</v>
       </c>
       <c r="N81">
-        <v>-2097.911798943918</v>
+        <v>-2318.047081338198</v>
       </c>
       <c r="O81">
-        <v>-524.4779497359796</v>
+        <v>-579.5117703345495</v>
       </c>
       <c r="P81">
-        <v>-1573.433849207939</v>
+        <v>-1738.535311003649</v>
       </c>
       <c r="Q81">
-        <v>1922.566150792061</v>
+        <v>1757.464688996351</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1853129717242146</v>
+        <v>0.1922886203104254</v>
       </c>
       <c r="T81">
-        <v>2.719367494262657</v>
+        <v>2.855335868975791</v>
       </c>
       <c r="U81">
         <v>0.1245366166625341</v>
       </c>
       <c r="V81">
-        <v>0.2198414478730758</v>
+        <v>0.2170934297746623</v>
       </c>
       <c r="W81">
-        <v>0.09715830654222839</v>
+        <v>0.09750053541873221</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8793657914923031</v>
+        <v>0.8683737190986492</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1164581523970708</v>
+        <v>0.1172455185636962</v>
       </c>
       <c r="C82">
-        <v>-31567.04701411948</v>
+        <v>-34166.37781442782</v>
       </c>
       <c r="D82">
-        <v>109843.7529858805</v>
+        <v>109012.0571855722</v>
       </c>
       <c r="E82">
-        <v>63154.80000000002</v>
+        <v>64922.435</v>
       </c>
       <c r="F82">
-        <v>141410.8</v>
+        <v>143178.435</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8139,37 +8139,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M82">
-        <v>17610.82259154228</v>
+        <v>17830.95787393656</v>
       </c>
       <c r="N82">
-        <v>-2318.047081338198</v>
+        <v>-2538.182363732474</v>
       </c>
       <c r="O82">
-        <v>-579.5117703345495</v>
+        <v>-634.5455909331185</v>
       </c>
       <c r="P82">
-        <v>-1738.535311003649</v>
+        <v>-1903.636772799356</v>
       </c>
       <c r="Q82">
-        <v>1757.464688996351</v>
+        <v>1592.363227200644</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1922886203104254</v>
+        <v>0.1999985476951846</v>
       </c>
       <c r="T82">
-        <v>2.855335868975791</v>
+        <v>3.005616704185043</v>
       </c>
       <c r="U82">
         <v>0.1245366166625341</v>
       </c>
       <c r="V82">
-        <v>0.2170934297746623</v>
+        <v>0.2144132639749751</v>
       </c>
       <c r="W82">
-        <v>0.09750053541873221</v>
+        <v>0.09783431419951988</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8683737190986492</v>
+        <v>0.8576530558999006</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1172455185636962</v>
+        <v>0.1180328847303215</v>
       </c>
       <c r="C83">
-        <v>-34166.37781442782</v>
+        <v>-36753.20868070677</v>
       </c>
       <c r="D83">
-        <v>109012.0571855722</v>
+        <v>108192.8613192932</v>
       </c>
       <c r="E83">
-        <v>64922.435</v>
+        <v>66690.07000000001</v>
       </c>
       <c r="F83">
-        <v>143178.435</v>
+        <v>144946.07</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8221,37 +8221,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M83">
-        <v>17830.95787393656</v>
+        <v>18051.09315633083</v>
       </c>
       <c r="N83">
-        <v>-2538.182363732474</v>
+        <v>-2758.31764612675</v>
       </c>
       <c r="O83">
-        <v>-634.5455909331185</v>
+        <v>-689.5794115316876</v>
       </c>
       <c r="P83">
-        <v>-1903.636772799356</v>
+        <v>-2068.738234595063</v>
       </c>
       <c r="Q83">
-        <v>1592.363227200644</v>
+        <v>1427.261765404937</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1999985476951846</v>
+        <v>0.2085651336782504</v>
       </c>
       <c r="T83">
-        <v>3.005616704185043</v>
+        <v>3.172595409973101</v>
       </c>
       <c r="U83">
         <v>0.1245366166625341</v>
       </c>
       <c r="V83">
-        <v>0.2144132639749751</v>
+        <v>0.2117984680728413</v>
       </c>
       <c r="W83">
-        <v>0.09783431419951988</v>
+        <v>0.0981599520344347</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8576530558999006</v>
+        <v>0.8471938722913653</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1180328847303215</v>
+        <v>0.1188202508969469</v>
       </c>
       <c r="C84">
-        <v>-36753.20868070677</v>
+        <v>-39327.81931187629</v>
       </c>
       <c r="D84">
-        <v>108192.8613192932</v>
+        <v>107385.8856881237</v>
       </c>
       <c r="E84">
-        <v>66690.07000000001</v>
+        <v>68457.70500000002</v>
       </c>
       <c r="F84">
-        <v>144946.07</v>
+        <v>146713.705</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8303,37 +8303,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M84">
-        <v>18051.09315633083</v>
+        <v>18271.22843872511</v>
       </c>
       <c r="N84">
-        <v>-2758.31764612675</v>
+        <v>-2978.45292852103</v>
       </c>
       <c r="O84">
-        <v>-689.5794115316876</v>
+        <v>-744.6132321302575</v>
       </c>
       <c r="P84">
-        <v>-2068.738234595063</v>
+        <v>-2233.839696390773</v>
       </c>
       <c r="Q84">
-        <v>1427.261765404937</v>
+        <v>1262.160303609227</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2085651336782504</v>
+        <v>0.2181395533063828</v>
       </c>
       <c r="T84">
-        <v>3.172595409973101</v>
+        <v>3.359218669383283</v>
       </c>
       <c r="U84">
         <v>0.1245366166625341</v>
       </c>
       <c r="V84">
-        <v>0.2117984680728413</v>
+        <v>0.2092466793008794</v>
       </c>
       <c r="W84">
-        <v>0.0981599520344347</v>
+        <v>0.09847774317453228</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8471938722913653</v>
+        <v>0.8369867172035175</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1188202508969469</v>
+        <v>0.1196076170635722</v>
       </c>
       <c r="C85">
-        <v>-39327.81931187629</v>
+        <v>-41890.48112390038</v>
       </c>
       <c r="D85">
-        <v>107385.8856881237</v>
+        <v>106590.8588760996</v>
       </c>
       <c r="E85">
-        <v>68457.70500000002</v>
+        <v>70225.34000000003</v>
       </c>
       <c r="F85">
-        <v>146713.705</v>
+        <v>148481.34</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8385,37 +8385,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M85">
-        <v>18271.22843872511</v>
+        <v>18491.36372111939</v>
       </c>
       <c r="N85">
-        <v>-2978.45292852103</v>
+        <v>-3198.58821091531</v>
       </c>
       <c r="O85">
-        <v>-744.6132321302575</v>
+        <v>-799.6470527288275</v>
       </c>
       <c r="P85">
-        <v>-2233.839696390773</v>
+        <v>-2398.941158186482</v>
       </c>
       <c r="Q85">
-        <v>1262.160303609227</v>
+        <v>1097.058841813518</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2181395533063828</v>
+        <v>0.2289107753880318</v>
       </c>
       <c r="T85">
-        <v>3.359218669383283</v>
+        <v>3.569169836219739</v>
       </c>
       <c r="U85">
         <v>0.1245366166625341</v>
       </c>
       <c r="V85">
-        <v>0.2092466793008794</v>
+        <v>0.2067556474044403</v>
       </c>
       <c r="W85">
-        <v>0.09847774317453228</v>
+        <v>0.09878796785891325</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8369867172035175</v>
+        <v>0.8270225896177613</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1196076170635722</v>
+        <v>0.1203949832301975</v>
       </c>
       <c r="C86">
-        <v>-41890.48112390035</v>
+        <v>-44441.45755414625</v>
       </c>
       <c r="D86">
-        <v>106590.8588760996</v>
+        <v>105807.5174458538</v>
       </c>
       <c r="E86">
-        <v>70225.34</v>
+        <v>71992.97500000001</v>
       </c>
       <c r="F86">
-        <v>148481.34</v>
+        <v>150248.975</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8467,37 +8467,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M86">
-        <v>18491.36372111939</v>
+        <v>18711.49900351367</v>
       </c>
       <c r="N86">
-        <v>-3198.588210915306</v>
+        <v>-3418.723493309586</v>
       </c>
       <c r="O86">
-        <v>-799.6470527288266</v>
+        <v>-854.6808733273965</v>
       </c>
       <c r="P86">
-        <v>-2398.94115818648</v>
+        <v>-2564.04261998219</v>
       </c>
       <c r="Q86">
-        <v>1097.05884181352</v>
+        <v>931.9573800178105</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2289107753880316</v>
+        <v>0.2411181604139004</v>
       </c>
       <c r="T86">
-        <v>3.569169836219737</v>
+        <v>3.807114491967719</v>
       </c>
       <c r="U86">
         <v>0.1245366166625341</v>
       </c>
       <c r="V86">
-        <v>0.2067556474044404</v>
+        <v>0.2043232280232117</v>
       </c>
       <c r="W86">
-        <v>0.09878796785891325</v>
+        <v>0.09909089313895585</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8270225896177614</v>
+        <v>0.8172929120928465</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1203949832301975</v>
+        <v>0.1211823493968229</v>
       </c>
       <c r="C87">
-        <v>-44441.45755414625</v>
+        <v>-46981.00435242117</v>
       </c>
       <c r="D87">
-        <v>105807.5174458538</v>
+        <v>105035.6056475788</v>
       </c>
       <c r="E87">
-        <v>71992.97500000001</v>
+        <v>73760.60999999999</v>
       </c>
       <c r="F87">
-        <v>150248.975</v>
+        <v>152016.61</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8549,37 +8549,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M87">
-        <v>18711.49900351367</v>
+        <v>18931.63428590795</v>
       </c>
       <c r="N87">
-        <v>-3418.723493309586</v>
+        <v>-3638.858775703862</v>
       </c>
       <c r="O87">
-        <v>-854.6808733273965</v>
+        <v>-909.7146939259655</v>
       </c>
       <c r="P87">
-        <v>-2564.04261998219</v>
+        <v>-2729.144081777897</v>
       </c>
       <c r="Q87">
-        <v>931.9573800178105</v>
+        <v>766.8559182221034</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2411181604139004</v>
+        <v>0.2550694575863219</v>
       </c>
       <c r="T87">
-        <v>3.807114491967719</v>
+        <v>4.079051241393985</v>
       </c>
       <c r="U87">
         <v>0.1245366166625341</v>
       </c>
       <c r="V87">
-        <v>0.2043232280232117</v>
+        <v>0.2019473765345697</v>
       </c>
       <c r="W87">
-        <v>0.09909089313895585</v>
+        <v>0.09938677364504397</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8172929120928465</v>
+        <v>0.8077895061382787</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1211823493968229</v>
+        <v>0.1476406239405827</v>
       </c>
       <c r="C88">
-        <v>-46981.00435242117</v>
+        <v>-69428.61400623845</v>
       </c>
       <c r="D88">
-        <v>105035.6056475788</v>
+        <v>84355.63099376154</v>
       </c>
       <c r="E88">
-        <v>73760.60999999999</v>
+        <v>75528.245</v>
       </c>
       <c r="F88">
-        <v>152016.61</v>
+        <v>153784.245</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8631,45 +8631,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M88">
-        <v>18931.63428590795</v>
+        <v>23488.48527730222</v>
       </c>
       <c r="N88">
-        <v>-3638.858775703862</v>
+        <v>-8195.709767098142</v>
       </c>
       <c r="O88">
-        <v>-909.7146939259655</v>
+        <v>-2048.927441774536</v>
       </c>
       <c r="P88">
-        <v>-2729.144081777897</v>
+        <v>-6146.782325323607</v>
       </c>
       <c r="Q88">
-        <v>766.8559182221034</v>
+        <v>-2650.782325323607</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2550694575863219</v>
+        <v>0.2799125572247658</v>
       </c>
       <c r="T88">
-        <v>4.079051241393985</v>
+        <v>4.563289493784297</v>
       </c>
       <c r="U88">
-        <v>0.1245366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V88">
-        <v>0.2019473765345697</v>
+        <v>0.1627688559911316</v>
       </c>
       <c r="W88">
-        <v>0.09938677364504397</v>
+        <v>0.1278758523004174</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.8077895061382787</v>
+        <v>0.6510754239645264</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1476406239405827</v>
+        <v>0.197541434185251</v>
       </c>
       <c r="C89">
-        <v>-69428.61400623845</v>
+        <v>-94038.12523215439</v>
       </c>
       <c r="D89">
-        <v>84355.63099376154</v>
+        <v>61513.75476784561</v>
       </c>
       <c r="E89">
-        <v>75528.245</v>
+        <v>77295.88</v>
       </c>
       <c r="F89">
-        <v>153784.245</v>
+        <v>155551.88</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8713,45 +8713,45 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M89">
-        <v>23488.48527730222</v>
+        <v>32158.26938669651</v>
       </c>
       <c r="N89">
-        <v>-8195.709767098142</v>
+        <v>-16865.49387649242</v>
       </c>
       <c r="O89">
-        <v>-2048.927441774536</v>
+        <v>-4216.373469123106</v>
       </c>
       <c r="P89">
-        <v>-6146.782325323607</v>
+        <v>-12649.12040736932</v>
       </c>
       <c r="Q89">
-        <v>-2650.782325323607</v>
+        <v>-9153.120407369317</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2799125572247658</v>
+        <v>0.3103506376438545</v>
       </c>
       <c r="T89">
-        <v>4.563289493784297</v>
+        <v>5.156584335521626</v>
       </c>
       <c r="U89">
-        <v>0.1527366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.1627688559911316</v>
+        <v>0.1188868042486338</v>
       </c>
       <c r="W89">
-        <v>0.1278758523004174</v>
+        <v>0.1821583609863505</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.6510754239645264</v>
+        <v>0.4755472169945353</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.197541434185251</v>
+        <v>0.1991508003518764</v>
       </c>
       <c r="C90">
-        <v>-94038.12523215439</v>
+        <v>-96338.31093275723</v>
       </c>
       <c r="D90">
-        <v>61513.75476784561</v>
+        <v>60981.20406724278</v>
       </c>
       <c r="E90">
-        <v>77295.88</v>
+        <v>79063.51500000001</v>
       </c>
       <c r="F90">
-        <v>155551.88</v>
+        <v>157319.515</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8795,37 +8795,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M90">
-        <v>32158.26938669651</v>
+        <v>32523.70426609079</v>
       </c>
       <c r="N90">
-        <v>-16865.49387649242</v>
+        <v>-17230.9287558867</v>
       </c>
       <c r="O90">
-        <v>-4216.373469123106</v>
+        <v>-4307.732188971676</v>
       </c>
       <c r="P90">
-        <v>-12649.12040736932</v>
+        <v>-12923.19656691503</v>
       </c>
       <c r="Q90">
-        <v>-9153.120407369317</v>
+        <v>-9427.196566915027</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3103506376438545</v>
+        <v>0.3344006956114776</v>
       </c>
       <c r="T90">
-        <v>5.156584335521626</v>
+        <v>5.625364729659956</v>
       </c>
       <c r="U90">
         <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.1188868042486338</v>
+        <v>0.1175509974593233</v>
       </c>
       <c r="W90">
-        <v>0.1821583609863505</v>
+        <v>0.1824345211624875</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4755472169945353</v>
+        <v>0.4702039898372933</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1991508003518764</v>
+        <v>0.2007601665185017</v>
       </c>
       <c r="C91">
-        <v>-96338.31093275723</v>
+        <v>-98629.35474339343</v>
       </c>
       <c r="D91">
-        <v>60981.20406724278</v>
+        <v>60457.79525660657</v>
       </c>
       <c r="E91">
-        <v>79063.51500000001</v>
+        <v>80831.14999999999</v>
       </c>
       <c r="F91">
-        <v>157319.515</v>
+        <v>159087.15</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8877,37 +8877,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M91">
-        <v>32523.70426609079</v>
+        <v>32889.13914548506</v>
       </c>
       <c r="N91">
-        <v>-17230.9287558867</v>
+        <v>-17596.36363528098</v>
       </c>
       <c r="O91">
-        <v>-4307.732188971676</v>
+        <v>-4399.090908820244</v>
       </c>
       <c r="P91">
-        <v>-12923.19656691503</v>
+        <v>-13197.27272646073</v>
       </c>
       <c r="Q91">
-        <v>-9427.196566915027</v>
+        <v>-9701.272726460733</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3344006956114776</v>
+        <v>0.3632607651726253</v>
       </c>
       <c r="T91">
-        <v>5.625364729659956</v>
+        <v>6.187901202625952</v>
       </c>
       <c r="U91">
         <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.1175509974593233</v>
+        <v>0.1162448752653309</v>
       </c>
       <c r="W91">
-        <v>0.1824345211624875</v>
+        <v>0.1827045444458213</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4702039898372933</v>
+        <v>0.4649795010613234</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2007601665185017</v>
+        <v>0.202369532685127</v>
       </c>
       <c r="C92">
-        <v>-98629.35474339343</v>
+        <v>-100911.4900585451</v>
       </c>
       <c r="D92">
-        <v>60457.79525660657</v>
+        <v>59943.29494145492</v>
       </c>
       <c r="E92">
-        <v>80831.14999999999</v>
+        <v>82598.785</v>
       </c>
       <c r="F92">
-        <v>159087.15</v>
+        <v>160854.785</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8959,37 +8959,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M92">
-        <v>32889.13914548506</v>
+        <v>33254.57402487934</v>
       </c>
       <c r="N92">
-        <v>-17596.36363528098</v>
+        <v>-17961.79851467525</v>
       </c>
       <c r="O92">
-        <v>-4399.090908820244</v>
+        <v>-4490.449628668814</v>
       </c>
       <c r="P92">
-        <v>-13197.27272646073</v>
+        <v>-13471.34888600644</v>
       </c>
       <c r="Q92">
-        <v>-9701.272726460733</v>
+        <v>-9975.348886006441</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3632607651726253</v>
+        <v>0.3985341835251393</v>
       </c>
       <c r="T92">
-        <v>6.187901202625952</v>
+        <v>6.875445780695503</v>
       </c>
       <c r="U92">
         <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.1162448752653309</v>
+        <v>0.1149674590536239</v>
       </c>
       <c r="W92">
-        <v>0.1827045444458213</v>
+        <v>0.1829686331514995</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4649795010613234</v>
+        <v>0.4598698362144956</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.202369532685127</v>
+        <v>0.2039788988517524</v>
       </c>
       <c r="C93">
-        <v>-100911.4900585451</v>
+        <v>-103184.9423949173</v>
       </c>
       <c r="D93">
-        <v>59943.29494145492</v>
+        <v>59437.47760508268</v>
       </c>
       <c r="E93">
-        <v>82598.785</v>
+        <v>84366.42000000001</v>
       </c>
       <c r="F93">
-        <v>160854.785</v>
+        <v>162622.42</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -9041,37 +9041,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M93">
-        <v>33254.57402487934</v>
+        <v>33620.00890427362</v>
       </c>
       <c r="N93">
-        <v>-17961.79851467525</v>
+        <v>-18327.23339406954</v>
       </c>
       <c r="O93">
-        <v>-4490.449628668814</v>
+        <v>-4581.808348517385</v>
       </c>
       <c r="P93">
-        <v>-13471.34888600644</v>
+        <v>-13745.42504555215</v>
       </c>
       <c r="Q93">
-        <v>-9975.348886006441</v>
+        <v>-10249.42504555215</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3985341835251393</v>
+        <v>0.4426259564657819</v>
       </c>
       <c r="T93">
-        <v>6.875445780695503</v>
+        <v>7.734876503282444</v>
       </c>
       <c r="U93">
         <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.1149674590536239</v>
+        <v>0.1137178127595628</v>
       </c>
       <c r="W93">
-        <v>0.1829686331514995</v>
+        <v>0.1832269807983586</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4598698362144956</v>
+        <v>0.4548712510382511</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2039788988517524</v>
+        <v>0.2055882650183777</v>
       </c>
       <c r="C94">
-        <v>-103184.9423949173</v>
+        <v>-105449.929721031</v>
       </c>
       <c r="D94">
-        <v>59437.47760508268</v>
+        <v>58940.12527896897</v>
       </c>
       <c r="E94">
-        <v>84366.42000000001</v>
+        <v>86134.05500000002</v>
       </c>
       <c r="F94">
-        <v>162622.42</v>
+        <v>164390.055</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -9123,37 +9123,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M94">
-        <v>33620.00890427362</v>
+        <v>33985.4437836679</v>
       </c>
       <c r="N94">
-        <v>-18327.23339406954</v>
+        <v>-18692.66827346382</v>
       </c>
       <c r="O94">
-        <v>-4581.808348517385</v>
+        <v>-4673.167068365954</v>
       </c>
       <c r="P94">
-        <v>-13745.42504555215</v>
+        <v>-14019.50120509786</v>
       </c>
       <c r="Q94">
-        <v>-10249.42504555215</v>
+        <v>-10523.50120509786</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4426259564657819</v>
+        <v>0.4993153788180366</v>
       </c>
       <c r="T94">
-        <v>7.734876503282444</v>
+        <v>8.839858860894223</v>
       </c>
       <c r="U94">
         <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.1137178127595628</v>
+        <v>0.1124950405793524</v>
       </c>
       <c r="W94">
-        <v>0.1832269807983586</v>
+        <v>0.1834797725818443</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4548712510382511</v>
+        <v>0.4499801623174097</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2055882650183777</v>
+        <v>0.2071976311850031</v>
       </c>
       <c r="C95">
-        <v>-105449.929721031</v>
+        <v>-107706.6627704054</v>
       </c>
       <c r="D95">
-        <v>58940.12527896897</v>
+        <v>58451.02722959465</v>
       </c>
       <c r="E95">
-        <v>86134.05500000002</v>
+        <v>87901.69</v>
       </c>
       <c r="F95">
-        <v>164390.055</v>
+        <v>166157.69</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9205,37 +9205,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M95">
-        <v>33985.4437836679</v>
+        <v>34350.87866306218</v>
       </c>
       <c r="N95">
-        <v>-18692.66827346382</v>
+        <v>-19058.10315285809</v>
       </c>
       <c r="O95">
-        <v>-4673.167068365954</v>
+        <v>-4764.525788214523</v>
       </c>
       <c r="P95">
-        <v>-14019.50120509786</v>
+        <v>-14293.57736464357</v>
       </c>
       <c r="Q95">
-        <v>-10523.50120509786</v>
+        <v>-10797.57736464357</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4993153788180366</v>
+        <v>0.5749012752877094</v>
       </c>
       <c r="T95">
-        <v>8.839858860894223</v>
+        <v>10.31316867104326</v>
       </c>
       <c r="U95">
         <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.1124950405793524</v>
+        <v>0.1112982848285082</v>
       </c>
       <c r="W95">
-        <v>0.1834797725818443</v>
+        <v>0.1837271858167452</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4499801623174097</v>
+        <v>0.445193139314033</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2071976311850031</v>
+        <v>0.2088069973516284</v>
       </c>
       <c r="C96">
-        <v>-107706.6627704054</v>
+        <v>-109955.3453392751</v>
       </c>
       <c r="D96">
-        <v>58451.02722959465</v>
+        <v>57969.97966072486</v>
       </c>
       <c r="E96">
-        <v>87901.69</v>
+        <v>89669.32500000001</v>
       </c>
       <c r="F96">
-        <v>166157.69</v>
+        <v>167925.325</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9287,37 +9287,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M96">
-        <v>34350.87866306218</v>
+        <v>34716.31354245645</v>
       </c>
       <c r="N96">
-        <v>-19058.10315285809</v>
+        <v>-19423.53803225237</v>
       </c>
       <c r="O96">
-        <v>-4764.525788214523</v>
+        <v>-4855.884508063093</v>
       </c>
       <c r="P96">
-        <v>-14293.57736464357</v>
+        <v>-14567.65352418928</v>
       </c>
       <c r="Q96">
-        <v>-10797.57736464357</v>
+        <v>-11071.65352418928</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5749012752877094</v>
+        <v>0.6807215303452515</v>
       </c>
       <c r="T96">
-        <v>10.31316867104326</v>
+        <v>12.37580240525192</v>
       </c>
       <c r="U96">
         <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.1112982848285082</v>
+        <v>0.1101267239355766</v>
       </c>
       <c r="W96">
-        <v>0.1837271858167452</v>
+        <v>0.1839693903519641</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.445193139314033</v>
+        <v>0.4405068957423064</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2088069973516284</v>
+        <v>0.2104163635182538</v>
       </c>
       <c r="C97">
-        <v>-109955.3453392751</v>
+        <v>-112196.1745697276</v>
       </c>
       <c r="D97">
-        <v>57969.97966072486</v>
+        <v>57496.78543027244</v>
       </c>
       <c r="E97">
-        <v>89669.32500000001</v>
+        <v>91436.96000000002</v>
       </c>
       <c r="F97">
-        <v>167925.325</v>
+        <v>169692.96</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9369,37 +9369,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M97">
-        <v>34716.31354245645</v>
+        <v>35081.74842185074</v>
       </c>
       <c r="N97">
-        <v>-19423.53803225237</v>
+        <v>-19788.97291164666</v>
       </c>
       <c r="O97">
-        <v>-4855.884508063093</v>
+        <v>-4947.243227911664</v>
       </c>
       <c r="P97">
-        <v>-14567.65352418928</v>
+        <v>-14841.72968373499</v>
       </c>
       <c r="Q97">
-        <v>-11071.65352418928</v>
+        <v>-11345.72968373499</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6807215303452515</v>
+        <v>0.8394519129315647</v>
       </c>
       <c r="T97">
-        <v>12.37580240525192</v>
+        <v>15.46975300656491</v>
       </c>
       <c r="U97">
         <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.1101267239355766</v>
+        <v>0.1089795705612476</v>
       </c>
       <c r="W97">
-        <v>0.1839693903519641</v>
+        <v>0.1842065489593659</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4405068957423064</v>
+        <v>0.4359182822449906</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2104163635182538</v>
+        <v>0.2120257296848791</v>
       </c>
       <c r="C98">
-        <v>-112196.1745697275</v>
+        <v>-114429.3412190836</v>
       </c>
       <c r="D98">
-        <v>57496.78543027244</v>
+        <v>57031.25378091636</v>
       </c>
       <c r="E98">
-        <v>91436.95999999999</v>
+        <v>93204.595</v>
       </c>
       <c r="F98">
-        <v>169692.96</v>
+        <v>171460.595</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9451,37 +9451,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M98">
-        <v>35081.74842185073</v>
+        <v>35447.18330124501</v>
       </c>
       <c r="N98">
-        <v>-19788.97291164665</v>
+        <v>-20154.40779104093</v>
       </c>
       <c r="O98">
-        <v>-4947.243227911662</v>
+        <v>-5038.601947760231</v>
       </c>
       <c r="P98">
-        <v>-14841.72968373499</v>
+        <v>-15115.80584328069</v>
       </c>
       <c r="Q98">
-        <v>-11345.72968373499</v>
+        <v>-11619.80584328069</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8394519129315626</v>
+        <v>1.104002550575417</v>
       </c>
       <c r="T98">
-        <v>15.46975300656486</v>
+        <v>20.62633734208649</v>
       </c>
       <c r="U98">
         <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.1089795705612477</v>
+        <v>0.1078560698338121</v>
       </c>
       <c r="W98">
-        <v>0.1842065489593659</v>
+        <v>0.1844388176985738</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4359182822449906</v>
+        <v>0.4314242793352485</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2120257296848791</v>
+        <v>0.2136350958515044</v>
       </c>
       <c r="C99">
-        <v>-114429.3412190836</v>
+        <v>-116655.0299162987</v>
       </c>
       <c r="D99">
-        <v>57031.25378091636</v>
+        <v>56573.20008370128</v>
       </c>
       <c r="E99">
-        <v>93204.595</v>
+        <v>94972.23000000001</v>
       </c>
       <c r="F99">
-        <v>171460.595</v>
+        <v>173228.23</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9533,37 +9533,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M99">
-        <v>35447.18330124501</v>
+        <v>35812.61818063929</v>
       </c>
       <c r="N99">
-        <v>-20154.40779104093</v>
+        <v>-20519.84267043521</v>
       </c>
       <c r="O99">
-        <v>-5038.601947760231</v>
+        <v>-5129.960667608802</v>
       </c>
       <c r="P99">
-        <v>-15115.80584328069</v>
+        <v>-15389.88200282641</v>
       </c>
       <c r="Q99">
-        <v>-11619.80584328069</v>
+        <v>-11893.88200282641</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.104002550575417</v>
+        <v>1.633103825863125</v>
       </c>
       <c r="T99">
-        <v>20.62633734208649</v>
+        <v>30.93950601312973</v>
       </c>
       <c r="U99">
         <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.1078560698338121</v>
+        <v>0.1067554976926508</v>
       </c>
       <c r="W99">
-        <v>0.1844388176985738</v>
+        <v>0.1846663462594305</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4314242793352485</v>
+        <v>0.4270219907706031</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2136350958515044</v>
+        <v>0.2152444620181298</v>
       </c>
       <c r="C100">
-        <v>-116655.0299162987</v>
+        <v>-118873.4194061051</v>
       </c>
       <c r="D100">
-        <v>56573.20008370128</v>
+        <v>56122.4455938949</v>
       </c>
       <c r="E100">
-        <v>94972.23000000001</v>
+        <v>96739.86499999999</v>
       </c>
       <c r="F100">
-        <v>173228.23</v>
+        <v>174995.865</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9615,37 +9615,37 @@
         <v>15292.77551020408</v>
       </c>
       <c r="M100">
-        <v>35812.61818063929</v>
+        <v>36178.05306003356</v>
       </c>
       <c r="N100">
-        <v>-20519.84267043521</v>
+        <v>-20885.27754982948</v>
       </c>
       <c r="O100">
-        <v>-5129.960667608802</v>
+        <v>-5221.31938745737</v>
       </c>
       <c r="P100">
-        <v>-15389.88200282641</v>
+        <v>-15663.95816237211</v>
       </c>
       <c r="Q100">
-        <v>-11893.88200282641</v>
+        <v>-12167.95816237211</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.633103825863125</v>
+        <v>3.220407651726251</v>
       </c>
       <c r="T100">
-        <v>30.93950601312973</v>
+        <v>61.87901202625946</v>
       </c>
       <c r="U100">
         <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.1067554976926508</v>
+        <v>0.105677159332119</v>
       </c>
       <c r="W100">
-        <v>0.1846663462594305</v>
+        <v>0.1848892782837043</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4270219907706031</v>
+        <v>0.4227086373284759</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2152444620181298</v>
-      </c>
-      <c r="C101">
-        <v>-118873.4194061051</v>
-      </c>
-      <c r="D101">
-        <v>56122.4455938949</v>
-      </c>
-      <c r="E101">
-        <v>96739.86499999999</v>
-      </c>
-      <c r="F101">
-        <v>174995.865</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>98507.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>18788.77551020408</v>
-      </c>
-      <c r="K101">
-        <v>3496</v>
-      </c>
-      <c r="L101">
-        <v>15292.77551020408</v>
-      </c>
-      <c r="M101">
-        <v>36178.05306003356</v>
-      </c>
-      <c r="N101">
-        <v>-20885.27754982948</v>
-      </c>
-      <c r="O101">
-        <v>-5221.31938745737</v>
-      </c>
-      <c r="P101">
-        <v>-15663.95816237211</v>
-      </c>
-      <c r="Q101">
-        <v>-12167.95816237211</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.220407651726251</v>
-      </c>
-      <c r="T101">
-        <v>61.87901202625946</v>
-      </c>
-      <c r="U101">
-        <v>0.2067366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.105677159332119</v>
-      </c>
-      <c r="W101">
-        <v>0.1848892782837043</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4227086373284759</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
